--- a/tasks/phantichchuyensau/Mô tả logic công thức.xlsx
+++ b/tasks/phantichchuyensau/Mô tả logic công thức.xlsx
@@ -3,14 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30327"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="778" documentId="11_EB9E6C1DC9145D802531B83E79C2F3D43A475373" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77FCE5FF-C66F-4DC2-ADEF-06237112C2E9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FA09933B-E8D5-4786-9452-6C6D623F126B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Phân tích chuyên sâu" sheetId="1" r:id="rId1"/>
     <sheet name="Cấu hình cảnh báo" sheetId="2" r:id="rId2"/>
-    <sheet name="Nhom chi tieu" sheetId="4" r:id="rId3"/>
+    <sheet name="Nhóm chỉ tiêu - chỉ tiêu" sheetId="4" r:id="rId3"/>
+    <sheet name="Biến số khả dụng" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="576">
   <si>
     <t>STT</t>
   </si>
@@ -50,6 +51,9 @@
     <t>Chỉ số</t>
   </si>
   <si>
+    <t>field</t>
+  </si>
+  <si>
     <t>Công thức</t>
   </si>
   <si>
@@ -80,6 +84,9 @@
     <t>kỳ báo cáo gần nhất</t>
   </si>
   <si>
+    <t>dm_du_an.ky_bao_cao_gan_nhat_key</t>
+  </si>
+  <si>
     <t>raw</t>
   </si>
   <si>
@@ -96,6 +103,9 @@
   </si>
   <si>
     <t>Tên dự án</t>
+  </si>
+  <si>
+    <t>dm_du_an.ten_du_an</t>
   </si>
   <si>
     <t>tenDuAn</t>
@@ -108,6 +118,9 @@
     <t>Tên KCN/KKT</t>
   </si>
   <si>
+    <t>dm_du_an.dia_diem_thuc_hien</t>
+  </si>
+  <si>
     <t>diaDiemThucHien (chuỗi tự do)</t>
   </si>
   <si>
@@ -120,6 +133,9 @@
     <t>Ngày nộp báo cáo gần nhất</t>
   </si>
   <si>
+    <t>dm_du_an.ngay_nop_bc_gan_nhat</t>
+  </si>
+  <si>
     <t>NgayNop</t>
   </si>
   <si>
@@ -129,6 +145,9 @@
     <t>Đơn vị quản lý</t>
   </si>
   <si>
+    <t>dm_du_an.ten_tckt</t>
+  </si>
+  <si>
     <t>tenTCKT</t>
   </si>
   <si>
@@ -144,6 +163,9 @@
     <t>Lĩnh vực</t>
   </si>
   <si>
+    <t>dm_nganh.ten_nganh</t>
+  </si>
+  <si>
     <t>lấy từ raw mã ngành mapping sang bảng ngành</t>
   </si>
   <si>
@@ -156,6 +178,9 @@
     <t>Tổng mức đầu tư</t>
   </si>
   <si>
+    <t>bc_dinh_ky.tong_von_dau_tu_dang_ky</t>
+  </si>
+  <si>
     <t>raw (tổng vốn đầu tư đăng ký)</t>
   </si>
   <si>
@@ -168,6 +193,10 @@
     <t>Tỷ lệ giải ngân</t>
   </si>
   <si>
+    <t>bc_dinh_ky.von_dau_tu_thuc_hien_luy_ke_gcndt
+bc_dinh_ky.tong_von_dau_tu_dang_ky</t>
+  </si>
+  <si>
     <t>vốn đầu tư thực hiện lũy kế từ lúc đky / tổng vốn đầu tư đăng ký</t>
   </si>
   <si>
@@ -184,6 +213,9 @@
   </si>
   <si>
     <t>Tiến độ thực tế</t>
+  </si>
+  <si>
+    <t>bc_dinh_ky.tien_do_trang_thai</t>
   </si>
   <si>
     <t>Suy luận (fallback) từ khoKhanVuongMac: NẾU khoKhanVuongMac là null / rỗng / "không" / "không có" → mặc định "Đúng tiến độ"; NGƯỢC LẠI (có nội dung mô tả khó khăn) → "Gặp khó khăn"</t>
@@ -222,6 +254,9 @@
     <t>Tình hình hoạt động</t>
   </si>
   <si>
+    <t>dm_du_an.trang_thai_hoat_dong</t>
+  </si>
+  <si>
     <t>moTaChiTiet.tinhTrangDuAn/ 
 moTaChiTiet.tinhHinhThucHienMucTieu</t>
   </si>
@@ -232,6 +267,9 @@
     <t>rule-based hoặc llm</t>
   </si>
   <si>
+    <t>ai_insight</t>
+  </si>
+  <si>
     <t>Tiến độ thực hiện</t>
   </si>
   <si>
@@ -241,6 +279,9 @@
     <t>Khó khăn, vướng mắc</t>
   </si>
   <si>
+    <t>bc_dinh_ky.kho_khan_vuong_mac</t>
+  </si>
+  <si>
     <t>khoKhanVuongMac</t>
   </si>
   <si>
@@ -251,6 +292,10 @@
   </si>
   <si>
     <t>raw tên báo cáo</t>
+  </si>
+  <si>
+    <t>bổ sung vào bc_dinh_ky
+bc_dinh_ky.ten_bao_cao</t>
   </si>
   <si>
     <t>mapping sang bảng LoaiBaoCaos với trường TenLoaiBaoCao thông qua LoaiBaoCaoId</t>
@@ -386,6 +431,9 @@
   </si>
   <si>
     <t>Kỳ báo cáo (trục X)</t>
+  </si>
+  <si>
+    <t>bc_dinh_ky.ky_key</t>
   </si>
   <si>
     <t>Lấy từ data raw: danh sách kỳ báo cáo (Quý/Năm) đã ghi nhận</t>
@@ -1455,6 +1503,9 @@
     <t>Doanh thu</t>
   </si>
   <si>
+    <t>bc_dinh_ky.doanh_thu_thuan_ky</t>
+  </si>
+  <si>
     <t>doanhThuThuan.cotA</t>
   </si>
   <si>
@@ -1467,6 +1518,9 @@
     <t>Lợi nhuận</t>
   </si>
   <si>
+    <t>bc_dinh_ky.loi_nhuan</t>
+  </si>
+  <si>
     <t>loiNhuan.nam</t>
   </si>
   <si>
@@ -1476,12 +1530,18 @@
     <t>Lợi nhuận sau thuế</t>
   </si>
   <si>
+    <t>bc_dinh_ky.loi_nhuan_sau_thue_ky</t>
+  </si>
+  <si>
     <t>loiNhuanSauThue.cotA</t>
   </si>
   <si>
     <t>Thu khác</t>
   </si>
   <si>
+    <t>bc_dinh_ky.nguon_thu_khac_ky</t>
+  </si>
+  <si>
     <t>nguonThuKhac.nam</t>
   </si>
   <si>
@@ -1491,18 +1551,27 @@
     <t>Xuất khẩu</t>
   </si>
   <si>
+    <t>bc_dinh_ky.gia_tri_xuat_khau_ky</t>
+  </si>
+  <si>
     <t>giaTriHangXuatKhau.cotA</t>
   </si>
   <si>
     <t>Nhập khẩu</t>
   </si>
   <si>
+    <t>bc_dinh_ky.gia_tri_nhap_khau_ky</t>
+  </si>
+  <si>
     <t>giaTriHangNhapKhau.cotA</t>
   </si>
   <si>
     <t>Thuế và nộp ngân sách</t>
   </si>
   <si>
+    <t>bc_dinh_ky.thue_va_nop_ngan_sach_ky</t>
+  </si>
+  <si>
     <t>thueVaKhoanNopNSNN.cotA</t>
   </si>
   <si>
@@ -1515,6 +1584,9 @@
     <t>R&amp;D</t>
   </si>
   <si>
+    <t>bc_dinh_ky.chi_phi_rd_ky</t>
+  </si>
+  <si>
     <t>chiPhiRD.cotA</t>
   </si>
   <si>
@@ -1527,6 +1599,9 @@
     <t>Môi trường</t>
   </si>
   <si>
+    <t>bc_dinh_ky.chi_phi_moi_truong_ky</t>
+  </si>
+  <si>
     <t>chiPhiMoiTruong.cotA</t>
   </si>
   <si>
@@ -1548,6 +1623,9 @@
     <t>Vốn đầu tư thực hiện</t>
   </si>
   <si>
+    <t>bc_dinh_ky.von_dau_tu_thuc_hien_luy_ke_gcndt</t>
+  </si>
+  <si>
     <t>=vonVaycotC + vonGop.cotC + loiNhuanTaiDauTu.cotC</t>
   </si>
   <si>
@@ -1557,15 +1635,16 @@
     <t>=vonVay.cotB + vonGop.cotB</t>
   </si>
   <si>
-    <t>=vonVay.cotC + vonGop.cotC + loiNhuanTaiDauTu.cotC</t>
-  </si>
-  <si>
     <t>vonChuyenRa.luyke</t>
   </si>
   <si>
     <t>Vốn vay</t>
   </si>
   <si>
+    <t>bc_dinh_ky.von_vay_ky
+bc_dinh_ky.von_vay_luy_ke_gcndt</t>
+  </si>
+  <si>
     <t>vonVaycotA</t>
   </si>
   <si>
@@ -1584,6 +1663,10 @@
     <t>Vốn góp</t>
   </si>
   <si>
+    <t>bc_dinh_ky.von_gop_ky
+bc_dinh_ky.von_gop_luy_ke_gcndt</t>
+  </si>
+  <si>
     <t>vonGop.cotA</t>
   </si>
   <si>
@@ -1597,6 +1680,10 @@
   </si>
   <si>
     <t>Lợi nhuận tái đầu tư</t>
+  </si>
+  <si>
+    <t>bc_dinh_ky.loi_nhuan_tai_dau_tu_ky
+bc_dinh_ky.loi_nhuan_tai_dau_tu_luy_ke_gcndt</t>
   </si>
   <si>
     <t>loiNhuanTaiDauTu.cotA</t>
@@ -1636,8 +1723,126 @@
     <t>Nộp báo cáo định kỳ</t>
   </si>
   <si>
+    <t>bc_dinh_ky.ngay_nop_bao_cao</t>
+  </si>
+  <si>
+    <t>check NgayNop trong bảng BaoCaos với hạn nộp bc (fix):
+Trước ngày 10 tháng đầu quý sau (vd hạn nộp bc quý I 2026 là 10/4)</t>
+  </si>
+  <si>
     <t>check NgayNop trong bảng BaoCaos với hạn nộp bc:
 Trước ngày 10 tháng đầu quý sau (vd hạn nộp bc quý I 2026 là 10/4)</t>
+  </si>
+  <si>
+    <t>bc_tuan_thu_chi_tiet.trang_thai</t>
+  </si>
+  <si>
+    <t>Tên biến số khả dụng</t>
+  </si>
+  <si>
+    <t>Tên field tương ứng</t>
+  </si>
+  <si>
+    <t>tong_von_dau_tu_dang_ky</t>
+  </si>
+  <si>
+    <t>gcnđt</t>
+  </si>
+  <si>
+    <t>Vốn đầu tư thực hiện lũy kế gcndt</t>
+  </si>
+  <si>
+    <t>von_dau_tu_thuc_hien_luy_ke_gcndt</t>
+  </si>
+  <si>
+    <t>Vốn góp kỳ báo cáo</t>
+  </si>
+  <si>
+    <t>von_gop_ky</t>
+  </si>
+  <si>
+    <t>Vốn góp lũy kế gcndt</t>
+  </si>
+  <si>
+    <t>von_gop_luy_ke_gcndt</t>
+  </si>
+  <si>
+    <t>Vốn vay kỳ báo cáo</t>
+  </si>
+  <si>
+    <t>von_vay_ky</t>
+  </si>
+  <si>
+    <t>Vốn vay lũy kế gcndt</t>
+  </si>
+  <si>
+    <t>von_vay_luy_ke_gcndt</t>
+  </si>
+  <si>
+    <t>Lợi nhuận tái đầu tư kỳ báo cáo</t>
+  </si>
+  <si>
+    <t>loi_nhuan_tai_dau_tu_ky</t>
+  </si>
+  <si>
+    <t>Lợi nhuận tái đầu tư lũy kế gcndt</t>
+  </si>
+  <si>
+    <t>loi_nhuan_tai_dau_tu_luy_ke_gcndt</t>
+  </si>
+  <si>
+    <t>Doanh thu thuần kỳ báo cáo</t>
+  </si>
+  <si>
+    <t>doanh_thu_thuan_ky</t>
+  </si>
+  <si>
+    <t>Giá trị xuất khẩu kỳ báo cáo</t>
+  </si>
+  <si>
+    <t>gia_tri_xuat_khau_ky</t>
+  </si>
+  <si>
+    <t>Giá trị nhập khẩu kỳ báo cáo</t>
+  </si>
+  <si>
+    <t>gia_tri_nhap_khau_ky</t>
+  </si>
+  <si>
+    <t>Thuế và nộp ngân sách kỳ báo cáo</t>
+  </si>
+  <si>
+    <t>thue_va_nop_ngan_sach_ky</t>
+  </si>
+  <si>
+    <t>Lợi nhuận sau thuế kỳ báo cáo</t>
+  </si>
+  <si>
+    <t>loi_nhuan_sau_thue_ky</t>
+  </si>
+  <si>
+    <t>Chi phí R&amp;D kỳ báo cáo</t>
+  </si>
+  <si>
+    <t>chi_phi_rd_ky</t>
+  </si>
+  <si>
+    <t>Chi phí môi trường kỳ báo cáo</t>
+  </si>
+  <si>
+    <t>chi_phi_moi_truong_ky</t>
+  </si>
+  <si>
+    <t>Nguồn thu khác kỳ báo cáo</t>
+  </si>
+  <si>
+    <t>nguon_thu_khac_ky</t>
+  </si>
+  <si>
+    <t>Lợi nhuân kỳ báo cáo</t>
+  </si>
+  <si>
+    <t>loi_nhuan</t>
   </si>
 </sst>
 </file>
@@ -1751,7 +1956,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1880,49 +2085,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2028,45 +2195,40 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2086,10 +2248,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2404,19 +2562,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R159"/>
+  <dimension ref="A1:S159"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="2"/>
     <col min="2" max="2" width="21.5703125" style="1" customWidth="1"/>
     <col min="3" max="3" width="37.85546875" style="1" customWidth="1"/>
     <col min="4" max="4" width="24.140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="72.7109375" style="1" customWidth="1"/>
-    <col min="6" max="11" width="54.7109375" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="5" max="5" width="45.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="72.7109375" style="1" customWidth="1"/>
+    <col min="7" max="12" width="54.7109375" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="2" customFormat="1">
+    <row r="1" spans="1:19" s="2" customFormat="1">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2432,7 +2591,7 @@
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="22" t="s">
@@ -2450,2849 +2609,2993 @@
       <c r="K1" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="23"/>
-      <c r="N1" s="24"/>
+      <c r="L1" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="23"/>
       <c r="O1" s="24"/>
       <c r="P1" s="24"/>
       <c r="Q1" s="24"/>
-      <c r="R1" s="25"/>
-    </row>
-    <row r="2" spans="1:18" ht="30.75" customHeight="1">
+      <c r="R1" s="24"/>
+      <c r="S1" s="25"/>
+    </row>
+    <row r="2" spans="1:19" ht="30.75" customHeight="1">
       <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="52" t="s">
+      <c r="B2" s="52" t="s">
         <v>12</v>
       </c>
+      <c r="C2" s="51" t="s">
+        <v>13</v>
+      </c>
       <c r="D2" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14" t="s">
+      <c r="F2" s="17" t="s">
         <v>16</v>
       </c>
+      <c r="G2" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="14"/>
       <c r="I2" s="14" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J2" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="32" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" ht="28.5">
+      <c r="K2" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" s="32" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="28.5">
       <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="54"/>
-      <c r="C3" s="52"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="51"/>
       <c r="D3" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="33" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>16</v>
       </c>
       <c r="G3" s="33" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H3" s="33" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I3" s="33" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J3" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" s="15"/>
-    </row>
-    <row r="4" spans="1:18" ht="43.5">
+        <v>23</v>
+      </c>
+      <c r="K3" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="15"/>
+    </row>
+    <row r="4" spans="1:19" ht="43.5">
       <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="54"/>
-      <c r="C4" s="52"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="51"/>
       <c r="D4" s="5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="33" t="s">
-        <v>23</v>
+        <v>26</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>16</v>
       </c>
       <c r="G4" s="33" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H4" s="33" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I4" s="33" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J4" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="K4" s="32" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" ht="43.5">
+        <v>27</v>
+      </c>
+      <c r="K4" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="L4" s="32" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="30.75">
       <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="54"/>
-      <c r="C5" s="52"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="51"/>
       <c r="D5" s="5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="33" t="s">
-        <v>27</v>
+        <v>31</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>16</v>
       </c>
       <c r="G5" s="33" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H5" s="33" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="I5" s="33" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J5" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="K5" s="32" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" ht="28.5">
+        <v>32</v>
+      </c>
+      <c r="K5" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" s="32" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19">
       <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="54"/>
-      <c r="C6" s="52"/>
+      <c r="B6" s="53"/>
+      <c r="C6" s="51"/>
       <c r="D6" s="5" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="33" t="s">
-        <v>30</v>
+        <v>35</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>16</v>
       </c>
       <c r="G6" s="33" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H6" s="33" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I6" s="33" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J6" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="K6" s="32" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18">
+        <v>36</v>
+      </c>
+      <c r="K6" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="L6" s="32" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="30.75">
       <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" s="54"/>
-      <c r="C7" s="52"/>
+      <c r="B7" s="53"/>
+      <c r="C7" s="51"/>
       <c r="D7" s="5" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="33" t="s">
         <v>15</v>
       </c>
+      <c r="F7" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G7" s="33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H7" s="33" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I7" s="33" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J7" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="K7" s="15"/>
-    </row>
-    <row r="8" spans="1:18" ht="57.75">
+      <c r="K7" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="L7" s="15"/>
+    </row>
+    <row r="8" spans="1:19" ht="43.5">
       <c r="A8" s="4">
         <v>7</v>
       </c>
-      <c r="B8" s="54"/>
-      <c r="C8" s="52"/>
+      <c r="B8" s="53"/>
+      <c r="C8" s="51"/>
       <c r="D8" s="5" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="F8" s="33"/>
+        <v>41</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>42</v>
+      </c>
       <c r="G8" s="33"/>
       <c r="H8" s="33"/>
       <c r="I8" s="33"/>
       <c r="J8" s="33"/>
-      <c r="K8" s="32" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" ht="28.5">
+      <c r="K8" s="33"/>
+      <c r="L8" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="30.75">
       <c r="A9" s="4">
         <v>8</v>
       </c>
-      <c r="B9" s="54"/>
-      <c r="C9" s="53" t="s">
-        <v>37</v>
+      <c r="B9" s="53"/>
+      <c r="C9" s="52" t="s">
+        <v>44</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="33" t="s">
-        <v>40</v>
+        <v>46</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>47</v>
       </c>
       <c r="G9" s="33" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="H9" s="33" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="I9" s="33" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="J9" s="33" t="s">
-        <v>41</v>
-      </c>
-      <c r="K9" s="15"/>
-    </row>
-    <row r="10" spans="1:18" ht="60.75" customHeight="1">
+        <v>48</v>
+      </c>
+      <c r="K9" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="15"/>
+    </row>
+    <row r="10" spans="1:19" ht="60.75" customHeight="1">
       <c r="A10" s="4">
         <v>9</v>
       </c>
-      <c r="B10" s="54"/>
-      <c r="C10" s="54"/>
+      <c r="B10" s="53"/>
+      <c r="C10" s="53"/>
       <c r="D10" s="5" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="F10" s="33" t="s">
-        <v>44</v>
+        <v>51</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>52</v>
       </c>
       <c r="G10" s="33" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="H10" s="33" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="I10" s="33" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="J10" s="33" t="s">
-        <v>47</v>
-      </c>
-      <c r="K10" s="32"/>
-    </row>
-    <row r="11" spans="1:18" ht="78.75" customHeight="1">
+        <v>53</v>
+      </c>
+      <c r="K10" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="L10" s="32"/>
+    </row>
+    <row r="11" spans="1:19" ht="78.75" customHeight="1">
       <c r="A11" s="4">
         <v>10</v>
       </c>
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
+      <c r="B11" s="53"/>
+      <c r="C11" s="53"/>
       <c r="D11" s="5" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="33" t="s">
-        <v>49</v>
+        <v>58</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>14</v>
       </c>
       <c r="G11" s="33" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="H11" s="33" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="I11" s="33" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="J11" s="33" t="s">
-        <v>50</v>
-      </c>
-      <c r="K11" s="32" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18">
+        <v>59</v>
+      </c>
+      <c r="K11" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="L11" s="32" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19">
       <c r="A12" s="4">
         <v>12</v>
       </c>
-      <c r="B12" s="54"/>
-      <c r="C12" s="54"/>
+      <c r="B12" s="53"/>
+      <c r="C12" s="53"/>
       <c r="D12" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F12" s="33" t="s">
-        <v>54</v>
+        <v>62</v>
+      </c>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17" t="s">
+        <v>63</v>
       </c>
       <c r="G12" s="33" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="H12" s="33" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="I12" s="33" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="J12" s="33" t="s">
-        <v>54</v>
-      </c>
-      <c r="K12" s="32"/>
-    </row>
-    <row r="13" spans="1:18" ht="63.75" customHeight="1">
+        <v>64</v>
+      </c>
+      <c r="K12" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="L12" s="32"/>
+    </row>
+    <row r="13" spans="1:19" ht="63.75" customHeight="1">
       <c r="A13" s="4">
         <v>13</v>
       </c>
-      <c r="B13" s="55"/>
-      <c r="C13" s="55"/>
+      <c r="B13" s="54"/>
+      <c r="C13" s="54"/>
       <c r="D13" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E13" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="F13" s="14" t="s">
-        <v>57</v>
+        <v>65</v>
+      </c>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17" t="s">
+        <v>66</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="H13" s="14" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="K13" s="15"/>
-    </row>
-    <row r="14" spans="1:18" ht="30.75">
+        <v>67</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="L13" s="15"/>
+    </row>
+    <row r="14" spans="1:19" ht="30.75">
       <c r="A14" s="4">
         <v>14</v>
       </c>
-      <c r="B14" s="52" t="s">
-        <v>58</v>
+      <c r="B14" s="51" t="s">
+        <v>68</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="17"/>
-      <c r="F14" s="14"/>
+        <v>16</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="F14" s="17"/>
       <c r="G14" s="14"/>
       <c r="H14" s="14"/>
       <c r="I14" s="14"/>
-      <c r="J14" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="K14" s="32"/>
-    </row>
-    <row r="15" spans="1:18">
+      <c r="J14" s="14"/>
+      <c r="K14" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="L14" s="32"/>
+    </row>
+    <row r="15" spans="1:19">
       <c r="A15" s="4">
         <v>15</v>
       </c>
-      <c r="B15" s="52"/>
+      <c r="B15" s="51"/>
       <c r="C15" s="5" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E15" s="17"/>
-      <c r="F15" s="14"/>
+        <v>73</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="F15" s="17"/>
       <c r="G15" s="14"/>
       <c r="H15" s="14"/>
       <c r="I15" s="14"/>
       <c r="J15" s="14"/>
-      <c r="K15" s="32"/>
-    </row>
-    <row r="16" spans="1:18">
+      <c r="K15" s="14"/>
+      <c r="L15" s="32"/>
+    </row>
+    <row r="16" spans="1:19">
       <c r="A16" s="4">
         <v>16</v>
       </c>
-      <c r="B16" s="52"/>
+      <c r="B16" s="51"/>
       <c r="C16" s="5" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E16" s="17"/>
-      <c r="F16" s="33"/>
+        <v>73</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="F16" s="17"/>
       <c r="G16" s="33"/>
       <c r="H16" s="33"/>
       <c r="I16" s="33"/>
-      <c r="J16" s="33" t="s">
-        <v>64</v>
-      </c>
-      <c r="K16" s="15"/>
-    </row>
-    <row r="17" spans="1:11" ht="28.5">
+      <c r="J16" s="33"/>
+      <c r="K16" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="L16" s="15"/>
+    </row>
+    <row r="17" spans="1:12" ht="30.75">
       <c r="A17" s="4">
         <v>17</v>
       </c>
-      <c r="B17" s="52"/>
+      <c r="B17" s="51"/>
       <c r="C17" s="5" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" s="17"/>
-      <c r="F17" s="14" t="s">
-        <v>66</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="F17" s="17"/>
       <c r="G17" s="14" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="H17" s="14" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="J17" s="33" t="s">
-        <v>67</v>
-      </c>
-      <c r="K17" s="15"/>
-    </row>
-    <row r="18" spans="1:11" ht="45.75">
+        <v>79</v>
+      </c>
+      <c r="J17" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="K17" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="L17" s="15"/>
+    </row>
+    <row r="18" spans="1:12" ht="30.75">
       <c r="A18" s="4">
         <v>18</v>
       </c>
-      <c r="B18" s="52"/>
+      <c r="B18" s="51"/>
       <c r="C18" s="5" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E18" s="17"/>
-      <c r="F18" s="13" t="s">
-        <v>70</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="F18" s="17"/>
       <c r="G18" s="13" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="K18" s="15"/>
-    </row>
-    <row r="19" spans="1:11" ht="173.25">
+        <v>84</v>
+      </c>
+      <c r="K18" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="L18" s="15"/>
+    </row>
+    <row r="19" spans="1:12" ht="144">
       <c r="A19" s="4">
         <v>19</v>
       </c>
-      <c r="B19" s="51" t="s">
-        <v>71</v>
-      </c>
-      <c r="C19" s="51" t="s">
-        <v>72</v>
+      <c r="B19" s="50" t="s">
+        <v>85</v>
+      </c>
+      <c r="C19" s="50" t="s">
+        <v>86</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="E19" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="F19" s="33" t="s">
-        <v>75</v>
+        <v>87</v>
+      </c>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18" t="s">
+        <v>88</v>
       </c>
       <c r="G19" s="33" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="H19" s="33" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="I19" s="33" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="J19" s="33" t="s">
-        <v>78</v>
-      </c>
-      <c r="K19" s="32" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="115.5">
+        <v>89</v>
+      </c>
+      <c r="K19" s="33" t="s">
+        <v>92</v>
+      </c>
+      <c r="L19" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="86.25">
       <c r="A20" s="4">
         <v>20</v>
       </c>
-      <c r="B20" s="51"/>
-      <c r="C20" s="51"/>
+      <c r="B20" s="50"/>
+      <c r="C20" s="50"/>
       <c r="D20" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="E20" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="F20" s="34" t="s">
-        <v>82</v>
+        <v>94</v>
+      </c>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18" t="s">
+        <v>95</v>
       </c>
       <c r="G20" s="34" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="H20" s="34" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="I20" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="J20" s="33" t="s">
-        <v>85</v>
-      </c>
-      <c r="K20" s="32"/>
-    </row>
-    <row r="21" spans="1:11" ht="115.5">
+        <v>98</v>
+      </c>
+      <c r="J20" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="K20" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="L20" s="32"/>
+    </row>
+    <row r="21" spans="1:12" ht="86.25">
       <c r="A21" s="4">
         <v>21</v>
       </c>
-      <c r="B21" s="51"/>
-      <c r="C21" s="51"/>
+      <c r="B21" s="50"/>
+      <c r="C21" s="50"/>
       <c r="D21" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="E21" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="F21" s="34" t="s">
-        <v>88</v>
+        <v>100</v>
+      </c>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18" t="s">
+        <v>101</v>
       </c>
       <c r="G21" s="34" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="H21" s="34" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I21" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="J21" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="K21" s="15"/>
-    </row>
-    <row r="22" spans="1:11" ht="72">
+        <v>104</v>
+      </c>
+      <c r="J21" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="K21" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="L21" s="15"/>
+    </row>
+    <row r="22" spans="1:12" ht="43.5">
       <c r="A22" s="4">
         <v>22</v>
       </c>
-      <c r="B22" s="51"/>
-      <c r="C22" s="51" t="s">
-        <v>92</v>
+      <c r="B22" s="50"/>
+      <c r="C22" s="50" t="s">
+        <v>106</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="E22" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="F22" s="35" t="s">
-        <v>95</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>96</v>
+        <v>107</v>
+      </c>
+      <c r="E22" s="18"/>
+      <c r="F22" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="G22" s="35" t="s">
+        <v>109</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="I22" s="35" t="s">
-        <v>95</v>
-      </c>
-      <c r="J22" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="K22" s="32" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="115.5">
+        <v>110</v>
+      </c>
+      <c r="I22" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="J22" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="K22" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="L22" s="32" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="86.25">
       <c r="A23" s="4">
         <v>23</v>
       </c>
-      <c r="B23" s="51"/>
-      <c r="C23" s="51"/>
+      <c r="B23" s="50"/>
+      <c r="C23" s="50"/>
       <c r="D23" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E23" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="F23" s="34" t="s">
-        <v>88</v>
+        <v>113</v>
+      </c>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18" t="s">
+        <v>101</v>
       </c>
       <c r="G23" s="34" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="H23" s="34" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I23" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="J23" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="K23" s="32" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="115.5">
+        <v>104</v>
+      </c>
+      <c r="J23" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="K23" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="L23" s="32" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="86.25">
       <c r="A24" s="4">
         <v>24</v>
       </c>
-      <c r="B24" s="51"/>
-      <c r="C24" s="51"/>
+      <c r="B24" s="50"/>
+      <c r="C24" s="50"/>
       <c r="D24" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="E24" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="F24" s="34" t="s">
-        <v>82</v>
+        <v>115</v>
+      </c>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18" t="s">
+        <v>95</v>
       </c>
       <c r="G24" s="34" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="H24" s="34" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="I24" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="J24" s="33" t="s">
-        <v>85</v>
-      </c>
-      <c r="K24" s="32" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="72">
+        <v>98</v>
+      </c>
+      <c r="J24" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="K24" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="L24" s="32" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="43.5">
       <c r="A25" s="4">
         <v>25</v>
       </c>
-      <c r="B25" s="51"/>
-      <c r="C25" s="51"/>
+      <c r="B25" s="50"/>
+      <c r="C25" s="50"/>
       <c r="D25" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="E25" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="F25" s="14"/>
+        <v>116</v>
+      </c>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18" t="s">
+        <v>117</v>
+      </c>
       <c r="G25" s="14"/>
       <c r="H25" s="14"/>
       <c r="I25" s="14"/>
       <c r="J25" s="14"/>
-      <c r="K25" s="32" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="45.75">
+      <c r="K25" s="14"/>
+      <c r="L25" s="32" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="45.75">
       <c r="A26" s="4">
         <v>26</v>
       </c>
-      <c r="B26" s="51"/>
-      <c r="C26" s="51"/>
+      <c r="B26" s="50"/>
+      <c r="C26" s="50"/>
       <c r="D26" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="E26" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="F26" s="14"/>
+        <v>119</v>
+      </c>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18" t="s">
+        <v>120</v>
+      </c>
       <c r="G26" s="14"/>
       <c r="H26" s="14"/>
       <c r="I26" s="14"/>
       <c r="J26" s="14"/>
-      <c r="K26" s="32" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="45.75">
+      <c r="K26" s="14"/>
+      <c r="L26" s="32" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="45.75">
       <c r="A27" s="4">
         <v>27</v>
       </c>
-      <c r="B27" s="51"/>
+      <c r="B27" s="50"/>
       <c r="C27" s="6" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="E27" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="F27" s="14"/>
+        <v>123</v>
+      </c>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18" t="s">
+        <v>124</v>
+      </c>
       <c r="G27" s="14"/>
       <c r="H27" s="14"/>
       <c r="I27" s="14"/>
       <c r="J27" s="14"/>
-      <c r="K27" s="32"/>
-    </row>
-    <row r="28" spans="1:11">
+      <c r="K27" s="14"/>
+      <c r="L27" s="32"/>
+    </row>
+    <row r="28" spans="1:12">
       <c r="A28" s="4">
         <v>28</v>
       </c>
-      <c r="B28" s="51" t="s">
-        <v>63</v>
-      </c>
-      <c r="C28" s="51" t="s">
-        <v>111</v>
+      <c r="B28" s="50" t="s">
+        <v>75</v>
+      </c>
+      <c r="C28" s="50" t="s">
+        <v>125</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="F28" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="G28" s="14" t="s">
-        <v>16</v>
+        <v>127</v>
+      </c>
+      <c r="F28" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>17</v>
       </c>
       <c r="H28" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="I28" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J28" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="I28" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="J28" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="K28" s="32"/>
-    </row>
-    <row r="29" spans="1:11" ht="101.25">
+      <c r="K28" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="L28" s="32"/>
+    </row>
+    <row r="29" spans="1:12" ht="72">
       <c r="A29" s="4">
         <v>29</v>
       </c>
-      <c r="B29" s="51"/>
-      <c r="C29" s="51"/>
+      <c r="B29" s="50"/>
+      <c r="C29" s="50"/>
       <c r="D29" s="6" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="F29" s="33" t="s">
-        <v>49</v>
+        <v>58</v>
+      </c>
+      <c r="F29" s="18" t="s">
+        <v>130</v>
       </c>
       <c r="G29" s="33" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="H29" s="33" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="I29" s="33" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="J29" s="33" t="s">
-        <v>116</v>
-      </c>
-      <c r="K29" s="15"/>
-    </row>
-    <row r="30" spans="1:11" ht="61.5" customHeight="1">
+        <v>59</v>
+      </c>
+      <c r="K29" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="L29" s="15"/>
+    </row>
+    <row r="30" spans="1:12" ht="61.5" customHeight="1">
       <c r="A30" s="4">
         <v>30</v>
       </c>
-      <c r="B30" s="51"/>
-      <c r="C30" s="51" t="s">
-        <v>117</v>
+      <c r="B30" s="50"/>
+      <c r="C30" s="50" t="s">
+        <v>132</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="E30" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="F30" s="14"/>
+        <v>133</v>
+      </c>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18" t="s">
+        <v>134</v>
+      </c>
       <c r="G30" s="14"/>
       <c r="H30" s="14"/>
       <c r="I30" s="14"/>
       <c r="J30" s="14"/>
-      <c r="K30" s="15"/>
-    </row>
-    <row r="31" spans="1:11" ht="61.5" customHeight="1">
+      <c r="K30" s="14"/>
+      <c r="L30" s="15"/>
+    </row>
+    <row r="31" spans="1:12" ht="61.5" customHeight="1">
       <c r="A31" s="4">
         <v>31</v>
       </c>
-      <c r="B31" s="51"/>
-      <c r="C31" s="51"/>
+      <c r="B31" s="50"/>
+      <c r="C31" s="50"/>
       <c r="D31" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="E31" s="18" t="s">
-        <v>121</v>
-      </c>
-      <c r="F31" s="33"/>
+        <v>135</v>
+      </c>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18" t="s">
+        <v>136</v>
+      </c>
       <c r="G31" s="33"/>
       <c r="H31" s="33"/>
       <c r="I31" s="33"/>
       <c r="J31" s="33"/>
-      <c r="K31" s="15"/>
-    </row>
-    <row r="32" spans="1:11" ht="61.5" customHeight="1">
+      <c r="K31" s="33"/>
+      <c r="L31" s="15"/>
+    </row>
+    <row r="32" spans="1:12" ht="61.5" customHeight="1">
       <c r="A32" s="4">
         <v>32</v>
       </c>
-      <c r="B32" s="51"/>
-      <c r="C32" s="51"/>
+      <c r="B32" s="50"/>
+      <c r="C32" s="50"/>
       <c r="D32" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="E32" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="F32" s="33"/>
+        <v>137</v>
+      </c>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18" t="s">
+        <v>138</v>
+      </c>
       <c r="G32" s="33"/>
       <c r="H32" s="33"/>
       <c r="I32" s="33"/>
       <c r="J32" s="33"/>
-      <c r="K32" s="32"/>
-    </row>
-    <row r="33" spans="1:11" ht="61.5" customHeight="1">
+      <c r="K32" s="33"/>
+      <c r="L32" s="32"/>
+    </row>
+    <row r="33" spans="1:12" ht="61.5" customHeight="1">
       <c r="A33" s="4">
         <v>33</v>
       </c>
-      <c r="B33" s="51"/>
-      <c r="C33" s="51"/>
+      <c r="B33" s="50"/>
+      <c r="C33" s="50"/>
       <c r="D33" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="E33" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="F33" s="33"/>
+        <v>139</v>
+      </c>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18" t="s">
+        <v>140</v>
+      </c>
       <c r="G33" s="33"/>
       <c r="H33" s="33"/>
       <c r="I33" s="33"/>
       <c r="J33" s="33"/>
-      <c r="K33" s="32"/>
-    </row>
-    <row r="34" spans="1:11" ht="61.5" customHeight="1">
+      <c r="K33" s="33"/>
+      <c r="L33" s="32"/>
+    </row>
+    <row r="34" spans="1:12" ht="61.5" customHeight="1">
       <c r="A34" s="4">
         <v>34</v>
       </c>
-      <c r="B34" s="51"/>
-      <c r="C34" s="51"/>
+      <c r="B34" s="50"/>
+      <c r="C34" s="50"/>
       <c r="D34" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="E34" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="F34" s="33"/>
+        <v>141</v>
+      </c>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18" t="s">
+        <v>142</v>
+      </c>
       <c r="G34" s="33"/>
       <c r="H34" s="33"/>
       <c r="I34" s="33"/>
       <c r="J34" s="33"/>
-      <c r="K34" s="15"/>
-    </row>
-    <row r="35" spans="1:11" ht="61.5" customHeight="1">
+      <c r="K34" s="33"/>
+      <c r="L34" s="15"/>
+    </row>
+    <row r="35" spans="1:12" ht="61.5" customHeight="1">
       <c r="A35" s="4">
         <v>35</v>
       </c>
-      <c r="B35" s="51"/>
+      <c r="B35" s="50"/>
       <c r="C35" s="6" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="E35" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="F35" s="33"/>
+        <v>123</v>
+      </c>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18" t="s">
+        <v>143</v>
+      </c>
       <c r="G35" s="33"/>
       <c r="H35" s="33"/>
       <c r="I35" s="33"/>
       <c r="J35" s="33"/>
-      <c r="K35" s="15"/>
-    </row>
-    <row r="36" spans="1:11" ht="39.75" customHeight="1">
+      <c r="K35" s="33"/>
+      <c r="L35" s="15"/>
+    </row>
+    <row r="36" spans="1:12" ht="39.75" customHeight="1">
       <c r="A36" s="4">
         <v>36</v>
       </c>
-      <c r="B36" s="51" t="s">
-        <v>52</v>
-      </c>
-      <c r="C36" s="51" t="s">
-        <v>129</v>
+      <c r="B36" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="C36" s="50" t="s">
+        <v>144</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="E36" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="F36" s="33"/>
+        <v>145</v>
+      </c>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18" t="s">
+        <v>146</v>
+      </c>
       <c r="G36" s="33"/>
       <c r="H36" s="33"/>
       <c r="I36" s="33"/>
       <c r="J36" s="33"/>
-      <c r="K36" s="15"/>
-    </row>
-    <row r="37" spans="1:11" ht="39.75" customHeight="1">
+      <c r="K36" s="33"/>
+      <c r="L36" s="15"/>
+    </row>
+    <row r="37" spans="1:12" ht="39.75" customHeight="1">
       <c r="A37" s="4">
         <v>37</v>
       </c>
-      <c r="B37" s="51"/>
-      <c r="C37" s="51"/>
+      <c r="B37" s="50"/>
+      <c r="C37" s="50"/>
       <c r="D37" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="E37" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="F37" s="33"/>
+        <v>147</v>
+      </c>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18" t="s">
+        <v>148</v>
+      </c>
       <c r="G37" s="33"/>
       <c r="H37" s="33"/>
       <c r="I37" s="33"/>
       <c r="J37" s="33"/>
-      <c r="K37" s="32"/>
-    </row>
-    <row r="38" spans="1:11" ht="39.75" customHeight="1">
+      <c r="K37" s="33"/>
+      <c r="L37" s="32"/>
+    </row>
+    <row r="38" spans="1:12" ht="39.75" customHeight="1">
       <c r="A38" s="4">
         <v>38</v>
       </c>
-      <c r="B38" s="51"/>
-      <c r="C38" s="51" t="s">
-        <v>134</v>
+      <c r="B38" s="50"/>
+      <c r="C38" s="50" t="s">
+        <v>149</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="E38" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="F38" s="33"/>
+        <v>150</v>
+      </c>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18" t="s">
+        <v>151</v>
+      </c>
       <c r="G38" s="33"/>
       <c r="H38" s="33"/>
       <c r="I38" s="33"/>
       <c r="J38" s="33"/>
-      <c r="K38" s="32"/>
-    </row>
-    <row r="39" spans="1:11" ht="39.75" customHeight="1">
+      <c r="K38" s="33"/>
+      <c r="L38" s="32"/>
+    </row>
+    <row r="39" spans="1:12" ht="39.75" customHeight="1">
       <c r="A39" s="4">
         <v>40</v>
       </c>
-      <c r="B39" s="51"/>
-      <c r="C39" s="51"/>
+      <c r="B39" s="50"/>
+      <c r="C39" s="50"/>
       <c r="D39" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="E39" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="F39" s="14"/>
+        <v>152</v>
+      </c>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18" t="s">
+        <v>153</v>
+      </c>
       <c r="G39" s="14"/>
       <c r="H39" s="14"/>
       <c r="I39" s="14"/>
       <c r="J39" s="14"/>
-      <c r="K39" s="15"/>
-    </row>
-    <row r="40" spans="1:11" ht="39.75" customHeight="1">
+      <c r="K39" s="14"/>
+      <c r="L39" s="15"/>
+    </row>
+    <row r="40" spans="1:12" ht="39.75" customHeight="1">
       <c r="A40" s="4">
         <v>42</v>
       </c>
-      <c r="B40" s="51"/>
-      <c r="C40" s="51"/>
+      <c r="B40" s="50"/>
+      <c r="C40" s="50"/>
       <c r="D40" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="E40" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="F40" s="14"/>
+        <v>154</v>
+      </c>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18" t="s">
+        <v>155</v>
+      </c>
       <c r="G40" s="14"/>
       <c r="H40" s="14"/>
       <c r="I40" s="14"/>
       <c r="J40" s="14"/>
-      <c r="K40" s="15"/>
-    </row>
-    <row r="41" spans="1:11" ht="76.5">
+      <c r="K40" s="14"/>
+      <c r="L40" s="15"/>
+    </row>
+    <row r="41" spans="1:12" ht="76.5">
       <c r="A41" s="4">
         <v>44</v>
       </c>
-      <c r="B41" s="51"/>
-      <c r="C41" s="51"/>
+      <c r="B41" s="50"/>
+      <c r="C41" s="50"/>
       <c r="D41" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="E41" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="F41" s="14"/>
+        <v>156</v>
+      </c>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18" t="s">
+        <v>157</v>
+      </c>
       <c r="G41" s="14"/>
       <c r="H41" s="14"/>
       <c r="I41" s="14"/>
       <c r="J41" s="14"/>
-      <c r="K41" s="15"/>
-    </row>
-    <row r="42" spans="1:11" ht="54.75" customHeight="1">
+      <c r="K41" s="14"/>
+      <c r="L41" s="15"/>
+    </row>
+    <row r="42" spans="1:12" ht="54.75" customHeight="1">
       <c r="A42" s="4">
         <v>46</v>
       </c>
-      <c r="B42" s="51"/>
-      <c r="C42" s="51" t="s">
-        <v>143</v>
+      <c r="B42" s="50"/>
+      <c r="C42" s="50" t="s">
+        <v>158</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="E42" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="F42" s="14"/>
+        <v>159</v>
+      </c>
+      <c r="E42" s="18"/>
+      <c r="F42" s="18" t="s">
+        <v>160</v>
+      </c>
       <c r="G42" s="14"/>
       <c r="H42" s="14"/>
       <c r="I42" s="14"/>
       <c r="J42" s="14"/>
-      <c r="K42" s="15"/>
-    </row>
-    <row r="43" spans="1:11" ht="54.75" customHeight="1">
+      <c r="K42" s="14"/>
+      <c r="L42" s="15"/>
+    </row>
+    <row r="43" spans="1:12" ht="54.75" customHeight="1">
       <c r="A43" s="4">
         <v>47</v>
       </c>
-      <c r="B43" s="51"/>
-      <c r="C43" s="51"/>
+      <c r="B43" s="50"/>
+      <c r="C43" s="50"/>
       <c r="D43" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="E43" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="F43" s="14"/>
+        <v>161</v>
+      </c>
+      <c r="E43" s="18"/>
+      <c r="F43" s="18" t="s">
+        <v>162</v>
+      </c>
       <c r="G43" s="14"/>
       <c r="H43" s="14"/>
       <c r="I43" s="14"/>
       <c r="J43" s="14"/>
-      <c r="K43" s="15"/>
-    </row>
-    <row r="44" spans="1:11" ht="54.75" customHeight="1">
+      <c r="K43" s="14"/>
+      <c r="L43" s="15"/>
+    </row>
+    <row r="44" spans="1:12" ht="54.75" customHeight="1">
       <c r="A44" s="4">
         <v>48</v>
       </c>
-      <c r="B44" s="51"/>
-      <c r="C44" s="51"/>
+      <c r="B44" s="50"/>
+      <c r="C44" s="50"/>
       <c r="D44" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="E44" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="F44" s="14"/>
+        <v>163</v>
+      </c>
+      <c r="E44" s="18"/>
+      <c r="F44" s="18" t="s">
+        <v>164</v>
+      </c>
       <c r="G44" s="14"/>
       <c r="H44" s="14"/>
       <c r="I44" s="14"/>
       <c r="J44" s="14"/>
-      <c r="K44" s="15"/>
-    </row>
-    <row r="45" spans="1:11" ht="54.75" customHeight="1">
+      <c r="K44" s="14"/>
+      <c r="L44" s="15"/>
+    </row>
+    <row r="45" spans="1:12" ht="54.75" customHeight="1">
       <c r="A45" s="4">
         <v>49</v>
       </c>
-      <c r="B45" s="51"/>
-      <c r="C45" s="51"/>
+      <c r="B45" s="50"/>
+      <c r="C45" s="50"/>
       <c r="D45" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="E45" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="F45" s="14"/>
+        <v>165</v>
+      </c>
+      <c r="E45" s="18"/>
+      <c r="F45" s="18" t="s">
+        <v>166</v>
+      </c>
       <c r="G45" s="14"/>
       <c r="H45" s="14"/>
       <c r="I45" s="14"/>
       <c r="J45" s="14"/>
-      <c r="K45" s="15"/>
-    </row>
-    <row r="46" spans="1:11" ht="54.75" customHeight="1">
+      <c r="K45" s="14"/>
+      <c r="L45" s="15"/>
+    </row>
+    <row r="46" spans="1:12" ht="54.75" customHeight="1">
       <c r="A46" s="4">
         <v>50</v>
       </c>
-      <c r="B46" s="51" t="s">
-        <v>152</v>
-      </c>
-      <c r="C46" s="51" t="s">
-        <v>153</v>
+      <c r="B46" s="50" t="s">
+        <v>167</v>
+      </c>
+      <c r="C46" s="50" t="s">
+        <v>168</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="E46" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="F46" s="14"/>
+        <v>126</v>
+      </c>
+      <c r="E46" s="18"/>
+      <c r="F46" s="18" t="s">
+        <v>169</v>
+      </c>
       <c r="G46" s="14"/>
       <c r="H46" s="14"/>
       <c r="I46" s="14"/>
       <c r="J46" s="14"/>
-      <c r="K46" s="15"/>
-    </row>
-    <row r="47" spans="1:11" ht="45.75">
+      <c r="K46" s="14"/>
+      <c r="L46" s="15"/>
+    </row>
+    <row r="47" spans="1:12" ht="45.75">
       <c r="A47" s="4">
         <v>51</v>
       </c>
-      <c r="B47" s="51"/>
-      <c r="C47" s="51"/>
+      <c r="B47" s="50"/>
+      <c r="C47" s="50"/>
       <c r="D47" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="E47" s="18" t="s">
-        <v>156</v>
-      </c>
-      <c r="F47" s="14"/>
+        <v>170</v>
+      </c>
+      <c r="E47" s="18"/>
+      <c r="F47" s="18" t="s">
+        <v>171</v>
+      </c>
       <c r="G47" s="14"/>
       <c r="H47" s="14"/>
       <c r="I47" s="14"/>
       <c r="J47" s="14"/>
-      <c r="K47" s="15"/>
-    </row>
-    <row r="48" spans="1:11" ht="30.75" customHeight="1">
+      <c r="K47" s="14"/>
+      <c r="L47" s="15"/>
+    </row>
+    <row r="48" spans="1:12" ht="30.75" customHeight="1">
       <c r="A48" s="4">
         <v>54</v>
       </c>
-      <c r="B48" s="51"/>
-      <c r="C48" s="51" t="s">
-        <v>157</v>
+      <c r="B48" s="50"/>
+      <c r="C48" s="50" t="s">
+        <v>172</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="E48" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="F48" s="14"/>
+        <v>173</v>
+      </c>
+      <c r="E48" s="18"/>
+      <c r="F48" s="18" t="s">
+        <v>174</v>
+      </c>
       <c r="G48" s="14"/>
       <c r="H48" s="14"/>
       <c r="I48" s="14"/>
       <c r="J48" s="14"/>
-      <c r="K48" s="15"/>
-    </row>
-    <row r="49" spans="1:11" ht="72">
+      <c r="K48" s="14"/>
+      <c r="L48" s="15"/>
+    </row>
+    <row r="49" spans="1:12" ht="43.5">
       <c r="A49" s="4">
         <v>55</v>
       </c>
-      <c r="B49" s="51"/>
-      <c r="C49" s="51"/>
+      <c r="B49" s="50"/>
+      <c r="C49" s="50"/>
       <c r="D49" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="E49" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="F49" s="33" t="s">
-        <v>162</v>
+        <v>175</v>
+      </c>
+      <c r="E49" s="18"/>
+      <c r="F49" s="18" t="s">
+        <v>176</v>
       </c>
       <c r="G49" s="33" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="H49" s="33" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="I49" s="33" t="s">
-        <v>162</v>
-      </c>
-      <c r="J49" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="K49" s="15"/>
-    </row>
-    <row r="50" spans="1:11" ht="43.5">
+        <v>177</v>
+      </c>
+      <c r="J49" s="33" t="s">
+        <v>177</v>
+      </c>
+      <c r="K49" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="L49" s="15"/>
+    </row>
+    <row r="50" spans="1:12" ht="28.5">
       <c r="A50" s="4">
         <v>56</v>
       </c>
-      <c r="B50" s="51"/>
-      <c r="C50" s="51"/>
+      <c r="B50" s="50"/>
+      <c r="C50" s="50"/>
       <c r="D50" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="E50" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="F50" s="34" t="s">
-        <v>166</v>
+        <v>179</v>
+      </c>
+      <c r="E50" s="18"/>
+      <c r="F50" s="18" t="s">
+        <v>180</v>
       </c>
       <c r="G50" s="34" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="H50" s="34" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="I50" s="34" t="s">
-        <v>166</v>
-      </c>
-      <c r="J50" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="K50" s="15"/>
-    </row>
-    <row r="51" spans="1:11">
+        <v>181</v>
+      </c>
+      <c r="J50" s="34" t="s">
+        <v>181</v>
+      </c>
+      <c r="K50" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="L50" s="15"/>
+    </row>
+    <row r="51" spans="1:12">
       <c r="A51" s="4">
         <v>57</v>
       </c>
-      <c r="B51" s="51"/>
-      <c r="C51" s="51"/>
+      <c r="B51" s="50"/>
+      <c r="C51" s="50"/>
       <c r="D51" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="E51" s="18" t="s">
-        <v>168</v>
-      </c>
-      <c r="F51" s="33" t="s">
-        <v>169</v>
+        <v>182</v>
+      </c>
+      <c r="E51" s="18"/>
+      <c r="F51" s="18" t="s">
+        <v>183</v>
       </c>
       <c r="G51" s="33" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="H51" s="33" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="I51" s="33" t="s">
-        <v>169</v>
-      </c>
-      <c r="J51" s="33"/>
-      <c r="K51" s="15"/>
-    </row>
-    <row r="52" spans="1:11">
+        <v>184</v>
+      </c>
+      <c r="J51" s="33" t="s">
+        <v>184</v>
+      </c>
+      <c r="K51" s="33"/>
+      <c r="L51" s="15"/>
+    </row>
+    <row r="52" spans="1:12">
       <c r="A52" s="4">
         <v>58</v>
       </c>
-      <c r="B52" s="51"/>
-      <c r="C52" s="51"/>
+      <c r="B52" s="50"/>
+      <c r="C52" s="50"/>
       <c r="D52" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="E52" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="F52" s="14"/>
+        <v>185</v>
+      </c>
+      <c r="E52" s="18"/>
+      <c r="F52" s="18" t="s">
+        <v>186</v>
+      </c>
       <c r="G52" s="14"/>
       <c r="H52" s="14"/>
       <c r="I52" s="14"/>
       <c r="J52" s="14"/>
-      <c r="K52" s="32"/>
-    </row>
-    <row r="53" spans="1:11">
+      <c r="K52" s="14"/>
+      <c r="L52" s="32"/>
+    </row>
+    <row r="53" spans="1:12">
       <c r="A53" s="4">
         <v>59</v>
       </c>
-      <c r="B53" s="51"/>
-      <c r="C53" s="51"/>
+      <c r="B53" s="50"/>
+      <c r="C53" s="50"/>
       <c r="D53" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="E53" s="18" t="s">
-        <v>173</v>
-      </c>
-      <c r="F53" s="36" t="s">
-        <v>174</v>
+        <v>187</v>
+      </c>
+      <c r="E53" s="18"/>
+      <c r="F53" s="18" t="s">
+        <v>188</v>
       </c>
       <c r="G53" s="36" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="H53" s="36" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="I53" s="36" t="s">
-        <v>174</v>
-      </c>
-      <c r="J53" s="14"/>
-      <c r="K53" s="15"/>
-    </row>
-    <row r="54" spans="1:11" ht="72">
+        <v>189</v>
+      </c>
+      <c r="J53" s="36" t="s">
+        <v>189</v>
+      </c>
+      <c r="K53" s="14"/>
+      <c r="L53" s="15"/>
+    </row>
+    <row r="54" spans="1:12" ht="43.5">
       <c r="A54" s="4">
         <v>60</v>
       </c>
-      <c r="B54" s="51"/>
-      <c r="C54" s="51" t="s">
-        <v>175</v>
+      <c r="B54" s="50"/>
+      <c r="C54" s="50" t="s">
+        <v>190</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="E54" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="F54" s="34" t="s">
-        <v>178</v>
+        <v>191</v>
+      </c>
+      <c r="E54" s="18"/>
+      <c r="F54" s="18" t="s">
+        <v>192</v>
       </c>
       <c r="G54" s="34" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="H54" s="34" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="I54" s="34" t="s">
-        <v>178</v>
-      </c>
-      <c r="J54" s="14"/>
-      <c r="K54" s="15"/>
-    </row>
-    <row r="55" spans="1:11">
+        <v>194</v>
+      </c>
+      <c r="J54" s="34" t="s">
+        <v>193</v>
+      </c>
+      <c r="K54" s="14"/>
+      <c r="L54" s="15"/>
+    </row>
+    <row r="55" spans="1:12">
       <c r="A55" s="4">
         <v>61</v>
       </c>
-      <c r="B55" s="51"/>
-      <c r="C55" s="51"/>
+      <c r="B55" s="50"/>
+      <c r="C55" s="50"/>
       <c r="D55" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="E55" s="20" t="s">
-        <v>181</v>
-      </c>
-      <c r="F55" s="13"/>
-      <c r="G55" s="14"/>
+        <v>195</v>
+      </c>
+      <c r="E55" s="18"/>
+      <c r="F55" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="G55" s="13"/>
       <c r="H55" s="14"/>
-      <c r="I55" s="13"/>
-      <c r="J55" s="14"/>
-      <c r="K55" s="15"/>
-    </row>
-    <row r="56" spans="1:11">
+      <c r="I55" s="14"/>
+      <c r="J55" s="13"/>
+      <c r="K55" s="14"/>
+      <c r="L55" s="15"/>
+    </row>
+    <row r="56" spans="1:12">
       <c r="A56" s="4">
         <v>62</v>
       </c>
-      <c r="B56" s="51"/>
-      <c r="C56" s="51"/>
+      <c r="B56" s="50"/>
+      <c r="C56" s="50"/>
       <c r="D56" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="E56" s="18" t="s">
-        <v>183</v>
-      </c>
-      <c r="F56" s="14"/>
+        <v>197</v>
+      </c>
+      <c r="E56" s="18"/>
+      <c r="F56" s="18" t="s">
+        <v>198</v>
+      </c>
       <c r="G56" s="14"/>
       <c r="H56" s="14"/>
       <c r="I56" s="14"/>
       <c r="J56" s="14"/>
-      <c r="K56" s="15"/>
-    </row>
-    <row r="57" spans="1:11">
+      <c r="K56" s="14"/>
+      <c r="L56" s="15"/>
+    </row>
+    <row r="57" spans="1:12">
       <c r="A57" s="4">
         <v>63</v>
       </c>
-      <c r="B57" s="51"/>
-      <c r="C57" s="51"/>
+      <c r="B57" s="50"/>
+      <c r="C57" s="50"/>
       <c r="D57" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="E57" s="18" t="s">
-        <v>185</v>
-      </c>
-      <c r="F57" s="14"/>
+        <v>199</v>
+      </c>
+      <c r="E57" s="18"/>
+      <c r="F57" s="18" t="s">
+        <v>200</v>
+      </c>
       <c r="G57" s="14"/>
       <c r="H57" s="14"/>
       <c r="I57" s="14"/>
       <c r="J57" s="14"/>
-      <c r="K57" s="15"/>
-    </row>
-    <row r="58" spans="1:11" ht="28.5">
+      <c r="K57" s="14"/>
+      <c r="L57" s="15"/>
+    </row>
+    <row r="58" spans="1:12" ht="28.5">
       <c r="A58" s="4">
         <v>64</v>
       </c>
-      <c r="B58" s="51"/>
-      <c r="C58" s="51"/>
+      <c r="B58" s="50"/>
+      <c r="C58" s="50"/>
       <c r="D58" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="E58" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="F58" s="16" t="s">
-        <v>40</v>
+        <v>201</v>
+      </c>
+      <c r="E58" s="18"/>
+      <c r="F58" s="18" t="s">
+        <v>202</v>
       </c>
       <c r="G58" s="16" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="H58" s="16" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="I58" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="J58" s="33" t="s">
-        <v>41</v>
-      </c>
-      <c r="K58" s="15"/>
-    </row>
-    <row r="59" spans="1:11" ht="45.75">
+        <v>48</v>
+      </c>
+      <c r="J58" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="K58" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="L58" s="15"/>
+    </row>
+    <row r="59" spans="1:12" ht="45.75">
       <c r="A59" s="4">
         <v>65</v>
       </c>
-      <c r="B59" s="51"/>
-      <c r="C59" s="51" t="s">
-        <v>188</v>
+      <c r="B59" s="50"/>
+      <c r="C59" s="50" t="s">
+        <v>203</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="E59" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="F59" s="33" t="s">
-        <v>191</v>
+        <v>204</v>
+      </c>
+      <c r="E59" s="18"/>
+      <c r="F59" s="18" t="s">
+        <v>205</v>
       </c>
       <c r="G59" s="33" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="H59" s="33" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="I59" s="33" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="J59" s="33" t="s">
-        <v>192</v>
-      </c>
-      <c r="K59" s="15"/>
-    </row>
-    <row r="60" spans="1:11" ht="28.5">
+        <v>206</v>
+      </c>
+      <c r="K59" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="L59" s="15"/>
+    </row>
+    <row r="60" spans="1:12">
       <c r="A60" s="4">
         <v>66</v>
       </c>
-      <c r="B60" s="51"/>
-      <c r="C60" s="51"/>
+      <c r="B60" s="50"/>
+      <c r="C60" s="50"/>
       <c r="D60" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="E60" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="F60" s="33" t="s">
-        <v>194</v>
+        <v>208</v>
+      </c>
+      <c r="E60" s="18"/>
+      <c r="F60" s="18" t="s">
+        <v>101</v>
       </c>
       <c r="G60" s="33" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="H60" s="33" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="I60" s="33" t="s">
-        <v>194</v>
-      </c>
-      <c r="J60" s="33"/>
-      <c r="K60" s="32"/>
-    </row>
-    <row r="61" spans="1:11">
+        <v>209</v>
+      </c>
+      <c r="J60" s="33" t="s">
+        <v>209</v>
+      </c>
+      <c r="K60" s="33"/>
+      <c r="L60" s="32"/>
+    </row>
+    <row r="61" spans="1:12">
       <c r="A61" s="4">
         <v>67</v>
       </c>
-      <c r="B61" s="51"/>
-      <c r="C61" s="51"/>
+      <c r="B61" s="50"/>
+      <c r="C61" s="50"/>
       <c r="D61" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="E61" s="18" t="s">
-        <v>196</v>
-      </c>
-      <c r="F61" s="33"/>
+        <v>210</v>
+      </c>
+      <c r="E61" s="18"/>
+      <c r="F61" s="18" t="s">
+        <v>211</v>
+      </c>
       <c r="G61" s="33"/>
       <c r="H61" s="33"/>
       <c r="I61" s="33"/>
       <c r="J61" s="33"/>
-      <c r="K61" s="15"/>
-    </row>
-    <row r="62" spans="1:11" ht="28.5">
+      <c r="K61" s="33"/>
+      <c r="L61" s="15"/>
+    </row>
+    <row r="62" spans="1:12">
       <c r="A62" s="4">
         <v>68</v>
       </c>
-      <c r="B62" s="51"/>
-      <c r="C62" s="51"/>
+      <c r="B62" s="50"/>
+      <c r="C62" s="50"/>
       <c r="D62" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="E62" s="18" t="s">
-        <v>198</v>
-      </c>
-      <c r="F62" s="33" t="s">
-        <v>199</v>
+        <v>212</v>
+      </c>
+      <c r="E62" s="18"/>
+      <c r="F62" s="18" t="s">
+        <v>213</v>
       </c>
       <c r="G62" s="33" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="H62" s="33" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="I62" s="33" t="s">
-        <v>199</v>
-      </c>
-      <c r="J62" s="14"/>
-      <c r="K62" s="15"/>
-    </row>
-    <row r="63" spans="1:11">
+        <v>215</v>
+      </c>
+      <c r="J62" s="33" t="s">
+        <v>214</v>
+      </c>
+      <c r="K62" s="14"/>
+      <c r="L62" s="15"/>
+    </row>
+    <row r="63" spans="1:12">
       <c r="A63" s="4">
         <v>69</v>
       </c>
-      <c r="B63" s="51"/>
-      <c r="C63" s="51"/>
+      <c r="B63" s="50"/>
+      <c r="C63" s="50"/>
       <c r="D63" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="E63" s="18" t="s">
-        <v>202</v>
-      </c>
-      <c r="F63" s="33"/>
+        <v>216</v>
+      </c>
+      <c r="E63" s="18"/>
+      <c r="F63" s="18" t="s">
+        <v>217</v>
+      </c>
       <c r="G63" s="33"/>
       <c r="H63" s="33"/>
       <c r="I63" s="33"/>
       <c r="J63" s="33"/>
-      <c r="K63" s="32"/>
-    </row>
-    <row r="64" spans="1:11" ht="45.75">
+      <c r="K63" s="33"/>
+      <c r="L63" s="32"/>
+    </row>
+    <row r="64" spans="1:12" ht="45.75">
       <c r="A64" s="4">
         <v>70</v>
       </c>
-      <c r="B64" s="51"/>
+      <c r="B64" s="50"/>
       <c r="C64" s="6" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="E64" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="F64" s="14"/>
+        <v>123</v>
+      </c>
+      <c r="E64" s="18"/>
+      <c r="F64" s="18" t="s">
+        <v>219</v>
+      </c>
       <c r="G64" s="14"/>
       <c r="H64" s="14"/>
       <c r="I64" s="14"/>
       <c r="J64" s="14"/>
-      <c r="K64" s="15"/>
-    </row>
-    <row r="65" spans="1:11" ht="54" customHeight="1">
+      <c r="K64" s="14"/>
+      <c r="L64" s="15"/>
+    </row>
+    <row r="65" spans="1:12" ht="54" customHeight="1">
       <c r="A65" s="4">
         <v>71</v>
       </c>
-      <c r="B65" s="51" t="s">
-        <v>205</v>
-      </c>
-      <c r="C65" s="51" t="s">
-        <v>206</v>
+      <c r="B65" s="50" t="s">
+        <v>220</v>
+      </c>
+      <c r="C65" s="50" t="s">
+        <v>221</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="E65" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="F65" s="33"/>
+        <v>222</v>
+      </c>
+      <c r="E65" s="18"/>
+      <c r="F65" s="18" t="s">
+        <v>223</v>
+      </c>
       <c r="G65" s="33"/>
       <c r="H65" s="33"/>
       <c r="I65" s="33"/>
       <c r="J65" s="33"/>
-      <c r="K65" s="15"/>
-    </row>
-    <row r="66" spans="1:11" ht="54" customHeight="1">
+      <c r="K65" s="33"/>
+      <c r="L65" s="15"/>
+    </row>
+    <row r="66" spans="1:12" ht="54" customHeight="1">
       <c r="A66" s="4">
         <v>72</v>
       </c>
-      <c r="B66" s="51"/>
-      <c r="C66" s="51"/>
+      <c r="B66" s="50"/>
+      <c r="C66" s="50"/>
       <c r="D66" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="E66" s="18" t="s">
-        <v>210</v>
-      </c>
-      <c r="F66" s="33"/>
+        <v>224</v>
+      </c>
+      <c r="E66" s="18"/>
+      <c r="F66" s="18" t="s">
+        <v>225</v>
+      </c>
       <c r="G66" s="33"/>
       <c r="H66" s="33"/>
       <c r="I66" s="33"/>
       <c r="J66" s="33"/>
-      <c r="K66" s="15"/>
-    </row>
-    <row r="67" spans="1:11" ht="54" customHeight="1">
+      <c r="K66" s="33"/>
+      <c r="L66" s="15"/>
+    </row>
+    <row r="67" spans="1:12" ht="54" customHeight="1">
       <c r="A67" s="4">
         <v>73</v>
       </c>
-      <c r="B67" s="51"/>
-      <c r="C67" s="51"/>
+      <c r="B67" s="50"/>
+      <c r="C67" s="50"/>
       <c r="D67" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="E67" s="18" t="s">
-        <v>212</v>
-      </c>
-      <c r="F67" s="33"/>
+        <v>226</v>
+      </c>
+      <c r="E67" s="18"/>
+      <c r="F67" s="18" t="s">
+        <v>227</v>
+      </c>
       <c r="G67" s="33"/>
       <c r="H67" s="33"/>
       <c r="I67" s="33"/>
       <c r="J67" s="33"/>
-      <c r="K67" s="15"/>
-    </row>
-    <row r="68" spans="1:11" ht="54" customHeight="1">
+      <c r="K67" s="33"/>
+      <c r="L67" s="15"/>
+    </row>
+    <row r="68" spans="1:12" ht="54" customHeight="1">
       <c r="A68" s="4">
         <v>74</v>
       </c>
-      <c r="B68" s="51"/>
-      <c r="C68" s="51" t="s">
-        <v>213</v>
+      <c r="B68" s="50"/>
+      <c r="C68" s="50" t="s">
+        <v>228</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="E68" s="18" t="s">
-        <v>215</v>
-      </c>
-      <c r="F68" s="33"/>
+        <v>229</v>
+      </c>
+      <c r="E68" s="18"/>
+      <c r="F68" s="18" t="s">
+        <v>230</v>
+      </c>
       <c r="G68" s="33"/>
       <c r="H68" s="33"/>
       <c r="I68" s="33"/>
       <c r="J68" s="33"/>
-      <c r="K68" s="15"/>
-    </row>
-    <row r="69" spans="1:11" ht="54" customHeight="1">
+      <c r="K68" s="33"/>
+      <c r="L68" s="15"/>
+    </row>
+    <row r="69" spans="1:12" ht="54" customHeight="1">
       <c r="A69" s="4">
         <v>75</v>
       </c>
-      <c r="B69" s="51"/>
-      <c r="C69" s="51"/>
+      <c r="B69" s="50"/>
+      <c r="C69" s="50"/>
       <c r="D69" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="E69" s="18" t="s">
-        <v>217</v>
-      </c>
-      <c r="F69" s="14"/>
+        <v>231</v>
+      </c>
+      <c r="E69" s="18"/>
+      <c r="F69" s="18" t="s">
+        <v>232</v>
+      </c>
       <c r="G69" s="14"/>
       <c r="H69" s="14"/>
       <c r="I69" s="14"/>
       <c r="J69" s="14"/>
-      <c r="K69" s="15"/>
-    </row>
-    <row r="70" spans="1:11" ht="54" customHeight="1">
+      <c r="K69" s="14"/>
+      <c r="L69" s="15"/>
+    </row>
+    <row r="70" spans="1:12" ht="54" customHeight="1">
       <c r="A70" s="4">
         <v>76</v>
       </c>
-      <c r="B70" s="51"/>
-      <c r="C70" s="51"/>
+      <c r="B70" s="50"/>
+      <c r="C70" s="50"/>
       <c r="D70" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="E70" s="18" t="s">
-        <v>219</v>
-      </c>
-      <c r="F70" s="14"/>
+        <v>233</v>
+      </c>
+      <c r="E70" s="18"/>
+      <c r="F70" s="18" t="s">
+        <v>234</v>
+      </c>
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="14"/>
       <c r="J70" s="14"/>
-      <c r="K70" s="15"/>
-    </row>
-    <row r="71" spans="1:11" ht="54" customHeight="1">
+      <c r="K70" s="14"/>
+      <c r="L70" s="15"/>
+    </row>
+    <row r="71" spans="1:12" ht="54" customHeight="1">
       <c r="A71" s="4">
         <v>77</v>
       </c>
-      <c r="B71" s="51"/>
-      <c r="C71" s="51" t="s">
-        <v>220</v>
+      <c r="B71" s="50"/>
+      <c r="C71" s="50" t="s">
+        <v>235</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="E71" s="18" t="s">
-        <v>222</v>
-      </c>
-      <c r="F71" s="14"/>
+        <v>236</v>
+      </c>
+      <c r="E71" s="18"/>
+      <c r="F71" s="18" t="s">
+        <v>237</v>
+      </c>
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="14"/>
       <c r="J71" s="14"/>
-      <c r="K71" s="15"/>
-    </row>
-    <row r="72" spans="1:11" ht="54" customHeight="1">
+      <c r="K71" s="14"/>
+      <c r="L71" s="15"/>
+    </row>
+    <row r="72" spans="1:12" ht="54" customHeight="1">
       <c r="A72" s="4">
         <v>78</v>
       </c>
-      <c r="B72" s="51"/>
-      <c r="C72" s="51"/>
+      <c r="B72" s="50"/>
+      <c r="C72" s="50"/>
       <c r="D72" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="E72" s="18" t="s">
-        <v>224</v>
-      </c>
-      <c r="F72" s="14"/>
+        <v>238</v>
+      </c>
+      <c r="E72" s="18"/>
+      <c r="F72" s="18" t="s">
+        <v>239</v>
+      </c>
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="14"/>
       <c r="J72" s="14"/>
-      <c r="K72" s="15"/>
-    </row>
-    <row r="73" spans="1:11" ht="54" customHeight="1">
+      <c r="K72" s="14"/>
+      <c r="L72" s="15"/>
+    </row>
+    <row r="73" spans="1:12" ht="54" customHeight="1">
       <c r="A73" s="4">
         <v>79</v>
       </c>
-      <c r="B73" s="51"/>
-      <c r="C73" s="51" t="s">
-        <v>225</v>
+      <c r="B73" s="50"/>
+      <c r="C73" s="50" t="s">
+        <v>240</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="E73" s="18" t="s">
-        <v>227</v>
-      </c>
-      <c r="F73" s="14"/>
+        <v>241</v>
+      </c>
+      <c r="E73" s="18"/>
+      <c r="F73" s="18" t="s">
+        <v>242</v>
+      </c>
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="14"/>
       <c r="J73" s="14"/>
-      <c r="K73" s="15"/>
-    </row>
-    <row r="74" spans="1:11" ht="54" customHeight="1">
+      <c r="K73" s="14"/>
+      <c r="L73" s="15"/>
+    </row>
+    <row r="74" spans="1:12" ht="54" customHeight="1">
       <c r="A74" s="4">
         <v>80</v>
       </c>
-      <c r="B74" s="51"/>
-      <c r="C74" s="51"/>
+      <c r="B74" s="50"/>
+      <c r="C74" s="50"/>
       <c r="D74" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="E74" s="21" t="s">
-        <v>229</v>
-      </c>
-      <c r="F74" s="14"/>
+        <v>243</v>
+      </c>
+      <c r="E74" s="18"/>
+      <c r="F74" s="21" t="s">
+        <v>244</v>
+      </c>
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="14"/>
       <c r="J74" s="14"/>
-      <c r="K74" s="15"/>
-    </row>
-    <row r="75" spans="1:11" ht="71.25" customHeight="1">
+      <c r="K74" s="14"/>
+      <c r="L74" s="15"/>
+    </row>
+    <row r="75" spans="1:12" ht="71.25" customHeight="1">
       <c r="A75" s="4">
         <v>81</v>
       </c>
-      <c r="B75" s="51" t="s">
-        <v>55</v>
-      </c>
-      <c r="C75" s="51" t="s">
-        <v>230</v>
+      <c r="B75" s="50" t="s">
+        <v>65</v>
+      </c>
+      <c r="C75" s="50" t="s">
+        <v>245</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="E75" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="F75" s="14"/>
+        <v>246</v>
+      </c>
+      <c r="E75" s="18"/>
+      <c r="F75" s="18" t="s">
+        <v>247</v>
+      </c>
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="14"/>
       <c r="J75" s="14"/>
-      <c r="K75" s="15"/>
-    </row>
-    <row r="76" spans="1:11" ht="94.5" customHeight="1">
+      <c r="K75" s="14"/>
+      <c r="L75" s="15"/>
+    </row>
+    <row r="76" spans="1:12" ht="94.5" customHeight="1">
       <c r="A76" s="4">
         <v>82</v>
       </c>
-      <c r="B76" s="51"/>
-      <c r="C76" s="51"/>
+      <c r="B76" s="50"/>
+      <c r="C76" s="50"/>
       <c r="D76" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="E76" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="F76" s="14"/>
+        <v>248</v>
+      </c>
+      <c r="E76" s="18"/>
+      <c r="F76" s="18" t="s">
+        <v>249</v>
+      </c>
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="14"/>
       <c r="J76" s="14"/>
-      <c r="K76" s="15"/>
-    </row>
-    <row r="77" spans="1:11" ht="71.25" customHeight="1">
+      <c r="K76" s="14"/>
+      <c r="L76" s="15"/>
+    </row>
+    <row r="77" spans="1:12" ht="71.25" customHeight="1">
       <c r="A77" s="4">
         <v>83</v>
       </c>
-      <c r="B77" s="51"/>
-      <c r="C77" s="51"/>
+      <c r="B77" s="50"/>
+      <c r="C77" s="50"/>
       <c r="D77" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="E77" s="18" t="s">
-        <v>236</v>
-      </c>
-      <c r="F77" s="14"/>
+        <v>250</v>
+      </c>
+      <c r="E77" s="18"/>
+      <c r="F77" s="18" t="s">
+        <v>251</v>
+      </c>
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="14"/>
       <c r="J77" s="14"/>
-      <c r="K77" s="15"/>
-    </row>
-    <row r="78" spans="1:11" ht="121.5">
+      <c r="K77" s="14"/>
+      <c r="L77" s="15"/>
+    </row>
+    <row r="78" spans="1:12" ht="121.5">
       <c r="A78" s="4">
         <v>84</v>
       </c>
-      <c r="B78" s="51"/>
-      <c r="C78" s="51" t="s">
-        <v>237</v>
+      <c r="B78" s="50"/>
+      <c r="C78" s="50" t="s">
+        <v>252</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="E78" s="21" t="s">
-        <v>239</v>
-      </c>
-      <c r="F78" s="13" t="s">
-        <v>240</v>
+        <v>253</v>
+      </c>
+      <c r="E78" s="18"/>
+      <c r="F78" s="21" t="s">
+        <v>254</v>
       </c>
       <c r="G78" s="13" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="H78" s="13" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="I78" s="13" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="J78" s="13" t="s">
-        <v>243</v>
-      </c>
-      <c r="K78" s="15"/>
-    </row>
-    <row r="79" spans="1:11" ht="71.25" customHeight="1">
+        <v>255</v>
+      </c>
+      <c r="K78" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="L78" s="15"/>
+    </row>
+    <row r="79" spans="1:12" ht="71.25" customHeight="1">
       <c r="A79" s="4">
         <v>85</v>
       </c>
-      <c r="B79" s="51"/>
-      <c r="C79" s="51"/>
+      <c r="B79" s="50"/>
+      <c r="C79" s="50"/>
       <c r="D79" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="E79" s="18" t="s">
-        <v>245</v>
-      </c>
-      <c r="F79" s="14"/>
+        <v>259</v>
+      </c>
+      <c r="E79" s="18"/>
+      <c r="F79" s="18" t="s">
+        <v>260</v>
+      </c>
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="14"/>
       <c r="J79" s="14"/>
-      <c r="K79" s="32"/>
-    </row>
-    <row r="80" spans="1:11" ht="71.25" customHeight="1">
+      <c r="K79" s="14"/>
+      <c r="L79" s="32"/>
+    </row>
+    <row r="80" spans="1:12" ht="71.25" customHeight="1">
       <c r="A80" s="4">
         <v>86</v>
       </c>
-      <c r="B80" s="51"/>
-      <c r="C80" s="51"/>
+      <c r="B80" s="50"/>
+      <c r="C80" s="50"/>
       <c r="D80" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="E80" s="18" t="s">
-        <v>247</v>
-      </c>
-      <c r="F80" s="14"/>
+        <v>261</v>
+      </c>
+      <c r="E80" s="18"/>
+      <c r="F80" s="18" t="s">
+        <v>262</v>
+      </c>
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="14"/>
       <c r="J80" s="14"/>
-      <c r="K80" s="15"/>
-    </row>
-    <row r="81" spans="1:11" ht="71.25" customHeight="1">
+      <c r="K80" s="14"/>
+      <c r="L80" s="15"/>
+    </row>
+    <row r="81" spans="1:12" ht="71.25" customHeight="1">
       <c r="A81" s="4">
         <v>87</v>
       </c>
-      <c r="B81" s="51"/>
-      <c r="C81" s="51" t="s">
-        <v>248</v>
+      <c r="B81" s="50"/>
+      <c r="C81" s="50" t="s">
+        <v>263</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="E81" s="18" t="s">
-        <v>250</v>
-      </c>
-      <c r="F81" s="33"/>
+        <v>264</v>
+      </c>
+      <c r="E81" s="18"/>
+      <c r="F81" s="18" t="s">
+        <v>265</v>
+      </c>
       <c r="G81" s="33"/>
       <c r="H81" s="33"/>
       <c r="I81" s="33"/>
       <c r="J81" s="33"/>
-      <c r="K81" s="32"/>
-    </row>
-    <row r="82" spans="1:11" ht="71.25" customHeight="1">
+      <c r="K81" s="33"/>
+      <c r="L81" s="32"/>
+    </row>
+    <row r="82" spans="1:12" ht="71.25" customHeight="1">
       <c r="A82" s="4">
         <v>88</v>
       </c>
-      <c r="B82" s="51"/>
-      <c r="C82" s="51"/>
+      <c r="B82" s="50"/>
+      <c r="C82" s="50"/>
       <c r="D82" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="E82" s="18" t="s">
-        <v>252</v>
-      </c>
-      <c r="F82" s="14"/>
+        <v>266</v>
+      </c>
+      <c r="E82" s="18"/>
+      <c r="F82" s="18" t="s">
+        <v>267</v>
+      </c>
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="14"/>
       <c r="J82" s="14"/>
-      <c r="K82" s="15"/>
-    </row>
-    <row r="83" spans="1:11" ht="88.5" customHeight="1">
+      <c r="K82" s="14"/>
+      <c r="L82" s="15"/>
+    </row>
+    <row r="83" spans="1:12" ht="88.5" customHeight="1">
       <c r="A83" s="4">
         <v>89</v>
       </c>
-      <c r="B83" s="51"/>
-      <c r="C83" s="51"/>
+      <c r="B83" s="50"/>
+      <c r="C83" s="50"/>
       <c r="D83" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="E83" s="18" t="s">
-        <v>254</v>
-      </c>
-      <c r="F83" s="14"/>
+        <v>268</v>
+      </c>
+      <c r="E83" s="18"/>
+      <c r="F83" s="18" t="s">
+        <v>269</v>
+      </c>
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="14"/>
       <c r="J83" s="14"/>
-      <c r="K83" s="32"/>
-    </row>
-    <row r="84" spans="1:11" ht="88.5" customHeight="1">
+      <c r="K83" s="14"/>
+      <c r="L83" s="32"/>
+    </row>
+    <row r="84" spans="1:12" ht="88.5" customHeight="1">
       <c r="A84" s="4">
         <v>90</v>
       </c>
-      <c r="B84" s="51"/>
+      <c r="B84" s="50"/>
       <c r="C84" s="6" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="E84" s="18" t="s">
-        <v>257</v>
-      </c>
-      <c r="F84" s="14"/>
+        <v>271</v>
+      </c>
+      <c r="E84" s="18"/>
+      <c r="F84" s="18" t="s">
+        <v>272</v>
+      </c>
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="14"/>
       <c r="J84" s="14"/>
-      <c r="K84" s="15"/>
-    </row>
-    <row r="85" spans="1:11" ht="58.5" customHeight="1">
+      <c r="K84" s="14"/>
+      <c r="L84" s="15"/>
+    </row>
+    <row r="85" spans="1:12" ht="58.5" customHeight="1">
       <c r="A85" s="4">
         <v>91</v>
       </c>
-      <c r="B85" s="51" t="s">
-        <v>258</v>
-      </c>
-      <c r="C85" s="51" t="s">
-        <v>259</v>
+      <c r="B85" s="50" t="s">
+        <v>273</v>
+      </c>
+      <c r="C85" s="50" t="s">
+        <v>274</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="E85" s="18" t="s">
-        <v>261</v>
-      </c>
-      <c r="F85" s="14"/>
+        <v>275</v>
+      </c>
+      <c r="E85" s="18"/>
+      <c r="F85" s="18" t="s">
+        <v>276</v>
+      </c>
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="14"/>
       <c r="J85" s="14"/>
-      <c r="K85" s="15"/>
-    </row>
-    <row r="86" spans="1:11" ht="58.5" customHeight="1">
+      <c r="K85" s="14"/>
+      <c r="L85" s="15"/>
+    </row>
+    <row r="86" spans="1:12" ht="58.5" customHeight="1">
       <c r="A86" s="4">
         <v>92</v>
       </c>
-      <c r="B86" s="51"/>
-      <c r="C86" s="51"/>
+      <c r="B86" s="50"/>
+      <c r="C86" s="50"/>
       <c r="D86" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="E86" s="18" t="s">
-        <v>263</v>
-      </c>
-      <c r="F86" s="14"/>
+        <v>277</v>
+      </c>
+      <c r="E86" s="18"/>
+      <c r="F86" s="18" t="s">
+        <v>278</v>
+      </c>
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="14"/>
       <c r="J86" s="14"/>
-      <c r="K86" s="15"/>
-    </row>
-    <row r="87" spans="1:11" ht="46.5" customHeight="1">
+      <c r="K86" s="14"/>
+      <c r="L86" s="15"/>
+    </row>
+    <row r="87" spans="1:12" ht="46.5" customHeight="1">
       <c r="A87" s="4">
         <v>93</v>
       </c>
-      <c r="B87" s="51"/>
-      <c r="C87" s="51" t="s">
-        <v>264</v>
+      <c r="B87" s="50"/>
+      <c r="C87" s="50" t="s">
+        <v>279</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="E87" s="18" t="s">
-        <v>266</v>
-      </c>
-      <c r="F87" s="14"/>
+        <v>280</v>
+      </c>
+      <c r="E87" s="18"/>
+      <c r="F87" s="18" t="s">
+        <v>281</v>
+      </c>
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="14"/>
       <c r="J87" s="14"/>
-      <c r="K87" s="15"/>
-    </row>
-    <row r="88" spans="1:11" ht="46.5" customHeight="1">
+      <c r="K87" s="14"/>
+      <c r="L87" s="15"/>
+    </row>
+    <row r="88" spans="1:12" ht="46.5" customHeight="1">
       <c r="A88" s="4">
         <v>94</v>
       </c>
-      <c r="B88" s="51"/>
-      <c r="C88" s="51"/>
+      <c r="B88" s="50"/>
+      <c r="C88" s="50"/>
       <c r="D88" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="E88" s="18" t="s">
-        <v>268</v>
-      </c>
-      <c r="F88" s="14"/>
+        <v>282</v>
+      </c>
+      <c r="E88" s="18"/>
+      <c r="F88" s="18" t="s">
+        <v>283</v>
+      </c>
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="14"/>
       <c r="J88" s="14"/>
-      <c r="K88" s="15"/>
-    </row>
-    <row r="89" spans="1:11" ht="46.5" customHeight="1">
+      <c r="K88" s="14"/>
+      <c r="L88" s="15"/>
+    </row>
+    <row r="89" spans="1:12" ht="46.5" customHeight="1">
       <c r="A89" s="4">
         <v>95</v>
       </c>
-      <c r="B89" s="51"/>
-      <c r="C89" s="51"/>
+      <c r="B89" s="50"/>
+      <c r="C89" s="50"/>
       <c r="D89" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="E89" s="18" t="s">
-        <v>270</v>
-      </c>
-      <c r="F89" s="14"/>
+        <v>284</v>
+      </c>
+      <c r="E89" s="18"/>
+      <c r="F89" s="18" t="s">
+        <v>285</v>
+      </c>
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="14"/>
       <c r="J89" s="14"/>
-      <c r="K89" s="15"/>
-    </row>
-    <row r="90" spans="1:11" ht="46.5" customHeight="1">
+      <c r="K89" s="14"/>
+      <c r="L89" s="15"/>
+    </row>
+    <row r="90" spans="1:12" ht="46.5" customHeight="1">
       <c r="A90" s="4">
         <v>96</v>
       </c>
-      <c r="B90" s="51"/>
-      <c r="C90" s="51"/>
+      <c r="B90" s="50"/>
+      <c r="C90" s="50"/>
       <c r="D90" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="E90" s="18" t="s">
-        <v>272</v>
-      </c>
-      <c r="F90" s="14"/>
+        <v>286</v>
+      </c>
+      <c r="E90" s="18"/>
+      <c r="F90" s="18" t="s">
+        <v>287</v>
+      </c>
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="14"/>
       <c r="J90" s="14"/>
-      <c r="K90" s="15"/>
-    </row>
-    <row r="91" spans="1:11" ht="46.5" customHeight="1">
+      <c r="K90" s="14"/>
+      <c r="L90" s="15"/>
+    </row>
+    <row r="91" spans="1:12" ht="46.5" customHeight="1">
       <c r="A91" s="4">
         <v>97</v>
       </c>
-      <c r="B91" s="51"/>
-      <c r="C91" s="51"/>
+      <c r="B91" s="50"/>
+      <c r="C91" s="50"/>
       <c r="D91" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="E91" s="18" t="s">
-        <v>274</v>
-      </c>
-      <c r="F91" s="14"/>
+        <v>288</v>
+      </c>
+      <c r="E91" s="18"/>
+      <c r="F91" s="18" t="s">
+        <v>289</v>
+      </c>
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="14"/>
       <c r="J91" s="14"/>
-      <c r="K91" s="15"/>
-    </row>
-    <row r="92" spans="1:11" ht="54" customHeight="1">
+      <c r="K91" s="14"/>
+      <c r="L91" s="15"/>
+    </row>
+    <row r="92" spans="1:12" ht="54" customHeight="1">
       <c r="A92" s="4">
         <v>98</v>
       </c>
-      <c r="B92" s="51" t="s">
-        <v>275</v>
-      </c>
-      <c r="C92" s="51" t="s">
-        <v>276</v>
+      <c r="B92" s="50" t="s">
+        <v>290</v>
+      </c>
+      <c r="C92" s="50" t="s">
+        <v>291</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="E92" s="18" t="s">
-        <v>278</v>
-      </c>
-      <c r="F92" s="14"/>
+        <v>292</v>
+      </c>
+      <c r="E92" s="18"/>
+      <c r="F92" s="18" t="s">
+        <v>293</v>
+      </c>
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="14"/>
       <c r="J92" s="14"/>
-      <c r="K92" s="15"/>
-    </row>
-    <row r="93" spans="1:11" ht="54" customHeight="1">
+      <c r="K92" s="14"/>
+      <c r="L92" s="15"/>
+    </row>
+    <row r="93" spans="1:12" ht="54" customHeight="1">
       <c r="A93" s="4">
         <v>99</v>
       </c>
-      <c r="B93" s="51"/>
-      <c r="C93" s="51"/>
+      <c r="B93" s="50"/>
+      <c r="C93" s="50"/>
       <c r="D93" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="E93" s="18" t="s">
-        <v>280</v>
-      </c>
-      <c r="F93" s="14"/>
+        <v>294</v>
+      </c>
+      <c r="E93" s="18"/>
+      <c r="F93" s="18" t="s">
+        <v>295</v>
+      </c>
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="14"/>
       <c r="J93" s="14"/>
-      <c r="K93" s="15"/>
-    </row>
-    <row r="94" spans="1:11" ht="54" customHeight="1">
+      <c r="K93" s="14"/>
+      <c r="L93" s="15"/>
+    </row>
+    <row r="94" spans="1:12" ht="54" customHeight="1">
       <c r="A94" s="4">
         <v>100</v>
       </c>
-      <c r="B94" s="51"/>
-      <c r="C94" s="51"/>
+      <c r="B94" s="50"/>
+      <c r="C94" s="50"/>
       <c r="D94" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="E94" s="18" t="s">
-        <v>282</v>
-      </c>
-      <c r="F94" s="14"/>
+        <v>296</v>
+      </c>
+      <c r="E94" s="18"/>
+      <c r="F94" s="18" t="s">
+        <v>297</v>
+      </c>
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="14"/>
       <c r="J94" s="14"/>
-      <c r="K94" s="15"/>
-    </row>
-    <row r="95" spans="1:11" ht="54" customHeight="1">
+      <c r="K94" s="14"/>
+      <c r="L94" s="15"/>
+    </row>
+    <row r="95" spans="1:12" ht="54" customHeight="1">
       <c r="A95" s="4">
         <v>101</v>
       </c>
-      <c r="B95" s="51"/>
-      <c r="C95" s="51" t="s">
-        <v>283</v>
+      <c r="B95" s="50"/>
+      <c r="C95" s="50" t="s">
+        <v>298</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="E95" s="18" t="s">
-        <v>285</v>
-      </c>
-      <c r="F95" s="14"/>
+        <v>299</v>
+      </c>
+      <c r="E95" s="18"/>
+      <c r="F95" s="18" t="s">
+        <v>300</v>
+      </c>
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="14"/>
       <c r="J95" s="14"/>
-      <c r="K95" s="15"/>
-    </row>
-    <row r="96" spans="1:11" ht="54" customHeight="1">
+      <c r="K95" s="14"/>
+      <c r="L95" s="15"/>
+    </row>
+    <row r="96" spans="1:12" ht="54" customHeight="1">
       <c r="A96" s="4">
         <v>102</v>
       </c>
-      <c r="B96" s="51"/>
-      <c r="C96" s="51"/>
+      <c r="B96" s="50"/>
+      <c r="C96" s="50"/>
       <c r="D96" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="E96" s="18" t="s">
-        <v>287</v>
-      </c>
-      <c r="F96" s="14"/>
+        <v>301</v>
+      </c>
+      <c r="E96" s="18"/>
+      <c r="F96" s="18" t="s">
+        <v>302</v>
+      </c>
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="14"/>
       <c r="J96" s="14"/>
-      <c r="K96" s="15"/>
-    </row>
-    <row r="97" spans="1:11" ht="54" customHeight="1">
+      <c r="K96" s="14"/>
+      <c r="L96" s="15"/>
+    </row>
+    <row r="97" spans="1:12" ht="54" customHeight="1">
       <c r="A97" s="4">
         <v>103</v>
       </c>
-      <c r="B97" s="51"/>
-      <c r="C97" s="51"/>
+      <c r="B97" s="50"/>
+      <c r="C97" s="50"/>
       <c r="D97" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="E97" s="18" t="s">
-        <v>289</v>
-      </c>
-      <c r="F97" s="14"/>
+        <v>303</v>
+      </c>
+      <c r="E97" s="18"/>
+      <c r="F97" s="18" t="s">
+        <v>304</v>
+      </c>
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="14"/>
       <c r="J97" s="14"/>
-      <c r="K97" s="15"/>
-    </row>
-    <row r="98" spans="1:11" ht="54" customHeight="1">
+      <c r="K97" s="14"/>
+      <c r="L97" s="15"/>
+    </row>
+    <row r="98" spans="1:12" ht="54" customHeight="1">
       <c r="A98" s="4">
         <v>104</v>
       </c>
-      <c r="B98" s="51"/>
-      <c r="C98" s="51"/>
+      <c r="B98" s="50"/>
+      <c r="C98" s="50"/>
       <c r="D98" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="E98" s="18" t="s">
-        <v>291</v>
-      </c>
-      <c r="F98" s="14"/>
+        <v>305</v>
+      </c>
+      <c r="E98" s="18"/>
+      <c r="F98" s="18" t="s">
+        <v>306</v>
+      </c>
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="14"/>
       <c r="J98" s="14"/>
-      <c r="K98" s="15"/>
-    </row>
-    <row r="99" spans="1:11" ht="54" customHeight="1">
+      <c r="K98" s="14"/>
+      <c r="L98" s="15"/>
+    </row>
+    <row r="99" spans="1:12" ht="54" customHeight="1">
       <c r="A99" s="4">
         <v>105</v>
       </c>
-      <c r="B99" s="51"/>
-      <c r="C99" s="51"/>
+      <c r="B99" s="50"/>
+      <c r="C99" s="50"/>
       <c r="D99" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="E99" s="18" t="s">
-        <v>293</v>
-      </c>
-      <c r="F99" s="14"/>
+        <v>307</v>
+      </c>
+      <c r="E99" s="18"/>
+      <c r="F99" s="18" t="s">
+        <v>308</v>
+      </c>
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="14"/>
       <c r="J99" s="14"/>
-      <c r="K99" s="15"/>
-    </row>
-    <row r="100" spans="1:11" ht="54" customHeight="1">
+      <c r="K99" s="14"/>
+      <c r="L99" s="15"/>
+    </row>
+    <row r="100" spans="1:12" ht="54" customHeight="1">
       <c r="A100" s="4">
         <v>106</v>
       </c>
-      <c r="B100" s="51"/>
+      <c r="B100" s="50"/>
       <c r="C100" s="6" t="s">
-        <v>294</v>
+        <v>309</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="E100" s="18" t="s">
-        <v>295</v>
-      </c>
-      <c r="F100" s="14"/>
+        <v>123</v>
+      </c>
+      <c r="E100" s="18"/>
+      <c r="F100" s="18" t="s">
+        <v>310</v>
+      </c>
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="14"/>
       <c r="J100" s="14"/>
-      <c r="K100" s="15"/>
-    </row>
-    <row r="101" spans="1:11" ht="63" customHeight="1">
+      <c r="K100" s="14"/>
+      <c r="L100" s="15"/>
+    </row>
+    <row r="101" spans="1:12" ht="63" customHeight="1">
       <c r="A101" s="4">
         <v>107</v>
       </c>
-      <c r="B101" s="51" t="s">
-        <v>296</v>
-      </c>
-      <c r="C101" s="51" t="s">
-        <v>297</v>
+      <c r="B101" s="50" t="s">
+        <v>311</v>
+      </c>
+      <c r="C101" s="50" t="s">
+        <v>312</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="E101" s="18" t="s">
-        <v>299</v>
-      </c>
-      <c r="F101" s="14"/>
+        <v>313</v>
+      </c>
+      <c r="E101" s="18"/>
+      <c r="F101" s="18" t="s">
+        <v>314</v>
+      </c>
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="14"/>
       <c r="J101" s="14"/>
-      <c r="K101" s="32"/>
-    </row>
-    <row r="102" spans="1:11" ht="34.5" customHeight="1">
+      <c r="K101" s="14"/>
+      <c r="L101" s="32"/>
+    </row>
+    <row r="102" spans="1:12" ht="34.5" customHeight="1">
       <c r="A102" s="4">
         <v>108</v>
       </c>
-      <c r="B102" s="51"/>
-      <c r="C102" s="51"/>
+      <c r="B102" s="50"/>
+      <c r="C102" s="50"/>
       <c r="D102" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="E102" s="18" t="s">
-        <v>301</v>
-      </c>
-      <c r="F102" s="14"/>
+        <v>315</v>
+      </c>
+      <c r="E102" s="18"/>
+      <c r="F102" s="18" t="s">
+        <v>316</v>
+      </c>
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="14"/>
       <c r="J102" s="14"/>
-      <c r="K102" s="15"/>
-    </row>
-    <row r="103" spans="1:11" ht="36" customHeight="1">
+      <c r="K102" s="14"/>
+      <c r="L102" s="15"/>
+    </row>
+    <row r="103" spans="1:12" ht="36" customHeight="1">
       <c r="A103" s="4">
         <v>109</v>
       </c>
-      <c r="B103" s="51"/>
+      <c r="B103" s="50"/>
       <c r="C103" s="6" t="s">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="E103" s="18" t="s">
-        <v>304</v>
-      </c>
-      <c r="F103" s="14"/>
+        <v>318</v>
+      </c>
+      <c r="E103" s="18"/>
+      <c r="F103" s="18" t="s">
+        <v>319</v>
+      </c>
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="14"/>
       <c r="J103" s="14"/>
-      <c r="K103" s="15"/>
-    </row>
-    <row r="104" spans="1:11" ht="45.75">
+      <c r="K103" s="14"/>
+      <c r="L103" s="15"/>
+    </row>
+    <row r="104" spans="1:12" ht="45.75">
       <c r="A104" s="4">
         <v>110</v>
       </c>
-      <c r="B104" s="51"/>
-      <c r="C104" s="51" t="s">
-        <v>305</v>
+      <c r="B104" s="50"/>
+      <c r="C104" s="50" t="s">
+        <v>320</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="E104" s="18" t="s">
-        <v>307</v>
-      </c>
-      <c r="F104" s="13" t="s">
-        <v>308</v>
+        <v>321</v>
+      </c>
+      <c r="E104" s="18"/>
+      <c r="F104" s="18" t="s">
+        <v>322</v>
       </c>
       <c r="G104" s="13" t="s">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="H104" s="13" t="s">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="I104" s="13" t="s">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="J104" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="K104" s="15"/>
-    </row>
-    <row r="105" spans="1:11" ht="41.25" customHeight="1">
+        <v>323</v>
+      </c>
+      <c r="K104" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="L104" s="15"/>
+    </row>
+    <row r="105" spans="1:12" ht="41.25" customHeight="1">
       <c r="A105" s="4">
         <v>111</v>
       </c>
-      <c r="B105" s="51"/>
-      <c r="C105" s="51"/>
+      <c r="B105" s="50"/>
+      <c r="C105" s="50"/>
       <c r="D105" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="E105" s="18" t="s">
-        <v>310</v>
-      </c>
-      <c r="F105" s="14" t="s">
-        <v>311</v>
+        <v>324</v>
+      </c>
+      <c r="E105" s="18"/>
+      <c r="F105" s="18" t="s">
+        <v>325</v>
       </c>
       <c r="G105" s="14" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="H105" s="14" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="I105" s="14" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="J105" s="14" t="s">
-        <v>311</v>
-      </c>
-      <c r="K105" s="15"/>
-    </row>
-    <row r="106" spans="1:11" ht="41.25" customHeight="1">
+        <v>326</v>
+      </c>
+      <c r="K105" s="14" t="s">
+        <v>326</v>
+      </c>
+      <c r="L105" s="15"/>
+    </row>
+    <row r="106" spans="1:12" ht="41.25" customHeight="1">
       <c r="A106" s="4">
         <v>112</v>
       </c>
-      <c r="B106" s="51"/>
-      <c r="C106" s="51"/>
+      <c r="B106" s="50"/>
+      <c r="C106" s="50"/>
       <c r="D106" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="E106" s="29" t="s">
-        <v>313</v>
-      </c>
-      <c r="F106" s="30" t="s">
-        <v>311</v>
+        <v>327</v>
+      </c>
+      <c r="E106" s="29"/>
+      <c r="F106" s="29" t="s">
+        <v>328</v>
       </c>
       <c r="G106" s="30" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="H106" s="30" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="I106" s="30" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="J106" s="30" t="s">
-        <v>311</v>
-      </c>
-      <c r="K106" s="31"/>
-    </row>
-    <row r="107" spans="1:11" ht="41.25" customHeight="1">
+        <v>326</v>
+      </c>
+      <c r="K106" s="30" t="s">
+        <v>326</v>
+      </c>
+      <c r="L106" s="31"/>
+    </row>
+    <row r="107" spans="1:12" ht="41.25" customHeight="1">
       <c r="A107" s="4">
         <v>113</v>
       </c>
-      <c r="B107" s="51"/>
-      <c r="C107" s="51" t="s">
-        <v>314</v>
+      <c r="B107" s="50"/>
+      <c r="C107" s="50" t="s">
+        <v>329</v>
       </c>
       <c r="D107" s="18" t="s">
-        <v>315</v>
-      </c>
-      <c r="E107" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="F107" s="14"/>
+        <v>330</v>
+      </c>
+      <c r="E107" s="18"/>
+      <c r="F107" s="6" t="s">
+        <v>331</v>
+      </c>
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="14"/>
       <c r="J107" s="14"/>
-      <c r="K107" s="15"/>
-    </row>
-    <row r="108" spans="1:11" ht="41.25" customHeight="1">
+      <c r="K107" s="14"/>
+      <c r="L107" s="15"/>
+    </row>
+    <row r="108" spans="1:12" ht="41.25" customHeight="1">
       <c r="A108" s="4">
         <v>114</v>
       </c>
-      <c r="B108" s="51"/>
-      <c r="C108" s="51"/>
+      <c r="B108" s="50"/>
+      <c r="C108" s="50"/>
       <c r="D108" s="18" t="s">
-        <v>317</v>
-      </c>
-      <c r="E108" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="F108" s="14"/>
+        <v>332</v>
+      </c>
+      <c r="E108" s="18"/>
+      <c r="F108" s="6" t="s">
+        <v>333</v>
+      </c>
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="14"/>
       <c r="J108" s="14"/>
-      <c r="K108" s="15"/>
-    </row>
-    <row r="109" spans="1:11">
-      <c r="F109" s="26"/>
+      <c r="K108" s="14"/>
+      <c r="L108" s="15"/>
+    </row>
+    <row r="109" spans="1:12">
       <c r="G109" s="26"/>
       <c r="H109" s="26"/>
       <c r="I109" s="26"/>
       <c r="J109" s="26"/>
-      <c r="K109" s="27"/>
-    </row>
-    <row r="110" spans="1:11">
-      <c r="F110" s="26"/>
+      <c r="K109" s="26"/>
+      <c r="L109" s="27"/>
+    </row>
+    <row r="110" spans="1:12">
       <c r="G110" s="26"/>
       <c r="H110" s="26"/>
       <c r="I110" s="26"/>
       <c r="J110" s="26"/>
-      <c r="K110" s="27"/>
-    </row>
-    <row r="111" spans="1:11">
-      <c r="F111" s="26"/>
+      <c r="K110" s="26"/>
+      <c r="L110" s="27"/>
+    </row>
+    <row r="111" spans="1:12">
       <c r="G111" s="26"/>
       <c r="H111" s="26"/>
       <c r="I111" s="26"/>
       <c r="J111" s="26"/>
-      <c r="K111" s="27"/>
-    </row>
-    <row r="112" spans="1:11">
-      <c r="F112" s="26"/>
+      <c r="K111" s="26"/>
+      <c r="L111" s="27"/>
+    </row>
+    <row r="112" spans="1:12">
       <c r="G112" s="26"/>
       <c r="H112" s="26"/>
       <c r="I112" s="26"/>
       <c r="J112" s="26"/>
-      <c r="K112" s="27"/>
-    </row>
-    <row r="113" spans="6:11">
-      <c r="F113" s="26"/>
+      <c r="K112" s="26"/>
+      <c r="L112" s="27"/>
+    </row>
+    <row r="113" spans="7:12">
       <c r="G113" s="26"/>
       <c r="H113" s="26"/>
       <c r="I113" s="26"/>
       <c r="J113" s="26"/>
-      <c r="K113" s="28"/>
-    </row>
-    <row r="114" spans="6:11">
-      <c r="F114" s="26"/>
+      <c r="K113" s="26"/>
+      <c r="L113" s="28"/>
+    </row>
+    <row r="114" spans="7:12">
       <c r="G114" s="26"/>
       <c r="H114" s="26"/>
       <c r="I114" s="26"/>
       <c r="J114" s="26"/>
-      <c r="K114" s="27"/>
-    </row>
-    <row r="115" spans="6:11">
-      <c r="F115" s="26"/>
+      <c r="K114" s="26"/>
+      <c r="L114" s="27"/>
+    </row>
+    <row r="115" spans="7:12">
       <c r="G115" s="26"/>
       <c r="H115" s="26"/>
       <c r="I115" s="26"/>
       <c r="J115" s="26"/>
-      <c r="K115" s="27"/>
-    </row>
-    <row r="116" spans="6:11">
-      <c r="F116" s="26"/>
+      <c r="K115" s="26"/>
+      <c r="L115" s="27"/>
+    </row>
+    <row r="116" spans="7:12">
       <c r="G116" s="26"/>
       <c r="H116" s="26"/>
       <c r="I116" s="26"/>
       <c r="J116" s="26"/>
-      <c r="K116" s="27"/>
-    </row>
-    <row r="117" spans="6:11">
-      <c r="F117" s="26"/>
+      <c r="K116" s="26"/>
+      <c r="L116" s="27"/>
+    </row>
+    <row r="117" spans="7:12">
       <c r="G117" s="26"/>
       <c r="H117" s="26"/>
       <c r="I117" s="26"/>
       <c r="J117" s="26"/>
-      <c r="K117" s="27"/>
-    </row>
-    <row r="118" spans="6:11">
-      <c r="F118" s="26"/>
+      <c r="K117" s="26"/>
+      <c r="L117" s="27"/>
+    </row>
+    <row r="118" spans="7:12">
       <c r="G118" s="26"/>
       <c r="H118" s="26"/>
       <c r="I118" s="26"/>
       <c r="J118" s="26"/>
-      <c r="K118" s="27"/>
-    </row>
-    <row r="119" spans="6:11">
-      <c r="F119" s="27"/>
-      <c r="G119" s="26"/>
+      <c r="K118" s="26"/>
+      <c r="L118" s="27"/>
+    </row>
+    <row r="119" spans="7:12">
+      <c r="G119" s="27"/>
       <c r="H119" s="26"/>
       <c r="I119" s="26"/>
       <c r="J119" s="26"/>
-      <c r="K119" s="27"/>
-    </row>
-    <row r="120" spans="6:11">
-      <c r="F120" s="27"/>
-      <c r="G120" s="26"/>
+      <c r="K119" s="26"/>
+      <c r="L119" s="27"/>
+    </row>
+    <row r="120" spans="7:12">
+      <c r="G120" s="27"/>
       <c r="H120" s="26"/>
       <c r="I120" s="26"/>
       <c r="J120" s="26"/>
-      <c r="K120" s="27"/>
-    </row>
-    <row r="121" spans="6:11">
-      <c r="F121" s="27"/>
-      <c r="G121" s="26"/>
+      <c r="K120" s="26"/>
+      <c r="L120" s="27"/>
+    </row>
+    <row r="121" spans="7:12">
+      <c r="G121" s="27"/>
       <c r="H121" s="26"/>
       <c r="I121" s="26"/>
       <c r="J121" s="26"/>
-      <c r="K121" s="27"/>
-    </row>
-    <row r="122" spans="6:11">
-      <c r="F122" s="27"/>
-      <c r="G122" s="26"/>
+      <c r="K121" s="26"/>
+      <c r="L121" s="27"/>
+    </row>
+    <row r="122" spans="7:12">
+      <c r="G122" s="27"/>
       <c r="H122" s="26"/>
       <c r="I122" s="26"/>
       <c r="J122" s="26"/>
-      <c r="K122" s="27"/>
-    </row>
-    <row r="123" spans="6:11">
-      <c r="F123" s="27"/>
-      <c r="G123" s="26"/>
+      <c r="K122" s="26"/>
+      <c r="L122" s="27"/>
+    </row>
+    <row r="123" spans="7:12">
+      <c r="G123" s="27"/>
       <c r="H123" s="26"/>
       <c r="I123" s="26"/>
       <c r="J123" s="26"/>
-      <c r="K123" s="27"/>
-    </row>
-    <row r="124" spans="6:11">
-      <c r="F124" s="27"/>
-      <c r="G124" s="26"/>
+      <c r="K123" s="26"/>
+      <c r="L123" s="27"/>
+    </row>
+    <row r="124" spans="7:12">
+      <c r="G124" s="27"/>
       <c r="H124" s="26"/>
       <c r="I124" s="26"/>
       <c r="J124" s="26"/>
-      <c r="K124" s="28"/>
-    </row>
-    <row r="125" spans="6:11">
-      <c r="F125" s="27"/>
-      <c r="G125" s="26"/>
+      <c r="K124" s="26"/>
+      <c r="L124" s="28"/>
+    </row>
+    <row r="125" spans="7:12">
+      <c r="G125" s="27"/>
       <c r="H125" s="26"/>
       <c r="I125" s="26"/>
       <c r="J125" s="26"/>
-      <c r="K125" s="27"/>
-    </row>
-    <row r="126" spans="6:11">
-      <c r="F126" s="27"/>
-      <c r="G126" s="26"/>
+      <c r="K125" s="26"/>
+      <c r="L125" s="27"/>
+    </row>
+    <row r="126" spans="7:12">
+      <c r="G126" s="27"/>
       <c r="H126" s="26"/>
       <c r="I126" s="26"/>
       <c r="J126" s="26"/>
-      <c r="K126" s="27"/>
-    </row>
-    <row r="127" spans="6:11">
-      <c r="F127" s="27"/>
-      <c r="G127" s="26"/>
+      <c r="K126" s="26"/>
+      <c r="L126" s="27"/>
+    </row>
+    <row r="127" spans="7:12">
+      <c r="G127" s="27"/>
       <c r="H127" s="26"/>
       <c r="I127" s="26"/>
       <c r="J127" s="26"/>
-      <c r="K127" s="27"/>
-    </row>
-    <row r="128" spans="6:11">
-      <c r="F128" s="27"/>
-      <c r="G128" s="26"/>
+      <c r="K127" s="26"/>
+      <c r="L127" s="27"/>
+    </row>
+    <row r="128" spans="7:12">
+      <c r="G128" s="27"/>
       <c r="H128" s="26"/>
       <c r="I128" s="26"/>
       <c r="J128" s="26"/>
-      <c r="K128" s="27"/>
-    </row>
-    <row r="129" spans="6:11">
-      <c r="F129" s="27"/>
-      <c r="G129" s="26"/>
+      <c r="K128" s="26"/>
+      <c r="L128" s="27"/>
+    </row>
+    <row r="129" spans="7:12">
+      <c r="G129" s="27"/>
       <c r="H129" s="26"/>
       <c r="I129" s="26"/>
       <c r="J129" s="26"/>
-      <c r="K129" s="27"/>
-    </row>
-    <row r="130" spans="6:11">
-      <c r="F130" s="27"/>
-      <c r="G130" s="26"/>
+      <c r="K129" s="26"/>
+      <c r="L129" s="27"/>
+    </row>
+    <row r="130" spans="7:12">
+      <c r="G130" s="27"/>
       <c r="H130" s="26"/>
       <c r="I130" s="26"/>
       <c r="J130" s="26"/>
-      <c r="K130" s="27"/>
-    </row>
-    <row r="131" spans="6:11">
-      <c r="F131" s="27"/>
-      <c r="G131" s="26"/>
+      <c r="K130" s="26"/>
+      <c r="L130" s="27"/>
+    </row>
+    <row r="131" spans="7:12">
+      <c r="G131" s="27"/>
       <c r="H131" s="26"/>
       <c r="I131" s="26"/>
       <c r="J131" s="26"/>
-      <c r="K131" s="27"/>
-    </row>
-    <row r="132" spans="6:11">
-      <c r="F132" s="27"/>
-      <c r="G132" s="26"/>
+      <c r="K131" s="26"/>
+      <c r="L131" s="27"/>
+    </row>
+    <row r="132" spans="7:12">
+      <c r="G132" s="27"/>
       <c r="H132" s="26"/>
       <c r="I132" s="26"/>
       <c r="J132" s="26"/>
-      <c r="K132" s="27"/>
-    </row>
-    <row r="133" spans="6:11">
-      <c r="F133" s="27"/>
-      <c r="G133" s="26"/>
+      <c r="K132" s="26"/>
+      <c r="L132" s="27"/>
+    </row>
+    <row r="133" spans="7:12">
+      <c r="G133" s="27"/>
       <c r="H133" s="26"/>
       <c r="I133" s="26"/>
       <c r="J133" s="26"/>
-      <c r="K133" s="27"/>
-    </row>
-    <row r="134" spans="6:11">
-      <c r="F134" s="27"/>
-      <c r="G134" s="26"/>
+      <c r="K133" s="26"/>
+      <c r="L133" s="27"/>
+    </row>
+    <row r="134" spans="7:12">
+      <c r="G134" s="27"/>
       <c r="H134" s="26"/>
       <c r="I134" s="26"/>
       <c r="J134" s="26"/>
-      <c r="K134" s="27"/>
-    </row>
-    <row r="135" spans="6:11">
-      <c r="F135" s="27"/>
-      <c r="G135" s="26"/>
+      <c r="K134" s="26"/>
+      <c r="L134" s="27"/>
+    </row>
+    <row r="135" spans="7:12">
+      <c r="G135" s="27"/>
       <c r="H135" s="26"/>
       <c r="I135" s="26"/>
       <c r="J135" s="26"/>
-      <c r="K135" s="27"/>
-    </row>
-    <row r="136" spans="6:11">
-      <c r="G136" s="12"/>
+      <c r="K135" s="26"/>
+      <c r="L135" s="27"/>
+    </row>
+    <row r="136" spans="7:12">
       <c r="H136" s="12"/>
       <c r="I136" s="12"/>
       <c r="J136" s="12"/>
-    </row>
-    <row r="137" spans="6:11">
-      <c r="G137" s="12"/>
+      <c r="K136" s="12"/>
+    </row>
+    <row r="137" spans="7:12">
       <c r="H137" s="12"/>
       <c r="I137" s="12"/>
       <c r="J137" s="12"/>
-    </row>
-    <row r="138" spans="6:11">
-      <c r="G138" s="12"/>
+      <c r="K137" s="12"/>
+    </row>
+    <row r="138" spans="7:12">
       <c r="H138" s="12"/>
       <c r="I138" s="12"/>
       <c r="J138" s="12"/>
-    </row>
-    <row r="139" spans="6:11">
-      <c r="G139" s="12"/>
+      <c r="K138" s="12"/>
+    </row>
+    <row r="139" spans="7:12">
       <c r="H139" s="12"/>
       <c r="I139" s="12"/>
       <c r="J139" s="12"/>
-    </row>
-    <row r="140" spans="6:11">
-      <c r="G140" s="12"/>
+      <c r="K139" s="12"/>
+    </row>
+    <row r="140" spans="7:12">
       <c r="H140" s="12"/>
       <c r="I140" s="12"/>
       <c r="J140" s="12"/>
-    </row>
-    <row r="141" spans="6:11">
-      <c r="G141" s="12"/>
+      <c r="K140" s="12"/>
+    </row>
+    <row r="141" spans="7:12">
       <c r="H141" s="12"/>
       <c r="I141" s="12"/>
       <c r="J141" s="12"/>
-    </row>
-    <row r="142" spans="6:11">
-      <c r="G142" s="12"/>
+      <c r="K141" s="12"/>
+    </row>
+    <row r="142" spans="7:12">
       <c r="H142" s="12"/>
       <c r="I142" s="12"/>
       <c r="J142" s="12"/>
-    </row>
-    <row r="143" spans="6:11">
-      <c r="G143" s="12"/>
+      <c r="K142" s="12"/>
+    </row>
+    <row r="143" spans="7:12">
       <c r="H143" s="12"/>
       <c r="I143" s="12"/>
       <c r="J143" s="12"/>
-    </row>
-    <row r="144" spans="6:11">
-      <c r="G144" s="12"/>
+      <c r="K143" s="12"/>
+    </row>
+    <row r="144" spans="7:12">
       <c r="H144" s="12"/>
       <c r="I144" s="12"/>
       <c r="J144" s="12"/>
-    </row>
-    <row r="145" spans="7:10">
-      <c r="G145" s="12"/>
+      <c r="K144" s="12"/>
+    </row>
+    <row r="145" spans="8:11">
       <c r="H145" s="12"/>
       <c r="I145" s="12"/>
       <c r="J145" s="12"/>
-    </row>
-    <row r="146" spans="7:10">
-      <c r="G146" s="12"/>
+      <c r="K145" s="12"/>
+    </row>
+    <row r="146" spans="8:11">
       <c r="H146" s="12"/>
       <c r="I146" s="12"/>
       <c r="J146" s="12"/>
-    </row>
-    <row r="147" spans="7:10">
-      <c r="G147" s="12"/>
+      <c r="K146" s="12"/>
+    </row>
+    <row r="147" spans="8:11">
       <c r="H147" s="12"/>
       <c r="I147" s="12"/>
       <c r="J147" s="12"/>
-    </row>
-    <row r="148" spans="7:10">
-      <c r="G148" s="12"/>
+      <c r="K147" s="12"/>
+    </row>
+    <row r="148" spans="8:11">
       <c r="H148" s="12"/>
       <c r="I148" s="12"/>
       <c r="J148" s="12"/>
-    </row>
-    <row r="149" spans="7:10">
-      <c r="G149" s="12"/>
+      <c r="K148" s="12"/>
+    </row>
+    <row r="149" spans="8:11">
       <c r="H149" s="12"/>
       <c r="I149" s="12"/>
       <c r="J149" s="12"/>
-    </row>
-    <row r="150" spans="7:10">
-      <c r="G150" s="12"/>
+      <c r="K149" s="12"/>
+    </row>
+    <row r="150" spans="8:11">
       <c r="H150" s="12"/>
       <c r="I150" s="12"/>
       <c r="J150" s="12"/>
-    </row>
-    <row r="151" spans="7:10">
-      <c r="G151" s="12"/>
+      <c r="K150" s="12"/>
+    </row>
+    <row r="151" spans="8:11">
       <c r="H151" s="12"/>
       <c r="I151" s="12"/>
       <c r="J151" s="12"/>
-    </row>
-    <row r="152" spans="7:10">
-      <c r="G152" s="12"/>
+      <c r="K151" s="12"/>
+    </row>
+    <row r="152" spans="8:11">
       <c r="H152" s="12"/>
       <c r="I152" s="12"/>
       <c r="J152" s="12"/>
-    </row>
-    <row r="153" spans="7:10">
-      <c r="G153" s="12"/>
+      <c r="K152" s="12"/>
+    </row>
+    <row r="153" spans="8:11">
       <c r="H153" s="12"/>
       <c r="I153" s="12"/>
       <c r="J153" s="12"/>
-    </row>
-    <row r="154" spans="7:10">
-      <c r="G154" s="12"/>
+      <c r="K153" s="12"/>
+    </row>
+    <row r="154" spans="8:11">
       <c r="H154" s="12"/>
       <c r="I154" s="12"/>
       <c r="J154" s="12"/>
-    </row>
-    <row r="155" spans="7:10">
-      <c r="G155" s="12"/>
+      <c r="K154" s="12"/>
+    </row>
+    <row r="155" spans="8:11">
       <c r="H155" s="12"/>
       <c r="I155" s="12"/>
       <c r="J155" s="12"/>
-    </row>
-    <row r="156" spans="7:10">
-      <c r="G156" s="12"/>
+      <c r="K155" s="12"/>
+    </row>
+    <row r="156" spans="8:11">
       <c r="H156" s="12"/>
       <c r="I156" s="12"/>
       <c r="J156" s="12"/>
-    </row>
-    <row r="157" spans="7:10">
-      <c r="G157" s="12"/>
+      <c r="K156" s="12"/>
+    </row>
+    <row r="157" spans="8:11">
       <c r="H157" s="12"/>
       <c r="I157" s="12"/>
       <c r="J157" s="12"/>
-    </row>
-    <row r="158" spans="7:10">
-      <c r="G158" s="12"/>
+      <c r="K157" s="12"/>
+    </row>
+    <row r="158" spans="8:11">
       <c r="H158" s="12"/>
       <c r="I158" s="12"/>
       <c r="J158" s="12"/>
-    </row>
-    <row r="159" spans="7:10">
-      <c r="G159" s="12"/>
+      <c r="K158" s="12"/>
+    </row>
+    <row r="159" spans="8:11">
       <c r="H159" s="12"/>
       <c r="I159" s="12"/>
       <c r="J159" s="12"/>
+      <c r="K159" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="38">
@@ -5366,7 +5669,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -5394,751 +5697,751 @@
       <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="51" t="s">
-        <v>319</v>
-      </c>
-      <c r="C2" s="51" t="s">
-        <v>320</v>
+      <c r="B2" s="50" t="s">
+        <v>334</v>
+      </c>
+      <c r="C2" s="50" t="s">
+        <v>335</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>322</v>
+        <v>337</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="60.75" customHeight="1">
       <c r="A3" s="7">
         <v>2</v>
       </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="50"/>
       <c r="D3" s="6" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>324</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="60.75" customHeight="1">
       <c r="A4" s="7">
         <v>3</v>
       </c>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="50"/>
       <c r="D4" s="6" t="s">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="60.75" customHeight="1">
       <c r="A5" s="7">
         <v>4</v>
       </c>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
+      <c r="B5" s="50"/>
+      <c r="C5" s="50"/>
       <c r="D5" s="6" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="60.75" customHeight="1">
       <c r="A6" s="7">
         <v>5</v>
       </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="51"/>
+      <c r="B6" s="50"/>
+      <c r="C6" s="50"/>
       <c r="D6" s="6" t="s">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="60.75" customHeight="1">
       <c r="A7" s="7">
         <v>6</v>
       </c>
-      <c r="B7" s="51"/>
-      <c r="C7" s="51"/>
+      <c r="B7" s="50"/>
+      <c r="C7" s="50"/>
       <c r="D7" s="6" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>332</v>
+        <v>347</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="60.75" customHeight="1">
       <c r="A8" s="7">
         <v>7</v>
       </c>
-      <c r="B8" s="51"/>
-      <c r="C8" s="51" t="s">
-        <v>333</v>
+      <c r="B8" s="50"/>
+      <c r="C8" s="50" t="s">
+        <v>348</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>334</v>
+        <v>349</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>335</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="60.75" customHeight="1">
       <c r="A9" s="7">
         <v>8</v>
       </c>
-      <c r="B9" s="51"/>
-      <c r="C9" s="51"/>
+      <c r="B9" s="50"/>
+      <c r="C9" s="50"/>
       <c r="D9" s="6" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>337</v>
+        <v>352</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="60.75" customHeight="1">
       <c r="A10" s="7">
         <v>9</v>
       </c>
-      <c r="B10" s="51"/>
-      <c r="C10" s="51"/>
+      <c r="B10" s="50"/>
+      <c r="C10" s="50"/>
       <c r="D10" s="6" t="s">
-        <v>338</v>
+        <v>353</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>339</v>
+        <v>354</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="60.75" customHeight="1">
       <c r="A11" s="7">
         <v>10</v>
       </c>
-      <c r="B11" s="51"/>
-      <c r="C11" s="51"/>
+      <c r="B11" s="50"/>
+      <c r="C11" s="50"/>
       <c r="D11" s="6" t="s">
-        <v>340</v>
+        <v>355</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>341</v>
+        <v>356</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="60.75" customHeight="1">
       <c r="A12" s="7">
         <v>11</v>
       </c>
-      <c r="B12" s="51"/>
-      <c r="C12" s="51" t="s">
-        <v>342</v>
+      <c r="B12" s="50"/>
+      <c r="C12" s="50" t="s">
+        <v>357</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>344</v>
+        <v>359</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="60.75" customHeight="1">
       <c r="A13" s="7">
         <v>12</v>
       </c>
-      <c r="B13" s="51"/>
-      <c r="C13" s="51"/>
+      <c r="B13" s="50"/>
+      <c r="C13" s="50"/>
       <c r="D13" s="6" t="s">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>346</v>
+        <v>361</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="60.75" customHeight="1">
       <c r="A14" s="7">
         <v>13</v>
       </c>
-      <c r="B14" s="51"/>
-      <c r="C14" s="51"/>
+      <c r="B14" s="50"/>
+      <c r="C14" s="50"/>
       <c r="D14" s="6" t="s">
-        <v>347</v>
+        <v>362</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>348</v>
+        <v>363</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="60.75" customHeight="1">
       <c r="A15" s="7">
         <v>14</v>
       </c>
-      <c r="B15" s="51"/>
-      <c r="C15" s="51"/>
+      <c r="B15" s="50"/>
+      <c r="C15" s="50"/>
       <c r="D15" s="6" t="s">
-        <v>349</v>
+        <v>364</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>350</v>
+        <v>365</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="60.75" customHeight="1">
       <c r="A16" s="7">
         <v>15</v>
       </c>
-      <c r="B16" s="51"/>
-      <c r="C16" s="51"/>
+      <c r="B16" s="50"/>
+      <c r="C16" s="50"/>
       <c r="D16" s="6" t="s">
-        <v>351</v>
+        <v>366</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>352</v>
+        <v>367</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="60.75" customHeight="1">
       <c r="A17" s="7">
         <v>16</v>
       </c>
-      <c r="B17" s="51"/>
-      <c r="C17" s="51"/>
+      <c r="B17" s="50"/>
+      <c r="C17" s="50"/>
       <c r="D17" s="6" t="s">
-        <v>353</v>
+        <v>368</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>354</v>
+        <v>369</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="60.75" customHeight="1">
       <c r="A18" s="7">
         <v>17</v>
       </c>
-      <c r="B18" s="51"/>
-      <c r="C18" s="51"/>
+      <c r="B18" s="50"/>
+      <c r="C18" s="50"/>
       <c r="D18" s="6" t="s">
-        <v>355</v>
+        <v>370</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>356</v>
+        <v>371</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="60.75" customHeight="1">
       <c r="A19" s="7">
         <v>18</v>
       </c>
-      <c r="B19" s="51"/>
-      <c r="C19" s="51"/>
+      <c r="B19" s="50"/>
+      <c r="C19" s="50"/>
       <c r="D19" s="6" t="s">
-        <v>357</v>
+        <v>372</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>358</v>
+        <v>373</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="60.75" customHeight="1">
       <c r="A20" s="7">
         <v>19</v>
       </c>
-      <c r="B20" s="51"/>
-      <c r="C20" s="51"/>
+      <c r="B20" s="50"/>
+      <c r="C20" s="50"/>
       <c r="D20" s="6" t="s">
-        <v>359</v>
+        <v>374</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>360</v>
+        <v>375</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="60.75" customHeight="1">
       <c r="A21" s="7">
         <v>20</v>
       </c>
-      <c r="B21" s="51"/>
-      <c r="C21" s="51" t="s">
-        <v>361</v>
+      <c r="B21" s="50"/>
+      <c r="C21" s="50" t="s">
+        <v>376</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>362</v>
+        <v>377</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>363</v>
+        <v>378</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="60.75" customHeight="1">
       <c r="A22" s="7">
         <v>21</v>
       </c>
-      <c r="B22" s="51"/>
-      <c r="C22" s="51"/>
+      <c r="B22" s="50"/>
+      <c r="C22" s="50"/>
       <c r="D22" s="6" t="s">
-        <v>364</v>
+        <v>379</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>365</v>
+        <v>380</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="60.75" customHeight="1">
       <c r="A23" s="7">
         <v>22</v>
       </c>
-      <c r="B23" s="51"/>
-      <c r="C23" s="51"/>
+      <c r="B23" s="50"/>
+      <c r="C23" s="50"/>
       <c r="D23" s="6" t="s">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>367</v>
+        <v>382</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="60.75" customHeight="1">
       <c r="A24" s="7">
         <v>23</v>
       </c>
-      <c r="B24" s="51"/>
-      <c r="C24" s="51" t="s">
-        <v>368</v>
+      <c r="B24" s="50"/>
+      <c r="C24" s="50" t="s">
+        <v>383</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>369</v>
+        <v>384</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>370</v>
+        <v>385</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="60.75" customHeight="1">
       <c r="A25" s="7">
         <v>24</v>
       </c>
-      <c r="B25" s="51"/>
-      <c r="C25" s="51"/>
+      <c r="B25" s="50"/>
+      <c r="C25" s="50"/>
       <c r="D25" s="6" t="s">
-        <v>371</v>
+        <v>386</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>372</v>
+        <v>387</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="60.75" customHeight="1">
       <c r="A26" s="7">
         <v>25</v>
       </c>
-      <c r="B26" s="51"/>
-      <c r="C26" s="51"/>
+      <c r="B26" s="50"/>
+      <c r="C26" s="50"/>
       <c r="D26" s="6" t="s">
-        <v>373</v>
+        <v>388</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>374</v>
+        <v>389</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="60.75" customHeight="1">
       <c r="A27" s="7">
         <v>26</v>
       </c>
-      <c r="B27" s="51"/>
-      <c r="C27" s="51"/>
+      <c r="B27" s="50"/>
+      <c r="C27" s="50"/>
       <c r="D27" s="6" t="s">
-        <v>375</v>
+        <v>390</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>376</v>
+        <v>391</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="60.75" customHeight="1">
       <c r="A28" s="7">
         <v>27</v>
       </c>
-      <c r="B28" s="51"/>
-      <c r="C28" s="51"/>
+      <c r="B28" s="50"/>
+      <c r="C28" s="50"/>
       <c r="D28" s="6" t="s">
-        <v>377</v>
+        <v>392</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>378</v>
+        <v>393</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="60.75" customHeight="1">
       <c r="A29" s="7">
         <v>28</v>
       </c>
-      <c r="B29" s="51"/>
-      <c r="C29" s="51" t="s">
-        <v>379</v>
+      <c r="B29" s="50"/>
+      <c r="C29" s="50" t="s">
+        <v>394</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>380</v>
+        <v>395</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>381</v>
+        <v>396</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="60.75" customHeight="1">
       <c r="A30" s="7">
         <v>29</v>
       </c>
-      <c r="B30" s="51"/>
-      <c r="C30" s="51"/>
+      <c r="B30" s="50"/>
+      <c r="C30" s="50"/>
       <c r="D30" s="6" t="s">
-        <v>382</v>
+        <v>397</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>383</v>
+        <v>398</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="60.75" customHeight="1">
       <c r="A31" s="7">
         <v>30</v>
       </c>
-      <c r="B31" s="56"/>
-      <c r="C31" s="56"/>
+      <c r="B31" s="55"/>
+      <c r="C31" s="55"/>
       <c r="D31" s="10" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>385</v>
+        <v>400</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="60.75" customHeight="1">
       <c r="A32" s="9">
         <v>31</v>
       </c>
-      <c r="B32" s="51" t="s">
-        <v>386</v>
-      </c>
-      <c r="C32" s="51" t="s">
-        <v>387</v>
+      <c r="B32" s="50" t="s">
+        <v>401</v>
+      </c>
+      <c r="C32" s="50" t="s">
+        <v>402</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>389</v>
+        <v>404</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="60.75" customHeight="1">
       <c r="A33" s="9">
         <v>32</v>
       </c>
-      <c r="B33" s="51"/>
-      <c r="C33" s="51"/>
+      <c r="B33" s="50"/>
+      <c r="C33" s="50"/>
       <c r="D33" s="11" t="s">
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>391</v>
+        <v>406</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="60.75" customHeight="1">
       <c r="A34" s="9">
         <v>33</v>
       </c>
-      <c r="B34" s="51"/>
-      <c r="C34" s="51"/>
+      <c r="B34" s="50"/>
+      <c r="C34" s="50"/>
       <c r="D34" s="11" t="s">
-        <v>392</v>
+        <v>407</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>393</v>
+        <v>408</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="60.75" customHeight="1">
       <c r="A35" s="9">
         <v>34</v>
       </c>
-      <c r="B35" s="51"/>
-      <c r="C35" s="51" t="s">
-        <v>394</v>
+      <c r="B35" s="50"/>
+      <c r="C35" s="50" t="s">
+        <v>409</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="60.75" customHeight="1">
       <c r="A36" s="9">
         <v>35</v>
       </c>
-      <c r="B36" s="51"/>
-      <c r="C36" s="51"/>
+      <c r="B36" s="50"/>
+      <c r="C36" s="50"/>
       <c r="D36" s="11" t="s">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>398</v>
+        <v>413</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="60.75" customHeight="1">
       <c r="A37" s="9">
         <v>36</v>
       </c>
-      <c r="B37" s="51"/>
-      <c r="C37" s="51"/>
+      <c r="B37" s="50"/>
+      <c r="C37" s="50"/>
       <c r="D37" s="11" t="s">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>400</v>
+        <v>415</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="60.75" customHeight="1">
       <c r="A38" s="9">
         <v>37</v>
       </c>
-      <c r="B38" s="51"/>
-      <c r="C38" s="51"/>
+      <c r="B38" s="50"/>
+      <c r="C38" s="50"/>
       <c r="D38" s="11" t="s">
-        <v>401</v>
+        <v>416</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>402</v>
+        <v>417</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="60.75" customHeight="1">
       <c r="A39" s="9">
         <v>38</v>
       </c>
-      <c r="B39" s="51"/>
-      <c r="C39" s="51" t="s">
-        <v>403</v>
+      <c r="B39" s="50"/>
+      <c r="C39" s="50" t="s">
+        <v>418</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>404</v>
+        <v>419</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>405</v>
+        <v>420</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="60.75" customHeight="1">
       <c r="A40" s="9">
         <v>39</v>
       </c>
-      <c r="B40" s="51"/>
-      <c r="C40" s="51"/>
+      <c r="B40" s="50"/>
+      <c r="C40" s="50"/>
       <c r="D40" s="11" t="s">
-        <v>406</v>
+        <v>421</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>407</v>
+        <v>422</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="60.75" customHeight="1">
       <c r="A41" s="9">
         <v>40</v>
       </c>
-      <c r="B41" s="51"/>
-      <c r="C41" s="51" t="s">
-        <v>408</v>
+      <c r="B41" s="50"/>
+      <c r="C41" s="50" t="s">
+        <v>423</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>409</v>
+        <v>424</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="60.75" customHeight="1">
       <c r="A42" s="9">
         <v>41</v>
       </c>
-      <c r="B42" s="51"/>
-      <c r="C42" s="51"/>
+      <c r="B42" s="50"/>
+      <c r="C42" s="50"/>
       <c r="D42" s="11" t="s">
-        <v>410</v>
+        <v>425</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>411</v>
+        <v>426</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="60.75" customHeight="1">
       <c r="A43" s="9">
         <v>42</v>
       </c>
-      <c r="B43" s="51"/>
-      <c r="C43" s="51" t="s">
-        <v>412</v>
+      <c r="B43" s="50"/>
+      <c r="C43" s="50" t="s">
+        <v>427</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>413</v>
+        <v>428</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="60.75" customHeight="1">
       <c r="A44" s="9">
         <v>43</v>
       </c>
-      <c r="B44" s="51"/>
-      <c r="C44" s="51"/>
+      <c r="B44" s="50"/>
+      <c r="C44" s="50"/>
       <c r="D44" s="11" t="s">
-        <v>414</v>
+        <v>429</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>415</v>
+        <v>430</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="60.75" customHeight="1">
       <c r="A45" s="9"/>
-      <c r="B45" s="51"/>
-      <c r="C45" s="51"/>
+      <c r="B45" s="50"/>
+      <c r="C45" s="50"/>
       <c r="D45" s="11" t="s">
-        <v>416</v>
+        <v>431</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>417</v>
+        <v>432</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="60.75" customHeight="1">
       <c r="A46" s="9">
         <v>45</v>
       </c>
-      <c r="B46" s="51" t="s">
-        <v>418</v>
-      </c>
-      <c r="C46" s="51" t="s">
-        <v>419</v>
+      <c r="B46" s="50" t="s">
+        <v>433</v>
+      </c>
+      <c r="C46" s="50" t="s">
+        <v>434</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>421</v>
+        <v>436</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="60.75" customHeight="1">
       <c r="A47" s="9">
         <v>46</v>
       </c>
-      <c r="B47" s="51"/>
-      <c r="C47" s="51"/>
+      <c r="B47" s="50"/>
+      <c r="C47" s="50"/>
       <c r="D47" s="11" t="s">
-        <v>422</v>
+        <v>437</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>423</v>
+        <v>438</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="60.75" customHeight="1">
       <c r="A48" s="9">
         <v>47</v>
       </c>
-      <c r="B48" s="51"/>
-      <c r="C48" s="51" t="s">
-        <v>394</v>
+      <c r="B48" s="50"/>
+      <c r="C48" s="50" t="s">
+        <v>409</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>424</v>
+        <v>439</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>425</v>
+        <v>440</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="60.75" customHeight="1">
       <c r="A49" s="9">
         <v>48</v>
       </c>
-      <c r="B49" s="51"/>
-      <c r="C49" s="51"/>
+      <c r="B49" s="50"/>
+      <c r="C49" s="50"/>
       <c r="D49" s="11" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>427</v>
+        <v>442</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="60.75" customHeight="1">
       <c r="A50" s="9">
         <v>49</v>
       </c>
-      <c r="B50" s="51"/>
-      <c r="C50" s="51"/>
+      <c r="B50" s="50"/>
+      <c r="C50" s="50"/>
       <c r="D50" s="11" t="s">
-        <v>428</v>
+        <v>443</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>429</v>
+        <v>444</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="60.75" customHeight="1">
       <c r="A51" s="9">
         <v>50</v>
       </c>
-      <c r="B51" s="51"/>
-      <c r="C51" s="51"/>
+      <c r="B51" s="50"/>
+      <c r="C51" s="50"/>
       <c r="D51" s="11" t="s">
-        <v>430</v>
+        <v>445</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>431</v>
+        <v>446</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="60.75" customHeight="1">
       <c r="A52" s="9">
         <v>51</v>
       </c>
-      <c r="B52" s="51"/>
-      <c r="C52" s="51" t="s">
-        <v>432</v>
+      <c r="B52" s="50"/>
+      <c r="C52" s="50" t="s">
+        <v>447</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>433</v>
+        <v>448</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>434</v>
+        <v>449</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="60.75" customHeight="1">
       <c r="A53" s="9">
         <v>52</v>
       </c>
-      <c r="B53" s="51"/>
-      <c r="C53" s="51"/>
+      <c r="B53" s="50"/>
+      <c r="C53" s="50"/>
       <c r="D53" s="11" t="s">
-        <v>435</v>
+        <v>450</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>436</v>
+        <v>451</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="60.75" customHeight="1">
       <c r="A54" s="9">
         <v>53</v>
       </c>
-      <c r="B54" s="51"/>
+      <c r="B54" s="50"/>
       <c r="C54" s="11" t="s">
-        <v>437</v>
+        <v>452</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>438</v>
+        <v>453</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>439</v>
+        <v>454</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="60.75" customHeight="1">
       <c r="A55" s="9">
         <v>55</v>
       </c>
-      <c r="B55" s="51"/>
-      <c r="C55" s="51" t="s">
-        <v>440</v>
+      <c r="B55" s="50"/>
+      <c r="C55" s="50" t="s">
+        <v>455</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>441</v>
+        <v>456</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>442</v>
+        <v>457</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="60.75" customHeight="1">
       <c r="A56" s="9">
         <v>56</v>
       </c>
-      <c r="B56" s="51"/>
-      <c r="C56" s="51"/>
+      <c r="B56" s="50"/>
+      <c r="C56" s="50"/>
       <c r="D56" s="11" t="s">
-        <v>443</v>
+        <v>458</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>444</v>
+        <v>459</v>
       </c>
     </row>
   </sheetData>
@@ -6168,922 +6471,1196 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7BFED6D-21E8-4E6D-9269-B75B7E326689}">
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="35.7109375" customWidth="1"/>
-    <col min="4" max="5" width="29.140625" customWidth="1"/>
+    <col min="4" max="4" width="45.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.42578125" customWidth="1"/>
     <col min="6" max="7" width="30.140625" customWidth="1"/>
     <col min="8" max="8" width="34.28515625" customWidth="1"/>
     <col min="9" max="9" width="34.7109375" customWidth="1"/>
     <col min="10" max="11" width="30.140625" customWidth="1"/>
     <col min="12" max="12" width="33.85546875" customWidth="1"/>
     <col min="13" max="13" width="37.140625" customWidth="1"/>
+    <col min="14" max="14" width="15.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="47" t="s">
-        <v>445</v>
-      </c>
-      <c r="B1" s="47" t="s">
-        <v>446</v>
-      </c>
-      <c r="C1" s="47"/>
+    <row r="1" spans="1:14" s="1" customFormat="1">
+      <c r="A1" s="49" t="s">
+        <v>460</v>
+      </c>
+      <c r="B1" s="49" t="s">
+        <v>461</v>
+      </c>
+      <c r="C1" s="49"/>
       <c r="D1" s="49" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="50"/>
-      <c r="F1" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="49" t="s">
+      <c r="F1" s="49"/>
+      <c r="G1" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="50"/>
-      <c r="J1" s="49" t="s">
+      <c r="H1" s="49"/>
+      <c r="I1" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="50"/>
-      <c r="L1" s="44" t="s">
+      <c r="J1" s="49"/>
+      <c r="K1" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="45"/>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="48"/>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="37" t="s">
-        <v>118</v>
-      </c>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="49"/>
+    </row>
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="30.75">
+      <c r="A2" s="49"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
       <c r="E2" s="37" t="s">
-        <v>447</v>
+        <v>133</v>
       </c>
       <c r="F2" s="37" t="s">
-        <v>118</v>
+        <v>462</v>
       </c>
       <c r="G2" s="37" t="s">
-        <v>447</v>
+        <v>133</v>
       </c>
       <c r="H2" s="37" t="s">
-        <v>118</v>
+        <v>462</v>
       </c>
       <c r="I2" s="37" t="s">
-        <v>447</v>
+        <v>133</v>
       </c>
       <c r="J2" s="37" t="s">
-        <v>118</v>
+        <v>462</v>
       </c>
       <c r="K2" s="37" t="s">
-        <v>447</v>
+        <v>133</v>
       </c>
       <c r="L2" s="37" t="s">
-        <v>118</v>
+        <v>462</v>
       </c>
       <c r="M2" s="37" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>133</v>
+      </c>
+      <c r="N2" s="37" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="29.25">
       <c r="A3" s="46" t="s">
-        <v>71</v>
-      </c>
-      <c r="B3" s="57" t="s">
-        <v>448</v>
-      </c>
-      <c r="C3" s="57"/>
+        <v>85</v>
+      </c>
+      <c r="B3" s="46" t="s">
+        <v>463</v>
+      </c>
+      <c r="C3" s="46"/>
       <c r="D3" s="38" t="s">
-        <v>449</v>
-      </c>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38" t="s">
-        <v>449</v>
-      </c>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38" t="s">
-        <v>449</v>
-      </c>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38" t="s">
-        <v>449</v>
-      </c>
-      <c r="L3" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="M3" s="38" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="40"/>
-      <c r="B4" s="58" t="s">
-        <v>452</v>
-      </c>
-      <c r="C4" s="58"/>
-      <c r="L4" s="38" t="s">
-        <v>453</v>
-      </c>
-      <c r="M4" s="38" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="40"/>
-      <c r="B5" s="58" t="s">
-        <v>455</v>
-      </c>
-      <c r="C5" s="58"/>
-      <c r="F5" s="38" t="s">
-        <v>456</v>
-      </c>
-      <c r="G5" s="38"/>
-      <c r="H5" s="38" t="s">
-        <v>456</v>
-      </c>
-      <c r="I5" s="38"/>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="40"/>
-      <c r="B6" s="58" t="s">
-        <v>457</v>
-      </c>
-      <c r="C6" s="58"/>
-      <c r="L6" s="38" t="s">
-        <v>458</v>
-      </c>
-      <c r="M6" s="38" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="40"/>
-      <c r="B7" s="58" t="s">
-        <v>460</v>
-      </c>
-      <c r="C7" s="58"/>
-      <c r="D7" s="38" t="s">
-        <v>461</v>
-      </c>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38" t="s">
-        <v>461</v>
-      </c>
-      <c r="G7" s="38"/>
-      <c r="H7" s="38" t="s">
-        <v>461</v>
-      </c>
-      <c r="I7" s="38"/>
-      <c r="J7" s="38" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="40"/>
-      <c r="B8" s="58" t="s">
-        <v>462</v>
-      </c>
-      <c r="C8" s="58"/>
+        <v>464</v>
+      </c>
+      <c r="E3" s="45" t="s">
+        <v>465</v>
+      </c>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45" t="s">
+        <v>465</v>
+      </c>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45" t="s">
+        <v>465</v>
+      </c>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45" t="s">
+        <v>465</v>
+      </c>
+      <c r="L3" s="38"/>
+      <c r="M3" s="45" t="s">
+        <v>466</v>
+      </c>
+      <c r="N3" s="45" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="29.25">
+      <c r="A4" s="46"/>
+      <c r="B4" s="46" t="s">
+        <v>468</v>
+      </c>
+      <c r="C4" s="46"/>
+      <c r="D4" s="38" t="s">
+        <v>469</v>
+      </c>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="38"/>
+      <c r="K4" s="38"/>
+      <c r="L4" s="38"/>
+      <c r="M4" s="45" t="s">
+        <v>470</v>
+      </c>
+      <c r="N4" s="45" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" s="1" customFormat="1">
+      <c r="A5" s="46"/>
+      <c r="B5" s="46" t="s">
+        <v>472</v>
+      </c>
+      <c r="C5" s="46"/>
+      <c r="D5" s="39" t="s">
+        <v>473</v>
+      </c>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="45" t="s">
+        <v>474</v>
+      </c>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45" t="s">
+        <v>474</v>
+      </c>
+      <c r="J5" s="45"/>
+      <c r="K5" s="38"/>
+      <c r="L5" s="38"/>
+      <c r="M5" s="38"/>
+      <c r="N5" s="38"/>
+    </row>
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="44.25">
+      <c r="A6" s="46"/>
+      <c r="B6" s="46" t="s">
+        <v>475</v>
+      </c>
+      <c r="C6" s="46"/>
+      <c r="D6" s="39" t="s">
+        <v>476</v>
+      </c>
+      <c r="E6" s="38"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="38"/>
+      <c r="I6" s="38"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+      <c r="L6" s="38"/>
+      <c r="M6" s="45" t="s">
+        <v>477</v>
+      </c>
+      <c r="N6" s="45" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" s="1" customFormat="1">
+      <c r="A7" s="46"/>
+      <c r="B7" s="46" t="s">
+        <v>479</v>
+      </c>
+      <c r="C7" s="46"/>
+      <c r="D7" s="39" t="s">
+        <v>480</v>
+      </c>
+      <c r="E7" s="45" t="s">
+        <v>481</v>
+      </c>
+      <c r="F7" s="45"/>
+      <c r="G7" s="45" t="s">
+        <v>481</v>
+      </c>
+      <c r="H7" s="45"/>
+      <c r="I7" s="45" t="s">
+        <v>481</v>
+      </c>
+      <c r="J7" s="45"/>
+      <c r="K7" s="45" t="s">
+        <v>481</v>
+      </c>
+      <c r="L7" s="38"/>
+      <c r="M7" s="38"/>
+      <c r="N7" s="38"/>
+    </row>
+    <row r="8" spans="1:14" s="1" customFormat="1">
+      <c r="A8" s="46"/>
+      <c r="B8" s="46" t="s">
+        <v>482</v>
+      </c>
+      <c r="C8" s="46"/>
       <c r="D8" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="E8" s="45" t="s">
+        <v>484</v>
+      </c>
+      <c r="F8" s="45"/>
+      <c r="G8" s="38" t="s">
+        <v>484</v>
+      </c>
+      <c r="H8" s="38"/>
+      <c r="I8" s="45" t="s">
+        <v>484</v>
+      </c>
+      <c r="J8" s="45"/>
+      <c r="K8" s="45" t="s">
+        <v>484</v>
+      </c>
+      <c r="L8" s="38"/>
+      <c r="M8" s="38"/>
+      <c r="N8" s="38"/>
+    </row>
+    <row r="9" spans="1:14" s="1" customFormat="1" ht="73.5">
+      <c r="A9" s="46"/>
+      <c r="B9" s="46" t="s">
+        <v>485</v>
+      </c>
+      <c r="C9" s="46"/>
+      <c r="D9" s="38" t="s">
+        <v>486</v>
+      </c>
+      <c r="E9" s="45" t="s">
+        <v>487</v>
+      </c>
+      <c r="F9" s="45"/>
+      <c r="G9" s="45" t="s">
+        <v>487</v>
+      </c>
+      <c r="H9" s="45"/>
+      <c r="I9" s="45" t="s">
+        <v>487</v>
+      </c>
+      <c r="J9" s="45"/>
+      <c r="K9" s="45" t="s">
+        <v>487</v>
+      </c>
+      <c r="L9" s="38"/>
+      <c r="M9" s="45" t="s">
+        <v>488</v>
+      </c>
+      <c r="N9" s="45" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" s="1" customFormat="1" ht="29.25">
+      <c r="A10" s="46"/>
+      <c r="B10" s="46" t="s">
+        <v>490</v>
+      </c>
+      <c r="C10" s="46"/>
+      <c r="D10" s="39" t="s">
+        <v>491</v>
+      </c>
+      <c r="E10" s="38"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="45" t="s">
+        <v>492</v>
+      </c>
+      <c r="H10" s="45" t="s">
+        <v>493</v>
+      </c>
+      <c r="I10" s="45" t="s">
+        <v>494</v>
+      </c>
+      <c r="J10" s="45"/>
+      <c r="K10" s="38"/>
+      <c r="L10" s="38"/>
+      <c r="M10" s="38"/>
+      <c r="N10" s="38"/>
+    </row>
+    <row r="11" spans="1:14" s="1" customFormat="1" ht="29.25">
+      <c r="A11" s="46"/>
+      <c r="B11" s="46" t="s">
+        <v>495</v>
+      </c>
+      <c r="C11" s="46"/>
+      <c r="D11" s="39" t="s">
+        <v>496</v>
+      </c>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38" t="s">
+        <v>497</v>
+      </c>
+      <c r="H11" s="45" t="s">
+        <v>498</v>
+      </c>
+      <c r="I11" s="45" t="s">
+        <v>499</v>
+      </c>
+      <c r="J11" s="45" t="s">
+        <v>500</v>
+      </c>
+      <c r="K11" s="38"/>
+      <c r="L11" s="38"/>
+      <c r="M11" s="38"/>
+      <c r="N11" s="38"/>
+    </row>
+    <row r="12" spans="1:14" s="1" customFormat="1">
+      <c r="A12" s="46" t="s">
+        <v>501</v>
+      </c>
+      <c r="B12" s="46" t="s">
+        <v>502</v>
+      </c>
+      <c r="C12" s="46"/>
+      <c r="D12" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="47" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" s="47"/>
+      <c r="G12" s="47" t="s">
+        <v>48</v>
+      </c>
+      <c r="H12" s="47"/>
+      <c r="I12" s="47" t="s">
+        <v>48</v>
+      </c>
+      <c r="J12" s="47"/>
+      <c r="K12" s="47" t="s">
+        <v>48</v>
+      </c>
+      <c r="L12" s="47"/>
+      <c r="M12" s="46"/>
+      <c r="N12" s="46"/>
+    </row>
+    <row r="13" spans="1:14" s="1" customFormat="1">
+      <c r="A13" s="46"/>
+      <c r="B13" s="46" t="s">
+        <v>503</v>
+      </c>
+      <c r="C13" s="46"/>
+      <c r="D13" s="38" t="s">
+        <v>504</v>
+      </c>
+      <c r="E13" s="48" t="s">
+        <v>505</v>
+      </c>
+      <c r="F13" s="46"/>
+      <c r="G13" s="48" t="s">
+        <v>506</v>
+      </c>
+      <c r="H13" s="46"/>
+      <c r="I13" s="48" t="s">
+        <v>507</v>
+      </c>
+      <c r="J13" s="46"/>
+      <c r="K13" s="46"/>
+      <c r="L13" s="46"/>
+      <c r="M13" s="47" t="s">
+        <v>508</v>
+      </c>
+      <c r="N13" s="46"/>
+    </row>
+    <row r="14" spans="1:14" s="1" customFormat="1" ht="30.75">
+      <c r="A14" s="46"/>
+      <c r="B14" s="46" t="s">
+        <v>509</v>
+      </c>
+      <c r="C14" s="46"/>
+      <c r="D14" s="39" t="s">
+        <v>510</v>
+      </c>
+      <c r="E14" s="45" t="s">
+        <v>511</v>
+      </c>
+      <c r="F14" s="45" t="s">
+        <v>512</v>
+      </c>
+      <c r="G14" s="45" t="s">
+        <v>511</v>
+      </c>
+      <c r="H14" s="38" t="s">
+        <v>513</v>
+      </c>
+      <c r="I14" s="45" t="s">
+        <v>514</v>
+      </c>
+      <c r="J14" s="45" t="s">
+        <v>513</v>
+      </c>
+      <c r="K14" s="45" t="s">
+        <v>514</v>
+      </c>
+      <c r="L14" s="45" t="s">
+        <v>515</v>
+      </c>
+      <c r="M14" s="38"/>
+      <c r="N14" s="38"/>
+    </row>
+    <row r="15" spans="1:14" s="1" customFormat="1" ht="44.25">
+      <c r="A15" s="46"/>
+      <c r="B15" s="46" t="s">
+        <v>516</v>
+      </c>
+      <c r="C15" s="46"/>
+      <c r="D15" s="39" t="s">
+        <v>517</v>
+      </c>
+      <c r="E15" s="45" t="s">
+        <v>518</v>
+      </c>
+      <c r="F15" s="45" t="s">
+        <v>519</v>
+      </c>
+      <c r="G15" s="38" t="s">
+        <v>518</v>
+      </c>
+      <c r="H15" s="45" t="s">
+        <v>520</v>
+      </c>
+      <c r="I15" s="45" t="s">
+        <v>518</v>
+      </c>
+      <c r="J15" s="45" t="s">
+        <v>520</v>
+      </c>
+      <c r="K15" s="45" t="s">
+        <v>518</v>
+      </c>
+      <c r="L15" s="45" t="s">
+        <v>519</v>
+      </c>
+      <c r="M15" s="45" t="s">
+        <v>521</v>
+      </c>
+      <c r="N15" s="45" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" s="1" customFormat="1" ht="30.75">
+      <c r="A16" s="46"/>
+      <c r="B16" s="46" t="s">
+        <v>522</v>
+      </c>
+      <c r="C16" s="46"/>
+      <c r="D16" s="38" t="s">
+        <v>523</v>
+      </c>
+      <c r="E16" s="45" t="s">
+        <v>524</v>
+      </c>
+      <c r="F16" s="45" t="s">
+        <v>525</v>
+      </c>
+      <c r="G16" s="45" t="s">
+        <v>524</v>
+      </c>
+      <c r="H16" s="45" t="s">
+        <v>526</v>
+      </c>
+      <c r="I16" s="45" t="s">
+        <v>524</v>
+      </c>
+      <c r="J16" s="38"/>
+      <c r="K16" s="45" t="s">
+        <v>524</v>
+      </c>
+      <c r="L16" s="38" t="s">
+        <v>525</v>
+      </c>
+      <c r="M16" s="45" t="s">
+        <v>527</v>
+      </c>
+      <c r="N16" s="45" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" s="1" customFormat="1">
+      <c r="A17" s="46"/>
+      <c r="B17" s="46" t="s">
+        <v>529</v>
+      </c>
+      <c r="C17" s="46"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="38"/>
+      <c r="I17" s="38"/>
+      <c r="J17" s="38"/>
+      <c r="K17" s="38"/>
+      <c r="L17" s="38"/>
+      <c r="M17" s="38"/>
+      <c r="N17" s="38"/>
+    </row>
+    <row r="18" spans="1:14" s="1" customFormat="1" ht="336">
+      <c r="A18" s="46" t="s">
+        <v>530</v>
+      </c>
+      <c r="B18" s="46"/>
+      <c r="C18" s="46"/>
+      <c r="D18" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="E18" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="F18" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="G18" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="H18" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="I18" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="J18" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="K18" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="L18" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="M18" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="N18" s="38" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" s="1" customFormat="1">
+      <c r="A19" s="46" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" s="46" t="s">
+        <v>85</v>
+      </c>
+      <c r="C19" s="38" t="s">
         <v>463</v>
       </c>
-      <c r="E8" s="38"/>
-      <c r="F8" t="s">
+      <c r="D19" s="38" t="s">
+        <v>464</v>
+      </c>
+      <c r="E19" s="47"/>
+      <c r="F19" s="47"/>
+      <c r="G19" s="46"/>
+      <c r="H19" s="46"/>
+      <c r="I19" s="46"/>
+      <c r="J19" s="46"/>
+      <c r="K19" s="46"/>
+      <c r="L19" s="46"/>
+      <c r="M19" s="46"/>
+      <c r="N19" s="46"/>
+    </row>
+    <row r="20" spans="1:14" s="1" customFormat="1">
+      <c r="A20" s="46"/>
+      <c r="B20" s="46"/>
+      <c r="C20" s="38" t="s">
+        <v>468</v>
+      </c>
+      <c r="D20" s="38" t="s">
+        <v>469</v>
+      </c>
+      <c r="E20" s="47"/>
+      <c r="F20" s="47"/>
+      <c r="G20" s="46"/>
+      <c r="H20" s="46"/>
+      <c r="I20" s="46"/>
+      <c r="J20" s="46"/>
+      <c r="K20" s="46"/>
+      <c r="L20" s="46"/>
+      <c r="M20" s="46"/>
+      <c r="N20" s="46"/>
+    </row>
+    <row r="21" spans="1:14" s="1" customFormat="1">
+      <c r="A21" s="46"/>
+      <c r="B21" s="46"/>
+      <c r="C21" s="38" t="s">
+        <v>472</v>
+      </c>
+      <c r="D21" s="39" t="s">
+        <v>473</v>
+      </c>
+      <c r="E21" s="47"/>
+      <c r="F21" s="47"/>
+      <c r="G21" s="46"/>
+      <c r="H21" s="46"/>
+      <c r="I21" s="46"/>
+      <c r="J21" s="46"/>
+      <c r="K21" s="46"/>
+      <c r="L21" s="46"/>
+      <c r="M21" s="46"/>
+      <c r="N21" s="46"/>
+    </row>
+    <row r="22" spans="1:14" s="1" customFormat="1">
+      <c r="A22" s="46"/>
+      <c r="B22" s="46"/>
+      <c r="C22" s="38" t="s">
+        <v>475</v>
+      </c>
+      <c r="D22" s="39" t="s">
+        <v>476</v>
+      </c>
+      <c r="E22" s="47"/>
+      <c r="F22" s="47"/>
+      <c r="G22" s="46"/>
+      <c r="H22" s="46"/>
+      <c r="I22" s="46"/>
+      <c r="J22" s="46"/>
+      <c r="K22" s="46"/>
+      <c r="L22" s="46"/>
+      <c r="M22" s="46"/>
+      <c r="N22" s="46"/>
+    </row>
+    <row r="23" spans="1:14" s="1" customFormat="1">
+      <c r="A23" s="46"/>
+      <c r="B23" s="46"/>
+      <c r="C23" s="38" t="s">
+        <v>479</v>
+      </c>
+      <c r="D23" s="39" t="s">
+        <v>480</v>
+      </c>
+      <c r="E23" s="47"/>
+      <c r="F23" s="47"/>
+      <c r="G23" s="46"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="46"/>
+      <c r="J23" s="46"/>
+      <c r="K23" s="46"/>
+      <c r="L23" s="46"/>
+      <c r="M23" s="46"/>
+      <c r="N23" s="46"/>
+    </row>
+    <row r="24" spans="1:14" s="1" customFormat="1">
+      <c r="A24" s="46"/>
+      <c r="B24" s="46"/>
+      <c r="C24" s="38" t="s">
+        <v>482</v>
+      </c>
+      <c r="D24" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="E24" s="47"/>
+      <c r="F24" s="47"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="46"/>
+      <c r="I24" s="46"/>
+      <c r="J24" s="46"/>
+      <c r="K24" s="46"/>
+      <c r="L24" s="46"/>
+      <c r="M24" s="46"/>
+      <c r="N24" s="46"/>
+    </row>
+    <row r="25" spans="1:14" s="1" customFormat="1">
+      <c r="A25" s="46"/>
+      <c r="B25" s="46"/>
+      <c r="C25" s="38" t="s">
+        <v>485</v>
+      </c>
+      <c r="D25" s="38" t="s">
+        <v>486</v>
+      </c>
+      <c r="E25" s="47"/>
+      <c r="F25" s="47"/>
+      <c r="G25" s="46"/>
+      <c r="H25" s="46"/>
+      <c r="I25" s="46"/>
+      <c r="J25" s="46"/>
+      <c r="K25" s="46"/>
+      <c r="L25" s="46"/>
+      <c r="M25" s="46"/>
+      <c r="N25" s="46"/>
+    </row>
+    <row r="26" spans="1:14" s="1" customFormat="1">
+      <c r="A26" s="46"/>
+      <c r="B26" s="46"/>
+      <c r="C26" s="38" t="s">
+        <v>490</v>
+      </c>
+      <c r="D26" s="39" t="s">
+        <v>491</v>
+      </c>
+      <c r="E26" s="47"/>
+      <c r="F26" s="47"/>
+      <c r="G26" s="46"/>
+      <c r="H26" s="46"/>
+      <c r="I26" s="46"/>
+      <c r="J26" s="46"/>
+      <c r="K26" s="46"/>
+      <c r="L26" s="46"/>
+      <c r="M26" s="46"/>
+      <c r="N26" s="46"/>
+    </row>
+    <row r="27" spans="1:14" s="1" customFormat="1">
+      <c r="A27" s="46"/>
+      <c r="B27" s="46"/>
+      <c r="C27" s="38" t="s">
+        <v>495</v>
+      </c>
+      <c r="D27" s="39" t="s">
+        <v>496</v>
+      </c>
+      <c r="E27" s="47"/>
+      <c r="F27" s="47"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="46"/>
+      <c r="I27" s="46"/>
+      <c r="J27" s="46"/>
+      <c r="K27" s="46"/>
+      <c r="L27" s="46"/>
+      <c r="M27" s="46"/>
+      <c r="N27" s="46"/>
+    </row>
+    <row r="28" spans="1:14" s="1" customFormat="1" ht="76.5">
+      <c r="A28" s="46"/>
+      <c r="B28" s="46" t="s">
+        <v>530</v>
+      </c>
+      <c r="C28" s="46"/>
+      <c r="D28" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="E28" s="38" t="s">
+        <v>531</v>
+      </c>
+      <c r="F28" s="38" t="s">
+        <v>531</v>
+      </c>
+      <c r="G28" s="38" t="s">
+        <v>531</v>
+      </c>
+      <c r="H28" s="38" t="s">
+        <v>531</v>
+      </c>
+      <c r="I28" s="38" t="s">
+        <v>531</v>
+      </c>
+      <c r="J28" s="38" t="s">
+        <v>531</v>
+      </c>
+      <c r="K28" s="38" t="s">
+        <v>531</v>
+      </c>
+      <c r="L28" s="38" t="s">
+        <v>531</v>
+      </c>
+      <c r="M28" s="38" t="s">
+        <v>531</v>
+      </c>
+      <c r="N28" s="38" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" s="1" customFormat="1" ht="30.75">
+      <c r="A29" s="46"/>
+      <c r="B29" s="46" t="s">
+        <v>532</v>
+      </c>
+      <c r="C29" s="46"/>
+      <c r="D29" s="38" t="s">
+        <v>533</v>
+      </c>
+      <c r="E29" s="38" t="s">
+        <v>533</v>
+      </c>
+      <c r="F29" s="38" t="s">
+        <v>533</v>
+      </c>
+      <c r="G29" s="38" t="s">
+        <v>533</v>
+      </c>
+      <c r="H29" s="38" t="s">
+        <v>533</v>
+      </c>
+      <c r="I29" s="38" t="s">
+        <v>533</v>
+      </c>
+      <c r="J29" s="38" t="s">
+        <v>533</v>
+      </c>
+      <c r="K29" s="38" t="s">
+        <v>533</v>
+      </c>
+      <c r="L29" s="38" t="s">
+        <v>533</v>
+      </c>
+      <c r="M29" s="38" t="s">
+        <v>533</v>
+      </c>
+      <c r="N29" s="38" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" s="1" customFormat="1" ht="30.75">
+      <c r="A30" s="46"/>
+      <c r="B30" s="46" t="s">
+        <v>534</v>
+      </c>
+      <c r="C30" s="46"/>
+      <c r="D30" s="38" t="s">
+        <v>533</v>
+      </c>
+      <c r="E30" s="38" t="s">
+        <v>533</v>
+      </c>
+      <c r="F30" s="38" t="s">
+        <v>533</v>
+      </c>
+      <c r="G30" s="38" t="s">
+        <v>533</v>
+      </c>
+      <c r="H30" s="38" t="s">
+        <v>533</v>
+      </c>
+      <c r="I30" s="38" t="s">
+        <v>533</v>
+      </c>
+      <c r="J30" s="38" t="s">
+        <v>533</v>
+      </c>
+      <c r="K30" s="38" t="s">
+        <v>533</v>
+      </c>
+      <c r="L30" s="38" t="s">
+        <v>533</v>
+      </c>
+      <c r="M30" s="38" t="s">
+        <v>533</v>
+      </c>
+      <c r="N30" s="38" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" s="1" customFormat="1" ht="244.5">
+      <c r="A31" s="46"/>
+      <c r="B31" s="46" t="s">
+        <v>535</v>
+      </c>
+      <c r="C31" s="46"/>
+      <c r="D31" s="38" t="s">
+        <v>536</v>
+      </c>
+      <c r="E31" s="38" t="s">
+        <v>537</v>
+      </c>
+      <c r="F31" s="38" t="s">
+        <v>538</v>
+      </c>
+      <c r="G31" s="38" t="s">
+        <v>538</v>
+      </c>
+      <c r="H31" s="38" t="s">
+        <v>538</v>
+      </c>
+      <c r="I31" s="38" t="s">
+        <v>538</v>
+      </c>
+      <c r="J31" s="38" t="s">
+        <v>538</v>
+      </c>
+      <c r="K31" s="38" t="s">
+        <v>538</v>
+      </c>
+      <c r="L31" s="38" t="s">
+        <v>538</v>
+      </c>
+      <c r="M31" s="38" t="s">
+        <v>538</v>
+      </c>
+      <c r="N31" s="38" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" s="1" customFormat="1">
+      <c r="A32" s="46" t="s">
+        <v>65</v>
+      </c>
+      <c r="B32" s="46" t="s">
+        <v>85</v>
+      </c>
+      <c r="C32" s="38" t="s">
         <v>463</v>
       </c>
-      <c r="H8" s="38" t="s">
-        <v>463</v>
-      </c>
-      <c r="I8" s="38"/>
-      <c r="J8" s="38" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="40"/>
-      <c r="B9" s="40" t="s">
+      <c r="D32" s="38" t="s">
         <v>464</v>
       </c>
-      <c r="C9" s="40"/>
-      <c r="D9" s="38" t="s">
-        <v>465</v>
-      </c>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38" t="s">
-        <v>465</v>
-      </c>
-      <c r="G9" s="38"/>
-      <c r="H9" s="38" t="s">
-        <v>465</v>
-      </c>
-      <c r="I9" s="38"/>
-      <c r="J9" s="38" t="s">
-        <v>465</v>
-      </c>
-      <c r="L9" s="38" t="s">
-        <v>466</v>
-      </c>
-      <c r="M9" s="38" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="40"/>
-      <c r="B10" s="58" t="s">
+      <c r="E32" s="46"/>
+      <c r="F32" s="46"/>
+      <c r="G32" s="46"/>
+      <c r="H32" s="46"/>
+      <c r="I32" s="46"/>
+      <c r="J32" s="46"/>
+      <c r="K32" s="46"/>
+      <c r="L32" s="46"/>
+      <c r="M32" s="46"/>
+      <c r="N32" s="46"/>
+    </row>
+    <row r="33" spans="1:14" s="1" customFormat="1">
+      <c r="A33" s="46"/>
+      <c r="B33" s="46"/>
+      <c r="C33" s="38" t="s">
         <v>468</v>
       </c>
-      <c r="C10" s="58"/>
-      <c r="F10" s="38" t="s">
+      <c r="D33" s="38" t="s">
         <v>469</v>
       </c>
-      <c r="G10" s="38" t="s">
-        <v>470</v>
-      </c>
-      <c r="H10" s="38" t="s">
-        <v>471</v>
-      </c>
-      <c r="I10" s="38"/>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="40"/>
-      <c r="B11" s="58" t="s">
+      <c r="E33" s="46"/>
+      <c r="F33" s="46"/>
+      <c r="G33" s="46"/>
+      <c r="H33" s="46"/>
+      <c r="I33" s="46"/>
+      <c r="J33" s="46"/>
+      <c r="K33" s="46"/>
+      <c r="L33" s="46"/>
+      <c r="M33" s="46"/>
+      <c r="N33" s="46"/>
+    </row>
+    <row r="34" spans="1:14" s="1" customFormat="1">
+      <c r="A34" s="46"/>
+      <c r="B34" s="46"/>
+      <c r="C34" s="38" t="s">
         <v>472</v>
       </c>
-      <c r="C11" s="58"/>
-      <c r="F11" t="s">
+      <c r="D34" s="39" t="s">
         <v>473</v>
       </c>
-      <c r="G11" s="38" t="s">
-        <v>474</v>
-      </c>
-      <c r="H11" s="38" t="s">
+      <c r="E34" s="46"/>
+      <c r="F34" s="46"/>
+      <c r="G34" s="46"/>
+      <c r="H34" s="46"/>
+      <c r="I34" s="46"/>
+      <c r="J34" s="46"/>
+      <c r="K34" s="46"/>
+      <c r="L34" s="46"/>
+      <c r="M34" s="46"/>
+      <c r="N34" s="46"/>
+    </row>
+    <row r="35" spans="1:14" s="1" customFormat="1">
+      <c r="A35" s="46"/>
+      <c r="B35" s="46"/>
+      <c r="C35" s="38" t="s">
         <v>475</v>
       </c>
-      <c r="I11" s="38" t="s">
+      <c r="D35" s="39" t="s">
         <v>476</v>
       </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="40" t="s">
-        <v>477</v>
-      </c>
-      <c r="B12" s="58" t="s">
-        <v>478</v>
-      </c>
-      <c r="C12" s="58"/>
-      <c r="D12" s="59" t="s">
-        <v>40</v>
-      </c>
-      <c r="E12" s="59"/>
-      <c r="F12" s="59" t="s">
-        <v>40</v>
-      </c>
-      <c r="G12" s="59"/>
-      <c r="H12" s="59" t="s">
-        <v>40</v>
-      </c>
-      <c r="I12" s="59"/>
-      <c r="J12" s="59" t="s">
-        <v>40</v>
-      </c>
-      <c r="K12" s="59"/>
-      <c r="L12" s="58"/>
-      <c r="M12" s="58"/>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="40"/>
-      <c r="B13" s="58" t="s">
+      <c r="E35" s="46"/>
+      <c r="F35" s="46"/>
+      <c r="G35" s="46"/>
+      <c r="H35" s="46"/>
+      <c r="I35" s="46"/>
+      <c r="J35" s="46"/>
+      <c r="K35" s="46"/>
+      <c r="L35" s="46"/>
+      <c r="M35" s="46"/>
+      <c r="N35" s="46"/>
+    </row>
+    <row r="36" spans="1:14" s="1" customFormat="1">
+      <c r="A36" s="46"/>
+      <c r="B36" s="46"/>
+      <c r="C36" s="38" t="s">
         <v>479</v>
       </c>
-      <c r="C13" s="58"/>
-      <c r="D13" s="43" t="s">
+      <c r="D36" s="39" t="s">
         <v>480</v>
       </c>
-      <c r="E13" s="43"/>
-      <c r="F13" s="60" t="s">
-        <v>481</v>
-      </c>
-      <c r="G13" s="58"/>
-      <c r="H13" s="60" t="s">
+      <c r="E36" s="46"/>
+      <c r="F36" s="46"/>
+      <c r="G36" s="46"/>
+      <c r="H36" s="46"/>
+      <c r="I36" s="46"/>
+      <c r="J36" s="46"/>
+      <c r="K36" s="46"/>
+      <c r="L36" s="46"/>
+      <c r="M36" s="46"/>
+      <c r="N36" s="46"/>
+    </row>
+    <row r="37" spans="1:14" s="1" customFormat="1">
+      <c r="A37" s="46"/>
+      <c r="B37" s="46"/>
+      <c r="C37" s="38" t="s">
         <v>482</v>
       </c>
-      <c r="I13" s="58"/>
-      <c r="J13" s="60" t="s">
+      <c r="D37" s="38" t="s">
         <v>483</v>
       </c>
-      <c r="K13" s="58"/>
-      <c r="L13" s="59" t="s">
-        <v>484</v>
-      </c>
-      <c r="M13" s="58"/>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="40"/>
-      <c r="B14" s="58" t="s">
+      <c r="E37" s="46"/>
+      <c r="F37" s="46"/>
+      <c r="G37" s="46"/>
+      <c r="H37" s="46"/>
+      <c r="I37" s="46"/>
+      <c r="J37" s="46"/>
+      <c r="K37" s="46"/>
+      <c r="L37" s="46"/>
+      <c r="M37" s="46"/>
+      <c r="N37" s="46"/>
+    </row>
+    <row r="38" spans="1:14" s="1" customFormat="1">
+      <c r="A38" s="46"/>
+      <c r="B38" s="46"/>
+      <c r="C38" s="38" t="s">
         <v>485</v>
       </c>
-      <c r="C14" s="58"/>
-      <c r="D14" s="38" t="s">
+      <c r="D38" s="38" t="s">
         <v>486</v>
       </c>
-      <c r="E14" s="38" t="s">
-        <v>487</v>
-      </c>
-      <c r="F14" s="38" t="s">
-        <v>486</v>
-      </c>
-      <c r="G14" t="s">
-        <v>488</v>
-      </c>
-      <c r="H14" s="38" t="s">
-        <v>489</v>
-      </c>
-      <c r="I14" s="38" t="s">
-        <v>488</v>
-      </c>
-      <c r="J14" s="38" t="s">
-        <v>489</v>
-      </c>
-      <c r="K14" s="38" t="s">
+      <c r="E38" s="46"/>
+      <c r="F38" s="46"/>
+      <c r="G38" s="46"/>
+      <c r="H38" s="46"/>
+      <c r="I38" s="46"/>
+      <c r="J38" s="46"/>
+      <c r="K38" s="46"/>
+      <c r="L38" s="46"/>
+      <c r="M38" s="46"/>
+      <c r="N38" s="46"/>
+    </row>
+    <row r="39" spans="1:14" s="1" customFormat="1">
+      <c r="A39" s="46"/>
+      <c r="B39" s="46"/>
+      <c r="C39" s="38" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" s="40"/>
-      <c r="B15" s="58" t="s">
+      <c r="D39" s="39" t="s">
         <v>491</v>
       </c>
-      <c r="C15" s="58"/>
-      <c r="D15" s="38" t="s">
-        <v>492</v>
-      </c>
-      <c r="E15" s="38" t="s">
-        <v>493</v>
-      </c>
-      <c r="F15" t="s">
-        <v>492</v>
-      </c>
-      <c r="G15" s="38" t="s">
-        <v>494</v>
-      </c>
-      <c r="H15" s="38" t="s">
-        <v>492</v>
-      </c>
-      <c r="I15" s="38" t="s">
-        <v>494</v>
-      </c>
-      <c r="J15" s="38" t="s">
-        <v>492</v>
-      </c>
-      <c r="K15" s="38" t="s">
-        <v>493</v>
-      </c>
-      <c r="L15" s="38" t="s">
+      <c r="E39" s="46"/>
+      <c r="F39" s="46"/>
+      <c r="G39" s="46"/>
+      <c r="H39" s="46"/>
+      <c r="I39" s="46"/>
+      <c r="J39" s="46"/>
+      <c r="K39" s="46"/>
+      <c r="L39" s="46"/>
+      <c r="M39" s="46"/>
+      <c r="N39" s="46"/>
+    </row>
+    <row r="40" spans="1:14" s="1" customFormat="1">
+      <c r="A40" s="46"/>
+      <c r="B40" s="46"/>
+      <c r="C40" s="38" t="s">
         <v>495</v>
       </c>
-      <c r="M15" s="38" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16" s="40"/>
-      <c r="B16" s="58" t="s">
+      <c r="D40" s="39" t="s">
         <v>496</v>
       </c>
-      <c r="C16" s="58"/>
-      <c r="D16" s="38" t="s">
-        <v>497</v>
-      </c>
-      <c r="E16" s="38" t="s">
-        <v>498</v>
-      </c>
-      <c r="F16" s="38" t="s">
-        <v>497</v>
-      </c>
-      <c r="G16" s="38" t="s">
-        <v>499</v>
-      </c>
-      <c r="H16" s="38" t="s">
-        <v>497</v>
-      </c>
-      <c r="J16" s="38" t="s">
-        <v>497</v>
-      </c>
-      <c r="K16" t="s">
-        <v>498</v>
-      </c>
-      <c r="L16" s="38" t="s">
-        <v>500</v>
-      </c>
-      <c r="M16" s="38" t="s">
+      <c r="E40" s="46"/>
+      <c r="F40" s="46"/>
+      <c r="G40" s="46"/>
+      <c r="H40" s="46"/>
+      <c r="I40" s="46"/>
+      <c r="J40" s="46"/>
+      <c r="K40" s="46"/>
+      <c r="L40" s="46"/>
+      <c r="M40" s="46"/>
+      <c r="N40" s="46"/>
+    </row>
+    <row r="41" spans="1:14" s="1" customFormat="1">
+      <c r="A41" s="46"/>
+      <c r="B41" s="46" t="s">
         <v>501</v>
       </c>
-    </row>
-    <row r="17" spans="1:13">
-      <c r="A17" s="40"/>
-      <c r="B17" s="58" t="s">
+      <c r="C41" s="38" t="s">
         <v>502</v>
       </c>
-      <c r="C17" s="58"/>
-    </row>
-    <row r="18" spans="1:13" ht="106.5">
-      <c r="A18" s="40" t="s">
+      <c r="D41" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="E41" s="38"/>
+      <c r="F41" s="38"/>
+      <c r="G41" s="38"/>
+      <c r="H41" s="38"/>
+      <c r="I41" s="38"/>
+      <c r="J41" s="38"/>
+      <c r="K41" s="38"/>
+      <c r="L41" s="38"/>
+      <c r="M41" s="38"/>
+      <c r="N41" s="38"/>
+    </row>
+    <row r="42" spans="1:14" s="1" customFormat="1">
+      <c r="A42" s="46"/>
+      <c r="B42" s="46"/>
+      <c r="C42" s="38" t="s">
         <v>503</v>
       </c>
-      <c r="B18" s="40"/>
-      <c r="C18" s="40"/>
-      <c r="D18" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="M18" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
-      <c r="A19" s="40" t="s">
-        <v>52</v>
-      </c>
-      <c r="B19" s="40" t="s">
-        <v>71</v>
-      </c>
-      <c r="C19" t="s">
-        <v>448</v>
-      </c>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="39"/>
-      <c r="H19" s="39"/>
-      <c r="I19" s="39"/>
-      <c r="J19" s="39"/>
-      <c r="K19" s="39"/>
-      <c r="L19" s="39"/>
-      <c r="M19" s="39"/>
-    </row>
-    <row r="20" spans="1:13">
-      <c r="A20" s="40"/>
-      <c r="B20" s="40"/>
-      <c r="C20" t="s">
-        <v>452</v>
-      </c>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="39"/>
-      <c r="G20" s="39"/>
-      <c r="H20" s="39"/>
-      <c r="I20" s="39"/>
-      <c r="J20" s="39"/>
-      <c r="K20" s="39"/>
-      <c r="L20" s="39"/>
-      <c r="M20" s="39"/>
-    </row>
-    <row r="21" spans="1:13">
-      <c r="A21" s="40"/>
-      <c r="B21" s="40"/>
-      <c r="C21" t="s">
-        <v>455</v>
-      </c>
-      <c r="D21" s="42"/>
-      <c r="E21" s="42"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="39"/>
-      <c r="H21" s="39"/>
-      <c r="I21" s="39"/>
-      <c r="J21" s="39"/>
-      <c r="K21" s="39"/>
-      <c r="L21" s="39"/>
-      <c r="M21" s="39"/>
-    </row>
-    <row r="22" spans="1:13">
-      <c r="A22" s="40"/>
-      <c r="B22" s="40"/>
-      <c r="C22" t="s">
-        <v>457</v>
-      </c>
-      <c r="D22" s="42"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="39"/>
-      <c r="G22" s="39"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="39"/>
-      <c r="J22" s="39"/>
-      <c r="K22" s="39"/>
-      <c r="L22" s="39"/>
-      <c r="M22" s="39"/>
-    </row>
-    <row r="23" spans="1:13">
-      <c r="A23" s="40"/>
-      <c r="B23" s="40"/>
-      <c r="C23" t="s">
-        <v>460</v>
-      </c>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="39"/>
-      <c r="G23" s="39"/>
-      <c r="H23" s="39"/>
-      <c r="I23" s="39"/>
-      <c r="J23" s="39"/>
-      <c r="K23" s="39"/>
-      <c r="L23" s="39"/>
-      <c r="M23" s="39"/>
-    </row>
-    <row r="24" spans="1:13">
-      <c r="A24" s="40"/>
-      <c r="B24" s="40"/>
-      <c r="C24" t="s">
-        <v>462</v>
-      </c>
-      <c r="D24" s="42"/>
-      <c r="E24" s="42"/>
-      <c r="F24" s="39"/>
-      <c r="G24" s="39"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="39"/>
-      <c r="J24" s="39"/>
-      <c r="K24" s="39"/>
-      <c r="L24" s="39"/>
-      <c r="M24" s="39"/>
-    </row>
-    <row r="25" spans="1:13">
-      <c r="A25" s="40"/>
-      <c r="B25" s="40"/>
-      <c r="C25" t="s">
-        <v>468</v>
-      </c>
-      <c r="D25" s="42"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="39"/>
-      <c r="G25" s="39"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="39"/>
-      <c r="J25" s="39"/>
-      <c r="K25" s="39"/>
-      <c r="L25" s="39"/>
-      <c r="M25" s="39"/>
-    </row>
-    <row r="26" spans="1:13">
-      <c r="A26" s="40"/>
-      <c r="B26" s="40"/>
-      <c r="C26" t="s">
-        <v>472</v>
-      </c>
-      <c r="D26" s="42"/>
-      <c r="E26" s="42"/>
-      <c r="F26" s="39"/>
-      <c r="G26" s="39"/>
-      <c r="H26" s="39"/>
-      <c r="I26" s="39"/>
-      <c r="J26" s="39"/>
-      <c r="K26" s="39"/>
-      <c r="L26" s="39"/>
-      <c r="M26" s="39"/>
-    </row>
-    <row r="27" spans="1:13" ht="30.75">
-      <c r="A27" s="40"/>
-      <c r="B27" s="40" t="s">
-        <v>503</v>
-      </c>
-      <c r="C27" s="40"/>
-      <c r="D27" s="1" t="s">
+      <c r="D42" s="38" t="s">
         <v>504</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="L27" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="M27" s="1" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13">
-      <c r="A28" s="40"/>
-      <c r="B28" s="58" t="s">
-        <v>505</v>
-      </c>
-      <c r="C28" s="58"/>
-      <c r="D28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E28" t="s">
-        <v>506</v>
-      </c>
-      <c r="F28" t="s">
-        <v>506</v>
-      </c>
-      <c r="G28" t="s">
-        <v>506</v>
-      </c>
-      <c r="H28" t="s">
-        <v>506</v>
-      </c>
-      <c r="I28" t="s">
-        <v>506</v>
-      </c>
-      <c r="J28" t="s">
-        <v>506</v>
-      </c>
-      <c r="K28" t="s">
-        <v>506</v>
-      </c>
-      <c r="L28" t="s">
-        <v>506</v>
-      </c>
-      <c r="M28" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13">
-      <c r="A29" s="40"/>
-      <c r="B29" s="58" t="s">
-        <v>507</v>
-      </c>
-      <c r="C29" s="58"/>
-      <c r="D29" t="s">
-        <v>506</v>
-      </c>
-      <c r="E29" t="s">
-        <v>506</v>
-      </c>
-      <c r="F29" t="s">
-        <v>506</v>
-      </c>
-      <c r="G29" t="s">
-        <v>506</v>
-      </c>
-      <c r="H29" t="s">
-        <v>506</v>
-      </c>
-      <c r="I29" t="s">
-        <v>506</v>
-      </c>
-      <c r="J29" t="s">
-        <v>506</v>
-      </c>
-      <c r="K29" t="s">
-        <v>506</v>
-      </c>
-      <c r="L29" t="s">
-        <v>506</v>
-      </c>
-      <c r="M29" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="76.5">
-      <c r="A30" s="40"/>
-      <c r="B30" s="58" t="s">
-        <v>508</v>
-      </c>
-      <c r="C30" s="58"/>
-      <c r="D30" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="L30" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="M30" s="1" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13">
-      <c r="A31" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="B31" s="40" t="s">
-        <v>71</v>
-      </c>
-      <c r="C31" t="s">
-        <v>448</v>
-      </c>
-      <c r="D31" s="39"/>
-      <c r="E31" s="39"/>
-      <c r="F31" s="39"/>
-      <c r="G31" s="39"/>
-      <c r="H31" s="39"/>
-      <c r="I31" s="39"/>
-      <c r="J31" s="39"/>
-      <c r="K31" s="39"/>
-      <c r="L31" s="39"/>
-      <c r="M31" s="39"/>
-    </row>
-    <row r="32" spans="1:13">
-      <c r="A32" s="40"/>
-      <c r="B32" s="40"/>
-      <c r="C32" t="s">
-        <v>452</v>
-      </c>
-      <c r="D32" s="39"/>
-      <c r="E32" s="39"/>
-      <c r="F32" s="39"/>
-      <c r="G32" s="39"/>
-      <c r="H32" s="39"/>
-      <c r="I32" s="39"/>
-      <c r="J32" s="39"/>
-      <c r="K32" s="39"/>
-      <c r="L32" s="39"/>
-      <c r="M32" s="39"/>
-    </row>
-    <row r="33" spans="1:13">
-      <c r="A33" s="40"/>
-      <c r="B33" s="40"/>
-      <c r="C33" t="s">
-        <v>455</v>
-      </c>
-      <c r="D33" s="39"/>
-      <c r="E33" s="39"/>
-      <c r="F33" s="39"/>
-      <c r="G33" s="39"/>
-      <c r="H33" s="39"/>
-      <c r="I33" s="39"/>
-      <c r="J33" s="39"/>
-      <c r="K33" s="39"/>
-      <c r="L33" s="39"/>
-      <c r="M33" s="39"/>
-    </row>
-    <row r="34" spans="1:13">
-      <c r="A34" s="40"/>
-      <c r="B34" s="40"/>
-      <c r="C34" t="s">
-        <v>457</v>
-      </c>
-      <c r="D34" s="39"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="39"/>
-      <c r="G34" s="39"/>
-      <c r="H34" s="39"/>
-      <c r="I34" s="39"/>
-      <c r="J34" s="39"/>
-      <c r="K34" s="39"/>
-      <c r="L34" s="39"/>
-      <c r="M34" s="39"/>
-    </row>
-    <row r="35" spans="1:13">
-      <c r="A35" s="40"/>
-      <c r="B35" s="40"/>
-      <c r="C35" t="s">
-        <v>460</v>
-      </c>
-      <c r="D35" s="39"/>
-      <c r="E35" s="39"/>
-      <c r="F35" s="39"/>
-      <c r="G35" s="39"/>
-      <c r="H35" s="39"/>
-      <c r="I35" s="39"/>
-      <c r="J35" s="39"/>
-      <c r="K35" s="39"/>
-      <c r="L35" s="39"/>
-      <c r="M35" s="39"/>
-    </row>
-    <row r="36" spans="1:13">
-      <c r="A36" s="40"/>
-      <c r="B36" s="40"/>
-      <c r="C36" t="s">
-        <v>462</v>
-      </c>
-      <c r="D36" s="39"/>
-      <c r="E36" s="39"/>
-      <c r="F36" s="39"/>
-      <c r="G36" s="39"/>
-      <c r="H36" s="39"/>
-      <c r="I36" s="39"/>
-      <c r="J36" s="39"/>
-      <c r="K36" s="39"/>
-      <c r="L36" s="39"/>
-      <c r="M36" s="39"/>
-    </row>
-    <row r="37" spans="1:13">
-      <c r="A37" s="40"/>
-      <c r="B37" s="40"/>
-      <c r="C37" t="s">
-        <v>468</v>
-      </c>
-      <c r="D37" s="39"/>
-      <c r="E37" s="39"/>
-      <c r="F37" s="39"/>
-      <c r="G37" s="39"/>
-      <c r="H37" s="39"/>
-      <c r="I37" s="39"/>
-      <c r="J37" s="39"/>
-      <c r="K37" s="39"/>
-      <c r="L37" s="39"/>
-      <c r="M37" s="39"/>
-    </row>
-    <row r="38" spans="1:13">
-      <c r="A38" s="40"/>
-      <c r="B38" s="40"/>
-      <c r="C38" t="s">
-        <v>472</v>
-      </c>
-      <c r="D38" s="39"/>
-      <c r="E38" s="39"/>
-      <c r="F38" s="39"/>
-      <c r="G38" s="39"/>
-      <c r="H38" s="39"/>
-      <c r="I38" s="39"/>
-      <c r="J38" s="39"/>
-      <c r="K38" s="39"/>
-      <c r="L38" s="39"/>
-      <c r="M38" s="39"/>
-    </row>
-    <row r="39" spans="1:13">
-      <c r="A39" s="40"/>
-      <c r="B39" s="40" t="s">
-        <v>477</v>
-      </c>
-      <c r="C39" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13">
-      <c r="A40" s="40"/>
-      <c r="B40" s="40"/>
-      <c r="C40" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13">
-      <c r="A41" s="40"/>
-      <c r="B41" s="40" t="s">
-        <v>503</v>
-      </c>
-      <c r="C41" s="40"/>
-    </row>
-    <row r="42" spans="1:13">
-      <c r="A42" s="40"/>
-      <c r="B42" s="41" t="s">
-        <v>52</v>
-      </c>
-      <c r="C42" s="41"/>
+      <c r="E42" s="38"/>
+      <c r="F42" s="38"/>
+      <c r="G42" s="38"/>
+      <c r="H42" s="38"/>
+      <c r="I42" s="38"/>
+      <c r="J42" s="38"/>
+      <c r="K42" s="38"/>
+      <c r="L42" s="38"/>
+      <c r="M42" s="38"/>
+      <c r="N42" s="38"/>
+    </row>
+    <row r="43" spans="1:14" s="1" customFormat="1">
+      <c r="A43" s="46"/>
+      <c r="B43" s="46" t="s">
+        <v>530</v>
+      </c>
+      <c r="C43" s="46"/>
+      <c r="D43" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="E43" s="38"/>
+      <c r="F43" s="38"/>
+      <c r="G43" s="38"/>
+      <c r="H43" s="38"/>
+      <c r="I43" s="38"/>
+      <c r="J43" s="38"/>
+      <c r="K43" s="38"/>
+      <c r="L43" s="38"/>
+      <c r="M43" s="38"/>
+      <c r="N43" s="38"/>
+    </row>
+    <row r="44" spans="1:14" s="1" customFormat="1">
+      <c r="A44" s="46"/>
+      <c r="B44" s="46" t="s">
+        <v>62</v>
+      </c>
+      <c r="C44" s="46"/>
+      <c r="D44" s="38" t="s">
+        <v>539</v>
+      </c>
+      <c r="E44" s="38"/>
+      <c r="F44" s="38"/>
+      <c r="G44" s="38"/>
+      <c r="H44" s="38"/>
+      <c r="I44" s="38"/>
+      <c r="J44" s="38"/>
+      <c r="K44" s="38"/>
+      <c r="L44" s="38"/>
+      <c r="M44" s="38"/>
+      <c r="N44" s="38"/>
     </row>
   </sheetData>
-  <mergeCells count="56">
-    <mergeCell ref="L1:M1"/>
+  <mergeCells count="57">
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
     <mergeCell ref="A3:A11"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
@@ -7091,55 +7668,403 @@
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:C2"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="M12:N12"/>
     <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="L13:M13"/>
-    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:A31"/>
+    <mergeCell ref="B19:B27"/>
+    <mergeCell ref="E19:F27"/>
+    <mergeCell ref="G19:H27"/>
     <mergeCell ref="B30:C30"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:A30"/>
-    <mergeCell ref="B19:B26"/>
-    <mergeCell ref="D19:E26"/>
-    <mergeCell ref="J19:K26"/>
-    <mergeCell ref="L19:M26"/>
-    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="I19:J27"/>
+    <mergeCell ref="K19:L27"/>
+    <mergeCell ref="M19:N27"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="F19:G26"/>
-    <mergeCell ref="H19:I26"/>
-    <mergeCell ref="L31:M38"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="A31:A42"/>
-    <mergeCell ref="B31:B38"/>
-    <mergeCell ref="D31:E38"/>
-    <mergeCell ref="F31:G38"/>
-    <mergeCell ref="H31:I38"/>
-    <mergeCell ref="J31:K38"/>
+    <mergeCell ref="A32:A44"/>
+    <mergeCell ref="B32:B40"/>
+    <mergeCell ref="E32:F40"/>
+    <mergeCell ref="G32:H40"/>
+    <mergeCell ref="I32:J40"/>
+    <mergeCell ref="K32:L40"/>
+    <mergeCell ref="M32:N40"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
   </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0E62D68-85D6-4E11-B076-F1BCD7E7D187}">
+  <dimension ref="A1:C68"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="31.28515625" customWidth="1"/>
+    <col min="2" max="2" width="34.42578125" customWidth="1"/>
+    <col min="3" max="3" width="31.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="20.25" customHeight="1">
+      <c r="A1" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="C1" s="41"/>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="40" t="s">
+        <v>502</v>
+      </c>
+      <c r="B2" s="40" t="s">
+        <v>542</v>
+      </c>
+      <c r="C2" s="41" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="42" t="s">
+        <v>544</v>
+      </c>
+      <c r="B3" s="42" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="42" t="s">
+        <v>546</v>
+      </c>
+      <c r="B4" s="42" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="42" t="s">
+        <v>548</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="42" t="s">
+        <v>550</v>
+      </c>
+      <c r="B6" s="42" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="42" t="s">
+        <v>552</v>
+      </c>
+      <c r="B7" s="43" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="42" t="s">
+        <v>554</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="42" t="s">
+        <v>556</v>
+      </c>
+      <c r="B9" s="42" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="42" t="s">
+        <v>558</v>
+      </c>
+      <c r="B10" s="42" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="42" t="s">
+        <v>560</v>
+      </c>
+      <c r="B11" s="42" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="42" t="s">
+        <v>562</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="42" t="s">
+        <v>564</v>
+      </c>
+      <c r="B13" s="42" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="42" t="s">
+        <v>566</v>
+      </c>
+      <c r="B14" s="42" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="42" t="s">
+        <v>568</v>
+      </c>
+      <c r="B15" s="42" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="42" t="s">
+        <v>570</v>
+      </c>
+      <c r="B16" s="42" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="42" t="s">
+        <v>572</v>
+      </c>
+      <c r="B17" s="42" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="42" t="s">
+        <v>574</v>
+      </c>
+      <c r="B18" s="42" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="44"/>
+      <c r="B19" s="44"/>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="44"/>
+      <c r="B20" s="44"/>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="44"/>
+      <c r="B21" s="44"/>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="44"/>
+      <c r="B22" s="44"/>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="44"/>
+      <c r="B23" s="44"/>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="44"/>
+      <c r="B24" s="44"/>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="44"/>
+      <c r="B25" s="44"/>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="44"/>
+      <c r="B26" s="44"/>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="44"/>
+      <c r="B27" s="44"/>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="44"/>
+      <c r="B28" s="44"/>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="44"/>
+      <c r="B29" s="44"/>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="44"/>
+      <c r="B30" s="44"/>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="44"/>
+      <c r="B31" s="44"/>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="44"/>
+      <c r="B32" s="44"/>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="44"/>
+      <c r="B33" s="44"/>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="44"/>
+      <c r="B34" s="44"/>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="44"/>
+      <c r="B35" s="44"/>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="44"/>
+      <c r="B36" s="44"/>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="44"/>
+      <c r="B37" s="44"/>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="44"/>
+      <c r="B38" s="44"/>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="44"/>
+      <c r="B39" s="44"/>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="44"/>
+      <c r="B40" s="44"/>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="44"/>
+      <c r="B41" s="44"/>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="44"/>
+      <c r="B42" s="44"/>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="44"/>
+      <c r="B43" s="44"/>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="44"/>
+      <c r="B44" s="44"/>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="44"/>
+      <c r="B45" s="44"/>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="44"/>
+      <c r="B46" s="44"/>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="44"/>
+      <c r="B47" s="44"/>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="44"/>
+      <c r="B48" s="44"/>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="44"/>
+      <c r="B49" s="44"/>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="44"/>
+      <c r="B50" s="44"/>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="44"/>
+      <c r="B51" s="44"/>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="44"/>
+      <c r="B52" s="44"/>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="44"/>
+      <c r="B53" s="44"/>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="44"/>
+      <c r="B54" s="44"/>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="44"/>
+      <c r="B55" s="44"/>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="44"/>
+      <c r="B56" s="44"/>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="44"/>
+      <c r="B57" s="44"/>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="44"/>
+      <c r="B58" s="44"/>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="44"/>
+      <c r="B59" s="44"/>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="44"/>
+      <c r="B60" s="44"/>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="44"/>
+      <c r="B61" s="44"/>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="44"/>
+      <c r="B62" s="44"/>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="44"/>
+      <c r="B63" s="44"/>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="44"/>
+      <c r="B64" s="44"/>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="44"/>
+      <c r="B65" s="44"/>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="44"/>
+      <c r="B66" s="44"/>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="44"/>
+      <c r="B67" s="44"/>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="44"/>
+      <c r="B68" s="44"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -7165,8 +8090,8 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010005FFA18751C0744EA482910462967CE1" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d447366bdb230741127c7a7ac2fa697d">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6bc95d49-17e3-4d0a-929b-830fe3aa2f74" xmlns:ns3="cb815603-3128-4aee-956f-7cdc70044e75" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a539070d0a2f573325233470b52e9d41" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Tài liệu" ma:contentTypeID="0x01010005FFA18751C0744EA482910462967CE1" ma:contentTypeVersion="14" ma:contentTypeDescription="Tạo tài liệu mới." ma:contentTypeScope="" ma:versionID="ccb1c2cb59a6d87295d36fd0bb2c7bf9">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6bc95d49-17e3-4d0a-929b-830fe3aa2f74" xmlns:ns3="cb815603-3128-4aee-956f-7cdc70044e75" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e7fb121f459fab52ba0e926b4f132522" ns2:_="" ns3:_="">
     <xsd:import namespace="6bc95d49-17e3-4d0a-929b-830fe3aa2f74"/>
     <xsd:import namespace="cb815603-3128-4aee-956f-7cdc70044e75"/>
     <xsd:element name="properties">
@@ -7198,7 +8123,7 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="6bc95d49-17e3-4d0a-929b-830fe3aa2f74" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Chia sẻ Với" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -7217,7 +8142,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Chia sẻ Có Chi tiết" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -7249,7 +8174,7 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="fe08bad7-0531-4e50-a3a8-7b1f718b4e48" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Thẻ Hình ảnh" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="fe08bad7-0531-4e50-a3a8-7b1f718b4e48" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -7303,8 +8228,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Loại Nội dung"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Tiêu đề"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -7402,5 +8327,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C15EF8D-8B5E-483E-856E-98A5B1FABD9E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{059D3F59-86D6-44A9-B7D5-015CA0B15632}"/>
 </file>
--- a/tasks/phantichchuyensau/Mô tả logic công thức.xlsx
+++ b/tasks/phantichchuyensau/Mô tả logic công thức.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30410"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FA09933B-E8D5-4786-9452-6C6D623F126B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A464CDE0-D5A5-4090-A24B-A82A04F435E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Phân tích chuyên sâu" sheetId="1" r:id="rId1"/>
-    <sheet name="Cấu hình cảnh báo" sheetId="2" r:id="rId2"/>
-    <sheet name="Nhóm chỉ tiêu - chỉ tiêu" sheetId="4" r:id="rId3"/>
-    <sheet name="Biến số khả dụng" sheetId="5" r:id="rId4"/>
+    <sheet name="Biến số khả dụng" sheetId="5" r:id="rId1"/>
+    <sheet name="Phân tích chuyên sâu" sheetId="1" r:id="rId2"/>
+    <sheet name="Cấu hình cảnh báo" sheetId="2" r:id="rId3"/>
+    <sheet name="Nhóm chỉ tiêu - chỉ tiêu" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -37,7 +37,118 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="576">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="575">
+  <si>
+    <t>Tên biến số khả dụng</t>
+  </si>
+  <si>
+    <t>Tên field tương ứng</t>
+  </si>
+  <si>
+    <t>Tổng vốn đầu tư đăng ký</t>
+  </si>
+  <si>
+    <t>tong_von_dau_tu_dang_ky</t>
+  </si>
+  <si>
+    <t>gcnđt</t>
+  </si>
+  <si>
+    <t>Vốn đầu tư thực hiện lũy kế gcndt</t>
+  </si>
+  <si>
+    <t>von_dau_tu_thuc_hien_luy_ke_gcndt</t>
+  </si>
+  <si>
+    <t>Vốn góp kỳ báo cáo</t>
+  </si>
+  <si>
+    <t>von_gop_ky</t>
+  </si>
+  <si>
+    <t>Vốn góp lũy kế gcndt</t>
+  </si>
+  <si>
+    <t>von_gop_luy_ke_gcndt</t>
+  </si>
+  <si>
+    <t>Vốn vay kỳ báo cáo</t>
+  </si>
+  <si>
+    <t>von_vay_ky</t>
+  </si>
+  <si>
+    <t>Vốn vay lũy kế gcndt</t>
+  </si>
+  <si>
+    <t>von_vay_luy_ke_gcndt</t>
+  </si>
+  <si>
+    <t>Lợi nhuận tái đầu tư kỳ báo cáo</t>
+  </si>
+  <si>
+    <t>loi_nhuan_tai_dau_tu_ky</t>
+  </si>
+  <si>
+    <t>Lợi nhuận tái đầu tư lũy kế gcndt</t>
+  </si>
+  <si>
+    <t>loi_nhuan_tai_dau_tu_luy_ke_gcndt</t>
+  </si>
+  <si>
+    <t>Doanh thu thuần kỳ báo cáo</t>
+  </si>
+  <si>
+    <t>doanh_thu_thuan_ky</t>
+  </si>
+  <si>
+    <t>Giá trị xuất khẩu kỳ báo cáo</t>
+  </si>
+  <si>
+    <t>gia_tri_xuat_khau_ky</t>
+  </si>
+  <si>
+    <t>Giá trị nhập khẩu kỳ báo cáo</t>
+  </si>
+  <si>
+    <t>gia_tri_nhap_khau_ky</t>
+  </si>
+  <si>
+    <t>Thuế và nộp ngân sách kỳ báo cáo</t>
+  </si>
+  <si>
+    <t>thue_va_nop_ngan_sach_ky</t>
+  </si>
+  <si>
+    <t>Lợi nhuận sau thuế kỳ báo cáo</t>
+  </si>
+  <si>
+    <t>loi_nhuan_sau_thue_ky</t>
+  </si>
+  <si>
+    <t>Chi phí R&amp;D kỳ báo cáo</t>
+  </si>
+  <si>
+    <t>chi_phi_rd_ky</t>
+  </si>
+  <si>
+    <t>Chi phí môi trường kỳ báo cáo</t>
+  </si>
+  <si>
+    <t>chi_phi_moi_truong_ky</t>
+  </si>
+  <si>
+    <t>Nguồn thu khác kỳ báo cáo</t>
+  </si>
+  <si>
+    <t>nguon_thu_khac_ky</t>
+  </si>
+  <si>
+    <t>Lợi nhuân kỳ báo cáo</t>
+  </si>
+  <si>
+    <t>loi_nhuan</t>
+  </si>
   <si>
     <t>STT</t>
   </si>
@@ -508,16 +619,28 @@
     <t>Đếm số bản ghi nghĩa vụ dự án tới hiện tại</t>
   </si>
   <si>
+    <t>Biến động so với kỳ trước</t>
+  </si>
+  <si>
+    <t>Tăng/Giảm '(tổng số nghĩa vụ kỳ này - tổng số nghĩa vụ kỳ trước) / tổng số nghĩa vụ kỳ trước '</t>
+  </si>
+  <si>
     <t>Tổng số tuân thủ</t>
   </si>
   <si>
     <t>Đếm số nghĩa vụ có Trạng thái = "Tuân thủ" tới kỳ hiện tại</t>
   </si>
   <si>
+    <t xml:space="preserve">Tăng/Giảm '(tổng số tuân thủ kỳ này - tổng số tuân thủ kỳ trước) / tổng số tuân thủ kỳ trước </t>
+  </si>
+  <si>
     <t>Tổng số vi phạm</t>
   </si>
   <si>
     <t>Đếm số nghĩa vụ có Trạng thái = "Vi phạm" tới kỳ hiện tại</t>
+  </si>
+  <si>
+    <t>Tăng/Giảm '(tổng số vi phạm kỳ này - tổng số vi phạm kỳ trước) / tổng số nghĩa vi phạm trước '</t>
   </si>
   <si>
     <t>Mức độ rủi ro hệ thống</t>
@@ -530,13 +653,7 @@
 [75 - 100] -&gt; Nghiêm trọng</t>
   </si>
   <si>
-    <t>Bảng danh sách chi tiết nghĩa vụ</t>
-  </si>
-  <si>
-    <t>Tên nghĩa vụ</t>
-  </si>
-  <si>
-    <t>fix cứng: tên nhóm nghĩa vụ + kỳ báo cáo</t>
+    <t>Bảng chi tiết tuân thủ cam kết</t>
   </si>
   <si>
     <t>Tên nhóm nghĩa vụ</t>
@@ -554,7 +671,10 @@
     <t>Thực tế ghi nhận</t>
   </si>
   <si>
-    <t>Lấy từ data raw</t>
+    <t>Quy định pháp luật về môi trường, xây dựng và các quy định khác: mặc định "Đạt yêu cầu theo quy định"
+Thủ tục đăng ký cấp tài khoản: mặc định "Đạt yêu cầu theo quy định"
+Tiến độ: bc_dinh_ky.tien_do_trang_thai + bc_dinh_ky.ky_key
+Nộp báo cáo định kỳ: tên báo cáo + thời gian nộp</t>
   </si>
   <si>
     <t>Vốn &amp; Giải ngân</t>
@@ -783,29 +903,6 @@
   </si>
   <si>
     <t>Gọi API LLM bên ngoài, truyền dữ liệu ngữ cảnh liên quan làm input (toàn bộ bảng dữ liệu so sánh chi tiết) — sinh nhận xét tăng/giảm, cảnh báo, cải thiện theo từng nhóm chỉ tiêu</t>
-  </si>
-  <si>
-    <t>Nút Xem báo cáo chi tiết</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Điều hướng sang </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>trang báo cáo phân tích đầy đủ ứng với kỳ đang so sánh</t>
-    </r>
   </si>
   <si>
     <t>Chỉ số rủi ro tổng quát</t>
@@ -830,7 +927,7 @@
     <t>Mô tả khuyến nghị giám sát</t>
   </si>
   <si>
-    <t>Gọi API LLM bên ngoài, truyền dữ liệu ngữ cảnh liên quan làm input (điểm rủi ro theo từng danh mục) — sinh khuyến nghị giám sát ngắn gọn</t>
+    <t>Gọi API LLM bên ngoài, truyền dữ liệu ngữ cảnh liên quan làm input— sinh khuyến nghị giám sát ngắn gọn</t>
   </si>
   <si>
     <t>Phân tích rủi ro theo danh mục</t>
@@ -857,7 +954,10 @@
         <rFont val="Calibri"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">Vốn&amp;Giải ngân: 
+      <t xml:space="preserve">Vốn&amp;Giải ngân: tính Tỷ lệ giải ngân = Vốn giải ngân lũy kế / Tổng quy mô vốn; Tỷ lệ chưa giải ngân = 1 - Tỷ lệ giải ngân.
+Mức độ quy mô vốn được chuẩn hóa theo toàn bộ danh mục dự án: tính Quy mô vốn chuẩn hóa = ln(1 + Tổng quy mô vốn), tính Mức độ quy mô vốn = PercentileRank(Quy mô vốn chuẩn hóa), cho giá trị từ 0–1.
+Điểm rủi ro = 10 × Tỷ lệ chưa giải ngân × [0,60 + 0,25 × (1 - e^(-0,231 × Số kỳ)) + 0,15 × Mức độ quy mô vốn)].
+quy đổi ra 4 mức [0; 2,5): thấp, [2,5; 5): trung bình, [5; 7.5): cao, [7,7; 10]: nghiêm trọng
 </t>
     </r>
     <r>
@@ -871,16 +971,20 @@
     </r>
   </si>
   <si>
-    <t>Tài chính: tính theo 4 chỉ tiêu ở tab tài chính, mỗi chỉ tiêu có điểm rủi ro là 10/4 nếu Xu hướng của chỉ tiêu là giảm, =0 nếu ngược lại. tổng điểm rủi ro = số chỉ tiêu có xu hướng giảm * 10/4</t>
-  </si>
-  <si>
-    <t>Tài chính: tính theo 7 chỉ tiêu ở tab tài chính, mỗi chỉ tiêu có điểm rủi ro là 10/7 nếu Xu hướng của chỉ tiêu là giảm, =0 nếu ngược lại. tổng điểm rủi ro = số chỉ tiêu có xu hướng giảm * 10/7</t>
-  </si>
-  <si>
-    <t>Tài chính: tính theo 7 chỉ tiêu ở tab tài chính, mỗi chỉ tiêu có điểm rủi ro là 10/7 nếu Xu hướng của chỉ tiêu là giảm, =0 nếu ngược lại. tổng điểm rủi ro = số chỉ tiêu có xu hướng giảm * 10/8</t>
-  </si>
-  <si>
-    <t>Tài chính: tính theo 4 chỉ tiêu ở tab tài chính, mỗi chỉ tiêu có điểm rủi ro là 10/4 nếu Xu hướng của chỉ tiêu là giảm, =0 nếu ngược lại. tổng điểm rủi ro = số chỉ tiêu có xu hướng giảm * 10/5</t>
+    <t>Tài chính: tính theo 4 chỉ tiêu ở tab tài chính, mỗi chỉ tiêu có điểm rủi ro là 10/4 nếu Xu hướng của chỉ tiêu là giảm, =0 nếu ngược lại. tổng điểm rủi ro = số chỉ tiêu có xu hướng giảm * 10/4
+Vốn&amp;Giải ngân =10.(1 - von_dau_tu_thuc_hien_luy_ke_gcndt / tong_von_dau_tu_dang_ky).[0,6 + 0,25.(1 - e^(-ln2/3.số kỳ hoạt động) + 0.15.percentileRank(ln(1 + tong_von_dau_tu_dang_ky))]</t>
+  </si>
+  <si>
+    <t>Tài chính: tính theo 7 chỉ tiêu ở tab tài chính, mỗi chỉ tiêu có điểm rủi ro là 10/7 nếu Xu hướng của chỉ tiêu là giảm, =0 nếu ngược lại. tổng điểm rủi ro = số chỉ tiêu có xu hướng giảm * 10/7
+Vốn&amp;Giải ngân =10.(1 - von_dau_tu_thuc_hien_luy_ke_gcndt / tong_von_dau_tu_dang_ky).[0,6 + 0,25.(1 - e^(-ln2/3.số kỳ hoạt động) + 0.15.percentileRank(ln(1 + tong_von_dau_tu_dang_ky))]</t>
+  </si>
+  <si>
+    <t>Tài chính: tính theo 7 chỉ tiêu ở tab tài chính, mỗi chỉ tiêu có điểm rủi ro là 10/7 nếu Xu hướng của chỉ tiêu là giảm, =0 nếu ngược lại. tổng điểm rủi ro = số chỉ tiêu có xu hướng giảm * 10/8
+Vốn&amp;Giải ngân =10.(1 - von_dau_tu_thuc_hien_luy_ke_gcndt / tong_von_dau_tu_dang_ky).[0,6 + 0,25.(1 - e^(-ln2/3.số kỳ hoạt động) + 0.15.percentileRank(ln(1 + tong_von_dau_tu_dang_ky))]</t>
+  </si>
+  <si>
+    <t>Tài chính: tính theo 4 chỉ tiêu ở tab tài chính, mỗi chỉ tiêu có điểm rủi ro là 10/4 nếu Xu hướng của chỉ tiêu là giảm, =0 nếu ngược lại. tổng điểm rủi ro = số chỉ tiêu có xu hướng giảm * 10/5
+Vốn&amp;Giải ngân =10.(1 - von_dau_tu_thuc_hien_luy_ke_gcndt / tong_von_dau_tu_dang_ky).[0,6 + 0,25.(1 - e^(-ln2/3.số kỳ hoạt động) + 0.15.percentileRank(ln(1 + tong_von_dau_tu_dang_ky))]</t>
   </si>
   <si>
     <t>Thanh tiến trình theo danh mục</t>
@@ -1458,13 +1562,13 @@
     <t>Trường hợp chỉ tiêu thuộc nhóm giá trị định lượng (VD Tài chính/Vốn)</t>
   </si>
   <si>
-    <t>Trục X = kỳ báo cáo (Quý); Trục Y = giá trị chỉ tiêu (tỷ VNĐ), lấy từ data raw theo từng kỳ; đường ngưỡng an toàn = giá trị Ngưỡng cảnh báo đã cấu hình (vd ngưỡng X% -&gt; giá trị chỉ tiêu của ngưỡng =X%*giá trị chỉ tiêu so sánh + giá trị chỉ tiêu so sánh</t>
+    <t>Trục X = kỳ báo cáo (Quý/Năm tùy theo báo cáo là BC quý hay BC năm); Trục Y = giá trị chỉ tiêu (tỷ VNĐ), lấy từ data raw theo từng kỳ; đường ngưỡng = (giá trị của {Chỉ tiêu so sánh} * (ngưỡng+100)) / 100 (vd doanh thu &gt; 130% lợi nhuận -&gt; giá trị chỉ tiêu của ngưỡng =(lợi nhuận  * (130+100)) / 100</t>
   </si>
   <si>
     <t>Trường hợp chỉ tiêu thuộc nhóm tiến độ</t>
   </si>
   <si>
-    <t>Trục X = kỳ báo cáo (Quý); Trục Y = thang trạng thái tiến độ (Đúng tiến độ/Gặp khó khăn/Chậm tiến độ/Không có khả năng triển khai), lấy từ data raw trạng thái tiến độ theo từng kỳ</t>
+    <t>Trục X = kỳ báo cáo (Quý/Năm); Trục Y = thang trạng thái tiến độ (Đúng tiến độ/Gặp khó khăn/Chậm tiến độ/Không có khả năng triển khai), lấy từ data raw trạng thái tiến độ theo từng kỳ</t>
   </si>
   <si>
     <t>Thông tin dự án</t>
@@ -1615,9 +1719,6 @@
   </si>
   <si>
     <t>Vốn &amp; giải ngân</t>
-  </si>
-  <si>
-    <t>Tổng vốn đầu tư đăng ký</t>
   </si>
   <si>
     <t>Vốn đầu tư thực hiện</t>
@@ -1701,10 +1802,10 @@
     <t>taiDauTu.luyke</t>
   </si>
   <si>
-    <t>Vốn khác</t>
-  </si>
-  <si>
     <t>Tiến độ</t>
+  </si>
+  <si>
+    <t>Tiến độ (xét tất cả tiến độ của báo cáo năm)</t>
   </si>
   <si>
     <t>đúng tiến độ -&gt; tuân thủ
@@ -1720,136 +1821,25 @@
     <t>Quy định pháp luật về môi trường, xây dựng và các quy định khác</t>
   </si>
   <si>
-    <t>Nộp báo cáo định kỳ</t>
+    <t>Nộp báo cáo định kỳ (xét tất cả báo cáo quý và năm)</t>
   </si>
   <si>
     <t>bc_dinh_ky.ngay_nop_bao_cao</t>
   </si>
   <si>
     <t>check NgayNop trong bảng BaoCaos với hạn nộp bc (fix):
-Trước ngày 10 tháng đầu quý sau (vd hạn nộp bc quý I 2026 là 10/4)</t>
-  </si>
-  <si>
-    <t>check NgayNop trong bảng BaoCaos với hạn nộp bc:
-Trước ngày 10 tháng đầu quý sau (vd hạn nộp bc quý I 2026 là 10/4)</t>
+Trước ngày 10 tháng đầu quý sau (vd hạn nộp bc quý I 2026 là 10/4)
+Trước ngày 31/3 năm sau đối với báo cáo năm</t>
   </si>
   <si>
     <t>bc_tuan_thu_chi_tiet.trang_thai</t>
-  </si>
-  <si>
-    <t>Tên biến số khả dụng</t>
-  </si>
-  <si>
-    <t>Tên field tương ứng</t>
-  </si>
-  <si>
-    <t>tong_von_dau_tu_dang_ky</t>
-  </si>
-  <si>
-    <t>gcnđt</t>
-  </si>
-  <si>
-    <t>Vốn đầu tư thực hiện lũy kế gcndt</t>
-  </si>
-  <si>
-    <t>von_dau_tu_thuc_hien_luy_ke_gcndt</t>
-  </si>
-  <si>
-    <t>Vốn góp kỳ báo cáo</t>
-  </si>
-  <si>
-    <t>von_gop_ky</t>
-  </si>
-  <si>
-    <t>Vốn góp lũy kế gcndt</t>
-  </si>
-  <si>
-    <t>von_gop_luy_ke_gcndt</t>
-  </si>
-  <si>
-    <t>Vốn vay kỳ báo cáo</t>
-  </si>
-  <si>
-    <t>von_vay_ky</t>
-  </si>
-  <si>
-    <t>Vốn vay lũy kế gcndt</t>
-  </si>
-  <si>
-    <t>von_vay_luy_ke_gcndt</t>
-  </si>
-  <si>
-    <t>Lợi nhuận tái đầu tư kỳ báo cáo</t>
-  </si>
-  <si>
-    <t>loi_nhuan_tai_dau_tu_ky</t>
-  </si>
-  <si>
-    <t>Lợi nhuận tái đầu tư lũy kế gcndt</t>
-  </si>
-  <si>
-    <t>loi_nhuan_tai_dau_tu_luy_ke_gcndt</t>
-  </si>
-  <si>
-    <t>Doanh thu thuần kỳ báo cáo</t>
-  </si>
-  <si>
-    <t>doanh_thu_thuan_ky</t>
-  </si>
-  <si>
-    <t>Giá trị xuất khẩu kỳ báo cáo</t>
-  </si>
-  <si>
-    <t>gia_tri_xuat_khau_ky</t>
-  </si>
-  <si>
-    <t>Giá trị nhập khẩu kỳ báo cáo</t>
-  </si>
-  <si>
-    <t>gia_tri_nhap_khau_ky</t>
-  </si>
-  <si>
-    <t>Thuế và nộp ngân sách kỳ báo cáo</t>
-  </si>
-  <si>
-    <t>thue_va_nop_ngan_sach_ky</t>
-  </si>
-  <si>
-    <t>Lợi nhuận sau thuế kỳ báo cáo</t>
-  </si>
-  <si>
-    <t>loi_nhuan_sau_thue_ky</t>
-  </si>
-  <si>
-    <t>Chi phí R&amp;D kỳ báo cáo</t>
-  </si>
-  <si>
-    <t>chi_phi_rd_ky</t>
-  </si>
-  <si>
-    <t>Chi phí môi trường kỳ báo cáo</t>
-  </si>
-  <si>
-    <t>chi_phi_moi_truong_ky</t>
-  </si>
-  <si>
-    <t>Nguồn thu khác kỳ báo cáo</t>
-  </si>
-  <si>
-    <t>nguon_thu_khac_ky</t>
-  </si>
-  <si>
-    <t>Lợi nhuân kỳ báo cáo</t>
-  </si>
-  <si>
-    <t>loi_nhuan</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1935,6 +1925,28 @@
       <name val="Arial"/>
       <charset val="1"/>
     </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color rgb="FF1A1A1A"/>
+      <name val="Consolas"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1956,7 +1968,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -2085,11 +2097,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2218,16 +2243,22 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2247,6 +2278,27 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2561,8 +2613,371 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0E62D68-85D6-4E11-B076-F1BCD7E7D187}">
+  <dimension ref="A1:C68"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="31.28515625" customWidth="1"/>
+    <col min="2" max="2" width="34.42578125" customWidth="1"/>
+    <col min="3" max="3" width="31.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="20.25" customHeight="1">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="41"/>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="41" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="42" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="42" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="42" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="42" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="43" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="42" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="42" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="42" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="42" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="42" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="42" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="42" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="42" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="42" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="42" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="44"/>
+      <c r="B19" s="44"/>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="44"/>
+      <c r="B20" s="44"/>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="44"/>
+      <c r="B21" s="44"/>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="44"/>
+      <c r="B22" s="44"/>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="44"/>
+      <c r="B23" s="44"/>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="44"/>
+      <c r="B24" s="44"/>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="44"/>
+      <c r="B25" s="44"/>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="44"/>
+      <c r="B26" s="44"/>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="44"/>
+      <c r="B27" s="44"/>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="44"/>
+      <c r="B28" s="44"/>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="44"/>
+      <c r="B29" s="44"/>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="44"/>
+      <c r="B30" s="44"/>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="44"/>
+      <c r="B31" s="44"/>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="44"/>
+      <c r="B32" s="44"/>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="44"/>
+      <c r="B33" s="44"/>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="44"/>
+      <c r="B34" s="44"/>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="44"/>
+      <c r="B35" s="44"/>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="44"/>
+      <c r="B36" s="44"/>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="44"/>
+      <c r="B37" s="44"/>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="44"/>
+      <c r="B38" s="44"/>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="44"/>
+      <c r="B39" s="44"/>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="44"/>
+      <c r="B40" s="44"/>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="44"/>
+      <c r="B41" s="44"/>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="44"/>
+      <c r="B42" s="44"/>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="44"/>
+      <c r="B43" s="44"/>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="44"/>
+      <c r="B44" s="44"/>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="44"/>
+      <c r="B45" s="44"/>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="44"/>
+      <c r="B46" s="44"/>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="44"/>
+      <c r="B47" s="44"/>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="44"/>
+      <c r="B48" s="44"/>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="44"/>
+      <c r="B49" s="44"/>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="44"/>
+      <c r="B50" s="44"/>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="44"/>
+      <c r="B51" s="44"/>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="44"/>
+      <c r="B52" s="44"/>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="44"/>
+      <c r="B53" s="44"/>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="44"/>
+      <c r="B54" s="44"/>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="44"/>
+      <c r="B55" s="44"/>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="44"/>
+      <c r="B56" s="44"/>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="44"/>
+      <c r="B57" s="44"/>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="44"/>
+      <c r="B58" s="44"/>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="44"/>
+      <c r="B59" s="44"/>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="44"/>
+      <c r="B60" s="44"/>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="44"/>
+      <c r="B61" s="44"/>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="44"/>
+      <c r="B62" s="44"/>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="44"/>
+      <c r="B63" s="44"/>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="44"/>
+      <c r="B64" s="44"/>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="44"/>
+      <c r="B65" s="44"/>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="44"/>
+      <c r="B66" s="44"/>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="44"/>
+      <c r="B67" s="44"/>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="44"/>
+      <c r="B68" s="44"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S159"/>
+  <dimension ref="A1:S160"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="2"/>
@@ -2577,40 +2992,40 @@
   <sheetData>
     <row r="1" spans="1:19" s="2" customFormat="1">
       <c r="A1" s="3" t="s">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="G1" s="22" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="H1" s="22" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="I1" s="22" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="J1" s="22" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="K1" s="22" t="s">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="L1" s="22" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="N1" s="23"/>
       <c r="O1" s="24"/>
@@ -2623,67 +3038,67 @@
       <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="52" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="51" t="s">
-        <v>13</v>
+      <c r="B2" s="54" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="53" t="s">
+        <v>50</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="H2" s="14"/>
       <c r="I2" s="14" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="L2" s="32" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="28.5">
       <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="53"/>
-      <c r="C3" s="51"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="53"/>
       <c r="D3" s="5" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="G3" s="33" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="H3" s="33" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="I3" s="33" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="J3" s="33" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="K3" s="33" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="L3" s="15"/>
     </row>
@@ -2691,133 +3106,133 @@
       <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="53"/>
-      <c r="C4" s="51"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="53"/>
       <c r="D4" s="5" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="G4" s="33" t="s">
-        <v>27</v>
+        <v>64</v>
       </c>
       <c r="H4" s="33" t="s">
-        <v>27</v>
+        <v>64</v>
       </c>
       <c r="I4" s="33" t="s">
-        <v>27</v>
+        <v>64</v>
       </c>
       <c r="J4" s="33" t="s">
-        <v>27</v>
+        <v>64</v>
       </c>
       <c r="K4" s="33" t="s">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="L4" s="32" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="30.75">
       <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="53"/>
-      <c r="C5" s="51"/>
+      <c r="B5" s="55"/>
+      <c r="C5" s="53"/>
       <c r="D5" s="5" t="s">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="G5" s="33" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="H5" s="33" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="I5" s="33" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="J5" s="33" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="K5" s="33" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="L5" s="32" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:19">
       <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="53"/>
-      <c r="C6" s="51"/>
+      <c r="B6" s="55"/>
+      <c r="C6" s="53"/>
       <c r="D6" s="5" t="s">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="G6" s="33" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="H6" s="33" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="I6" s="33" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="J6" s="33" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="K6" s="33" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="L6" s="32" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="30.75">
       <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" s="53"/>
-      <c r="C7" s="51"/>
+      <c r="B7" s="55"/>
+      <c r="C7" s="53"/>
       <c r="D7" s="5" t="s">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="G7" s="33" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="H7" s="33" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="I7" s="33" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="J7" s="33" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="K7" s="33" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="L7" s="15"/>
     </row>
@@ -2825,16 +3240,16 @@
       <c r="A8" s="4">
         <v>7</v>
       </c>
-      <c r="B8" s="53"/>
-      <c r="C8" s="51"/>
+      <c r="B8" s="55"/>
+      <c r="C8" s="53"/>
       <c r="D8" s="5" t="s">
-        <v>40</v>
+        <v>77</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="G8" s="33"/>
       <c r="H8" s="33"/>
@@ -2842,40 +3257,40 @@
       <c r="J8" s="33"/>
       <c r="K8" s="33"/>
       <c r="L8" s="32" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="30.75">
       <c r="A9" s="4">
         <v>8</v>
       </c>
-      <c r="B9" s="53"/>
-      <c r="C9" s="52" t="s">
-        <v>44</v>
+      <c r="B9" s="55"/>
+      <c r="C9" s="54" t="s">
+        <v>81</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>46</v>
+        <v>83</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>47</v>
+        <v>84</v>
       </c>
       <c r="G9" s="33" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="H9" s="33" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="I9" s="33" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="J9" s="33" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="K9" s="33" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="L9" s="15"/>
     </row>
@@ -2883,31 +3298,31 @@
       <c r="A10" s="4">
         <v>9</v>
       </c>
-      <c r="B10" s="53"/>
-      <c r="C10" s="53"/>
+      <c r="B10" s="55"/>
+      <c r="C10" s="55"/>
       <c r="D10" s="5" t="s">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>51</v>
+        <v>88</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>52</v>
+        <v>89</v>
       </c>
       <c r="G10" s="33" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="H10" s="33" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="I10" s="33" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="J10" s="33" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="K10" s="33" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="L10" s="32"/>
     </row>
@@ -2915,63 +3330,63 @@
       <c r="A11" s="4">
         <v>10</v>
       </c>
-      <c r="B11" s="53"/>
-      <c r="C11" s="53"/>
+      <c r="B11" s="55"/>
+      <c r="C11" s="55"/>
       <c r="D11" s="5" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="G11" s="33" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="H11" s="33" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="I11" s="33" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="J11" s="33" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="K11" s="33" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="L11" s="32" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" spans="1:19">
       <c r="A12" s="4">
         <v>12</v>
       </c>
-      <c r="B12" s="53"/>
-      <c r="C12" s="53"/>
+      <c r="B12" s="55"/>
+      <c r="C12" s="55"/>
       <c r="D12" s="5" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="E12" s="17"/>
       <c r="F12" s="17" t="s">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="G12" s="33" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="H12" s="33" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="I12" s="33" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="J12" s="33" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="K12" s="33" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="L12" s="32"/>
     </row>
@@ -2979,29 +3394,29 @@
       <c r="A13" s="4">
         <v>13</v>
       </c>
-      <c r="B13" s="54"/>
-      <c r="C13" s="54"/>
+      <c r="B13" s="56"/>
+      <c r="C13" s="56"/>
       <c r="D13" s="5" t="s">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="E13" s="17"/>
       <c r="F13" s="17" t="s">
-        <v>66</v>
+        <v>103</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>67</v>
+        <v>104</v>
       </c>
       <c r="H13" s="14" t="s">
-        <v>67</v>
+        <v>104</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>67</v>
+        <v>104</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>67</v>
+        <v>104</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>67</v>
+        <v>104</v>
       </c>
       <c r="L13" s="15"/>
     </row>
@@ -3009,17 +3424,17 @@
       <c r="A14" s="4">
         <v>14</v>
       </c>
-      <c r="B14" s="51" t="s">
-        <v>68</v>
+      <c r="B14" s="53" t="s">
+        <v>105</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="F14" s="17"/>
       <c r="G14" s="14"/>
@@ -3027,7 +3442,7 @@
       <c r="I14" s="14"/>
       <c r="J14" s="14"/>
       <c r="K14" s="13" t="s">
-        <v>71</v>
+        <v>108</v>
       </c>
       <c r="L14" s="32"/>
     </row>
@@ -3035,15 +3450,15 @@
       <c r="A15" s="4">
         <v>15</v>
       </c>
-      <c r="B15" s="51"/>
+      <c r="B15" s="53"/>
       <c r="C15" s="5" t="s">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>74</v>
+        <v>111</v>
       </c>
       <c r="F15" s="17"/>
       <c r="G15" s="14"/>
@@ -3057,15 +3472,15 @@
       <c r="A16" s="4">
         <v>16</v>
       </c>
-      <c r="B16" s="51"/>
+      <c r="B16" s="53"/>
       <c r="C16" s="5" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>74</v>
+        <v>111</v>
       </c>
       <c r="F16" s="17"/>
       <c r="G16" s="33"/>
@@ -3073,7 +3488,7 @@
       <c r="I16" s="33"/>
       <c r="J16" s="33"/>
       <c r="K16" s="33" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="L16" s="15"/>
     </row>
@@ -3081,31 +3496,31 @@
       <c r="A17" s="4">
         <v>17</v>
       </c>
-      <c r="B17" s="51"/>
+      <c r="B17" s="53"/>
       <c r="C17" s="5" t="s">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="F17" s="17"/>
       <c r="G17" s="14" t="s">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="H17" s="14" t="s">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="K17" s="33" t="s">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="L17" s="15"/>
     </row>
@@ -3113,31 +3528,31 @@
       <c r="A18" s="4">
         <v>18</v>
       </c>
-      <c r="B18" s="51"/>
+      <c r="B18" s="53"/>
       <c r="C18" s="5" t="s">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="F18" s="17"/>
       <c r="G18" s="13" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="K18" s="13" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="L18" s="15"/>
     </row>
@@ -3145,65 +3560,65 @@
       <c r="A19" s="4">
         <v>19</v>
       </c>
-      <c r="B19" s="50" t="s">
-        <v>85</v>
-      </c>
-      <c r="C19" s="50" t="s">
-        <v>86</v>
+      <c r="B19" s="52" t="s">
+        <v>122</v>
+      </c>
+      <c r="C19" s="52" t="s">
+        <v>123</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>87</v>
+        <v>124</v>
       </c>
       <c r="E19" s="18"/>
       <c r="F19" s="18" t="s">
-        <v>88</v>
+        <v>125</v>
       </c>
       <c r="G19" s="33" t="s">
-        <v>89</v>
+        <v>126</v>
       </c>
       <c r="H19" s="33" t="s">
-        <v>90</v>
+        <v>127</v>
       </c>
       <c r="I19" s="33" t="s">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="J19" s="33" t="s">
-        <v>89</v>
+        <v>126</v>
       </c>
       <c r="K19" s="33" t="s">
-        <v>92</v>
+        <v>129</v>
       </c>
       <c r="L19" s="32" t="s">
-        <v>93</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="86.25">
       <c r="A20" s="4">
         <v>20</v>
       </c>
-      <c r="B20" s="50"/>
-      <c r="C20" s="50"/>
+      <c r="B20" s="52"/>
+      <c r="C20" s="52"/>
       <c r="D20" s="6" t="s">
-        <v>94</v>
+        <v>131</v>
       </c>
       <c r="E20" s="18"/>
       <c r="F20" s="18" t="s">
-        <v>95</v>
+        <v>132</v>
       </c>
       <c r="G20" s="34" t="s">
-        <v>96</v>
+        <v>133</v>
       </c>
       <c r="H20" s="34" t="s">
-        <v>97</v>
+        <v>134</v>
       </c>
       <c r="I20" s="34" t="s">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="J20" s="34" t="s">
-        <v>96</v>
+        <v>133</v>
       </c>
       <c r="K20" s="33" t="s">
-        <v>99</v>
+        <v>136</v>
       </c>
       <c r="L20" s="32"/>
     </row>
@@ -3211,29 +3626,29 @@
       <c r="A21" s="4">
         <v>21</v>
       </c>
-      <c r="B21" s="50"/>
-      <c r="C21" s="50"/>
+      <c r="B21" s="52"/>
+      <c r="C21" s="52"/>
       <c r="D21" s="6" t="s">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="E21" s="18"/>
       <c r="F21" s="18" t="s">
-        <v>101</v>
+        <v>138</v>
       </c>
       <c r="G21" s="34" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="H21" s="34" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="I21" s="34" t="s">
-        <v>104</v>
+        <v>141</v>
       </c>
       <c r="J21" s="34" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="K21" s="13" t="s">
-        <v>105</v>
+        <v>142</v>
       </c>
       <c r="L21" s="15"/>
     </row>
@@ -3241,112 +3656,112 @@
       <c r="A22" s="4">
         <v>22</v>
       </c>
-      <c r="B22" s="50"/>
-      <c r="C22" s="50" t="s">
-        <v>106</v>
+      <c r="B22" s="52"/>
+      <c r="C22" s="52" t="s">
+        <v>143</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>107</v>
+        <v>144</v>
       </c>
       <c r="E22" s="18"/>
       <c r="F22" s="19" t="s">
-        <v>108</v>
+        <v>145</v>
       </c>
       <c r="G22" s="35" t="s">
-        <v>109</v>
+        <v>146</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="J22" s="35" t="s">
-        <v>109</v>
+        <v>146</v>
       </c>
       <c r="K22" s="13" t="s">
-        <v>111</v>
+        <v>148</v>
       </c>
       <c r="L22" s="32" t="s">
-        <v>112</v>
+        <v>149</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="86.25">
       <c r="A23" s="4">
         <v>23</v>
       </c>
-      <c r="B23" s="50"/>
-      <c r="C23" s="50"/>
+      <c r="B23" s="52"/>
+      <c r="C23" s="52"/>
       <c r="D23" s="6" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="E23" s="18"/>
       <c r="F23" s="18" t="s">
-        <v>101</v>
+        <v>138</v>
       </c>
       <c r="G23" s="34" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="H23" s="34" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="I23" s="34" t="s">
-        <v>104</v>
+        <v>141</v>
       </c>
       <c r="J23" s="34" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="K23" s="13" t="s">
-        <v>105</v>
+        <v>142</v>
       </c>
       <c r="L23" s="32" t="s">
-        <v>114</v>
+        <v>151</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="86.25">
       <c r="A24" s="4">
         <v>24</v>
       </c>
-      <c r="B24" s="50"/>
-      <c r="C24" s="50"/>
+      <c r="B24" s="52"/>
+      <c r="C24" s="52"/>
       <c r="D24" s="6" t="s">
-        <v>115</v>
+        <v>152</v>
       </c>
       <c r="E24" s="18"/>
       <c r="F24" s="18" t="s">
-        <v>95</v>
+        <v>132</v>
       </c>
       <c r="G24" s="34" t="s">
-        <v>96</v>
+        <v>133</v>
       </c>
       <c r="H24" s="34" t="s">
-        <v>97</v>
+        <v>134</v>
       </c>
       <c r="I24" s="34" t="s">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="J24" s="34" t="s">
-        <v>96</v>
+        <v>133</v>
       </c>
       <c r="K24" s="33" t="s">
-        <v>99</v>
+        <v>136</v>
       </c>
       <c r="L24" s="32" t="s">
-        <v>114</v>
+        <v>151</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="43.5">
       <c r="A25" s="4">
         <v>25</v>
       </c>
-      <c r="B25" s="50"/>
-      <c r="C25" s="50"/>
+      <c r="B25" s="52"/>
+      <c r="C25" s="52"/>
       <c r="D25" s="6" t="s">
-        <v>116</v>
+        <v>153</v>
       </c>
       <c r="E25" s="18"/>
       <c r="F25" s="18" t="s">
-        <v>117</v>
+        <v>154</v>
       </c>
       <c r="G25" s="14"/>
       <c r="H25" s="14"/>
@@ -3354,21 +3769,21 @@
       <c r="J25" s="14"/>
       <c r="K25" s="14"/>
       <c r="L25" s="32" t="s">
-        <v>118</v>
+        <v>155</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="45.75">
       <c r="A26" s="4">
         <v>26</v>
       </c>
-      <c r="B26" s="50"/>
-      <c r="C26" s="50"/>
+      <c r="B26" s="52"/>
+      <c r="C26" s="52"/>
       <c r="D26" s="6" t="s">
-        <v>119</v>
+        <v>156</v>
       </c>
       <c r="E26" s="18"/>
       <c r="F26" s="18" t="s">
-        <v>120</v>
+        <v>157</v>
       </c>
       <c r="G26" s="14"/>
       <c r="H26" s="14"/>
@@ -3376,23 +3791,23 @@
       <c r="J26" s="14"/>
       <c r="K26" s="14"/>
       <c r="L26" s="32" t="s">
-        <v>121</v>
+        <v>158</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="45.75">
       <c r="A27" s="4">
         <v>27</v>
       </c>
-      <c r="B27" s="50"/>
+      <c r="B27" s="52"/>
       <c r="C27" s="6" t="s">
-        <v>122</v>
+        <v>159</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="E27" s="18"/>
       <c r="F27" s="18" t="s">
-        <v>124</v>
+        <v>161</v>
       </c>
       <c r="G27" s="14"/>
       <c r="H27" s="14"/>
@@ -3405,35 +3820,35 @@
       <c r="A28" s="4">
         <v>28</v>
       </c>
-      <c r="B28" s="50" t="s">
-        <v>75</v>
-      </c>
-      <c r="C28" s="50" t="s">
-        <v>125</v>
+      <c r="B28" s="52" t="s">
+        <v>112</v>
+      </c>
+      <c r="C28" s="52" t="s">
+        <v>162</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>126</v>
+        <v>163</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>127</v>
+        <v>164</v>
       </c>
       <c r="F28" s="18" t="s">
-        <v>128</v>
+        <v>165</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="H28" s="14" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="I28" s="14" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="J28" s="13" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="K28" s="14" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="L28" s="32"/>
     </row>
@@ -3441,31 +3856,31 @@
       <c r="A29" s="4">
         <v>29</v>
       </c>
-      <c r="B29" s="50"/>
-      <c r="C29" s="50"/>
+      <c r="B29" s="52"/>
+      <c r="C29" s="52"/>
       <c r="D29" s="6" t="s">
-        <v>129</v>
+        <v>166</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="F29" s="18" t="s">
-        <v>130</v>
+        <v>167</v>
       </c>
       <c r="G29" s="33" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="H29" s="33" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="I29" s="33" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="J29" s="33" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="K29" s="33" t="s">
-        <v>131</v>
+        <v>168</v>
       </c>
       <c r="L29" s="15"/>
     </row>
@@ -3473,16 +3888,16 @@
       <c r="A30" s="4">
         <v>30</v>
       </c>
-      <c r="B30" s="50"/>
-      <c r="C30" s="50" t="s">
-        <v>132</v>
+      <c r="B30" s="52"/>
+      <c r="C30" s="52" t="s">
+        <v>169</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="E30" s="18"/>
       <c r="F30" s="18" t="s">
-        <v>134</v>
+        <v>171</v>
       </c>
       <c r="G30" s="14"/>
       <c r="H30" s="14"/>
@@ -3495,14 +3910,14 @@
       <c r="A31" s="4">
         <v>31</v>
       </c>
-      <c r="B31" s="50"/>
-      <c r="C31" s="50"/>
+      <c r="B31" s="52"/>
+      <c r="C31" s="52"/>
       <c r="D31" s="6" t="s">
-        <v>135</v>
+        <v>172</v>
       </c>
       <c r="E31" s="18"/>
       <c r="F31" s="18" t="s">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="G31" s="33"/>
       <c r="H31" s="33"/>
@@ -3515,14 +3930,14 @@
       <c r="A32" s="4">
         <v>32</v>
       </c>
-      <c r="B32" s="50"/>
-      <c r="C32" s="50"/>
+      <c r="B32" s="52"/>
+      <c r="C32" s="52"/>
       <c r="D32" s="6" t="s">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="E32" s="18"/>
       <c r="F32" s="18" t="s">
-        <v>138</v>
+        <v>175</v>
       </c>
       <c r="G32" s="33"/>
       <c r="H32" s="33"/>
@@ -3535,14 +3950,14 @@
       <c r="A33" s="4">
         <v>33</v>
       </c>
-      <c r="B33" s="50"/>
-      <c r="C33" s="50"/>
+      <c r="B33" s="52"/>
+      <c r="C33" s="52"/>
       <c r="D33" s="6" t="s">
-        <v>139</v>
+        <v>176</v>
       </c>
       <c r="E33" s="18"/>
       <c r="F33" s="18" t="s">
-        <v>140</v>
+        <v>177</v>
       </c>
       <c r="G33" s="33"/>
       <c r="H33" s="33"/>
@@ -3555,14 +3970,14 @@
       <c r="A34" s="4">
         <v>34</v>
       </c>
-      <c r="B34" s="50"/>
-      <c r="C34" s="50"/>
+      <c r="B34" s="52"/>
+      <c r="C34" s="52"/>
       <c r="D34" s="6" t="s">
-        <v>141</v>
+        <v>178</v>
       </c>
       <c r="E34" s="18"/>
       <c r="F34" s="18" t="s">
-        <v>142</v>
+        <v>179</v>
       </c>
       <c r="G34" s="33"/>
       <c r="H34" s="33"/>
@@ -3575,16 +3990,16 @@
       <c r="A35" s="4">
         <v>35</v>
       </c>
-      <c r="B35" s="50"/>
+      <c r="B35" s="52"/>
       <c r="C35" s="6" t="s">
-        <v>122</v>
+        <v>159</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="E35" s="18"/>
       <c r="F35" s="18" t="s">
-        <v>143</v>
+        <v>180</v>
       </c>
       <c r="G35" s="33"/>
       <c r="H35" s="33"/>
@@ -3593,22 +4008,22 @@
       <c r="K35" s="33"/>
       <c r="L35" s="15"/>
     </row>
-    <row r="36" spans="1:12" ht="39.75" customHeight="1">
+    <row r="36" spans="1:12">
       <c r="A36" s="4">
         <v>36</v>
       </c>
-      <c r="B36" s="50" t="s">
-        <v>62</v>
-      </c>
-      <c r="C36" s="50" t="s">
-        <v>144</v>
+      <c r="B36" s="52" t="s">
+        <v>99</v>
+      </c>
+      <c r="C36" s="52" t="s">
+        <v>181</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>145</v>
+        <v>182</v>
       </c>
       <c r="E36" s="18"/>
       <c r="F36" s="18" t="s">
-        <v>146</v>
+        <v>183</v>
       </c>
       <c r="G36" s="33"/>
       <c r="H36" s="33"/>
@@ -3617,18 +4032,18 @@
       <c r="K36" s="33"/>
       <c r="L36" s="15"/>
     </row>
-    <row r="37" spans="1:12" ht="39.75" customHeight="1">
+    <row r="37" spans="1:12" ht="30.75">
       <c r="A37" s="4">
         <v>37</v>
       </c>
-      <c r="B37" s="50"/>
-      <c r="C37" s="50"/>
+      <c r="B37" s="52"/>
+      <c r="C37" s="52"/>
       <c r="D37" s="6" t="s">
-        <v>147</v>
+        <v>184</v>
       </c>
       <c r="E37" s="18"/>
       <c r="F37" s="18" t="s">
-        <v>148</v>
+        <v>185</v>
       </c>
       <c r="G37" s="33"/>
       <c r="H37" s="33"/>
@@ -3637,20 +4052,20 @@
       <c r="K37" s="33"/>
       <c r="L37" s="32"/>
     </row>
-    <row r="38" spans="1:12" ht="39.75" customHeight="1">
+    <row r="38" spans="1:12">
       <c r="A38" s="4">
         <v>38</v>
       </c>
-      <c r="B38" s="50"/>
-      <c r="C38" s="50" t="s">
-        <v>149</v>
+      <c r="B38" s="52"/>
+      <c r="C38" s="52" t="s">
+        <v>186</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>150</v>
+        <v>187</v>
       </c>
       <c r="E38" s="18"/>
       <c r="F38" s="18" t="s">
-        <v>151</v>
+        <v>188</v>
       </c>
       <c r="G38" s="33"/>
       <c r="H38" s="33"/>
@@ -3659,38 +4074,36 @@
       <c r="K38" s="33"/>
       <c r="L38" s="32"/>
     </row>
-    <row r="39" spans="1:12" ht="39.75" customHeight="1">
-      <c r="A39" s="4">
-        <v>40</v>
-      </c>
-      <c r="B39" s="50"/>
-      <c r="C39" s="50"/>
+    <row r="39" spans="1:12" ht="30.75">
+      <c r="A39" s="4"/>
+      <c r="B39" s="52"/>
+      <c r="C39" s="52"/>
       <c r="D39" s="6" t="s">
-        <v>152</v>
+        <v>189</v>
       </c>
       <c r="E39" s="18"/>
       <c r="F39" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="14"/>
-      <c r="J39" s="14"/>
-      <c r="K39" s="14"/>
-      <c r="L39" s="15"/>
-    </row>
-    <row r="40" spans="1:12" ht="39.75" customHeight="1">
+        <v>190</v>
+      </c>
+      <c r="G39" s="33"/>
+      <c r="H39" s="33"/>
+      <c r="I39" s="33"/>
+      <c r="J39" s="33"/>
+      <c r="K39" s="33"/>
+      <c r="L39" s="32"/>
+    </row>
+    <row r="40" spans="1:12">
       <c r="A40" s="4">
-        <v>42</v>
-      </c>
-      <c r="B40" s="50"/>
-      <c r="C40" s="50"/>
+        <v>40</v>
+      </c>
+      <c r="B40" s="52"/>
+      <c r="C40" s="52"/>
       <c r="D40" s="6" t="s">
-        <v>154</v>
+        <v>191</v>
       </c>
       <c r="E40" s="18"/>
       <c r="F40" s="18" t="s">
-        <v>155</v>
+        <v>192</v>
       </c>
       <c r="G40" s="14"/>
       <c r="H40" s="14"/>
@@ -3699,18 +4112,16 @@
       <c r="K40" s="14"/>
       <c r="L40" s="15"/>
     </row>
-    <row r="41" spans="1:12" ht="76.5">
-      <c r="A41" s="4">
-        <v>44</v>
-      </c>
-      <c r="B41" s="50"/>
-      <c r="C41" s="50"/>
+    <row r="41" spans="1:12" ht="30.75">
+      <c r="A41" s="4"/>
+      <c r="B41" s="52"/>
+      <c r="C41" s="52"/>
       <c r="D41" s="6" t="s">
-        <v>156</v>
+        <v>189</v>
       </c>
       <c r="E41" s="18"/>
       <c r="F41" s="18" t="s">
-        <v>157</v>
+        <v>193</v>
       </c>
       <c r="G41" s="14"/>
       <c r="H41" s="14"/>
@@ -3719,20 +4130,18 @@
       <c r="K41" s="14"/>
       <c r="L41" s="15"/>
     </row>
-    <row r="42" spans="1:12" ht="54.75" customHeight="1">
+    <row r="42" spans="1:12">
       <c r="A42" s="4">
-        <v>46</v>
-      </c>
-      <c r="B42" s="50"/>
-      <c r="C42" s="50" t="s">
-        <v>158</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="B42" s="52"/>
+      <c r="C42" s="52"/>
       <c r="D42" s="6" t="s">
-        <v>159</v>
+        <v>194</v>
       </c>
       <c r="E42" s="18"/>
       <c r="F42" s="18" t="s">
-        <v>160</v>
+        <v>195</v>
       </c>
       <c r="G42" s="14"/>
       <c r="H42" s="14"/>
@@ -3741,18 +4150,16 @@
       <c r="K42" s="14"/>
       <c r="L42" s="15"/>
     </row>
-    <row r="43" spans="1:12" ht="54.75" customHeight="1">
-      <c r="A43" s="4">
-        <v>47</v>
-      </c>
-      <c r="B43" s="50"/>
-      <c r="C43" s="50"/>
+    <row r="43" spans="1:12" ht="30.75">
+      <c r="A43" s="4"/>
+      <c r="B43" s="52"/>
+      <c r="C43" s="52"/>
       <c r="D43" s="6" t="s">
-        <v>161</v>
+        <v>189</v>
       </c>
       <c r="E43" s="18"/>
       <c r="F43" s="18" t="s">
-        <v>162</v>
+        <v>196</v>
       </c>
       <c r="G43" s="14"/>
       <c r="H43" s="14"/>
@@ -3761,18 +4168,18 @@
       <c r="K43" s="14"/>
       <c r="L43" s="15"/>
     </row>
-    <row r="44" spans="1:12" ht="54.75" customHeight="1">
+    <row r="44" spans="1:12" ht="76.5" hidden="1">
       <c r="A44" s="4">
-        <v>48</v>
-      </c>
-      <c r="B44" s="50"/>
-      <c r="C44" s="50"/>
+        <v>44</v>
+      </c>
+      <c r="B44" s="52"/>
+      <c r="C44" s="52"/>
       <c r="D44" s="6" t="s">
-        <v>163</v>
+        <v>197</v>
       </c>
       <c r="E44" s="18"/>
       <c r="F44" s="18" t="s">
-        <v>164</v>
+        <v>198</v>
       </c>
       <c r="G44" s="14"/>
       <c r="H44" s="14"/>
@@ -3781,18 +4188,20 @@
       <c r="K44" s="14"/>
       <c r="L44" s="15"/>
     </row>
-    <row r="45" spans="1:12" ht="54.75" customHeight="1">
+    <row r="45" spans="1:12" ht="30.75">
       <c r="A45" s="4">
-        <v>49</v>
-      </c>
-      <c r="B45" s="50"/>
-      <c r="C45" s="50"/>
+        <v>47</v>
+      </c>
+      <c r="B45" s="52"/>
+      <c r="C45" s="52" t="s">
+        <v>199</v>
+      </c>
       <c r="D45" s="6" t="s">
-        <v>165</v>
+        <v>200</v>
       </c>
       <c r="E45" s="18"/>
       <c r="F45" s="18" t="s">
-        <v>166</v>
+        <v>201</v>
       </c>
       <c r="G45" s="14"/>
       <c r="H45" s="14"/>
@@ -3801,22 +4210,18 @@
       <c r="K45" s="14"/>
       <c r="L45" s="15"/>
     </row>
-    <row r="46" spans="1:12" ht="54.75" customHeight="1">
+    <row r="46" spans="1:12">
       <c r="A46" s="4">
-        <v>50</v>
-      </c>
-      <c r="B46" s="50" t="s">
-        <v>167</v>
-      </c>
-      <c r="C46" s="50" t="s">
-        <v>168</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="B46" s="52"/>
+      <c r="C46" s="52"/>
       <c r="D46" s="6" t="s">
-        <v>126</v>
+        <v>202</v>
       </c>
       <c r="E46" s="18"/>
       <c r="F46" s="18" t="s">
-        <v>169</v>
+        <v>203</v>
       </c>
       <c r="G46" s="14"/>
       <c r="H46" s="14"/>
@@ -3825,18 +4230,18 @@
       <c r="K46" s="14"/>
       <c r="L46" s="15"/>
     </row>
-    <row r="47" spans="1:12" ht="45.75">
+    <row r="47" spans="1:12" ht="76.5">
       <c r="A47" s="4">
-        <v>51</v>
-      </c>
-      <c r="B47" s="50"/>
-      <c r="C47" s="50"/>
+        <v>49</v>
+      </c>
+      <c r="B47" s="52"/>
+      <c r="C47" s="52"/>
       <c r="D47" s="6" t="s">
-        <v>170</v>
+        <v>204</v>
       </c>
       <c r="E47" s="18"/>
       <c r="F47" s="18" t="s">
-        <v>171</v>
+        <v>205</v>
       </c>
       <c r="G47" s="14"/>
       <c r="H47" s="14"/>
@@ -3845,20 +4250,22 @@
       <c r="K47" s="14"/>
       <c r="L47" s="15"/>
     </row>
-    <row r="48" spans="1:12" ht="30.75" customHeight="1">
+    <row r="48" spans="1:12" ht="54.75" customHeight="1">
       <c r="A48" s="4">
-        <v>54</v>
-      </c>
-      <c r="B48" s="50"/>
-      <c r="C48" s="50" t="s">
-        <v>172</v>
+        <v>50</v>
+      </c>
+      <c r="B48" s="52" t="s">
+        <v>206</v>
+      </c>
+      <c r="C48" s="52" t="s">
+        <v>207</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="E48" s="18"/>
       <c r="F48" s="18" t="s">
-        <v>174</v>
+        <v>208</v>
       </c>
       <c r="G48" s="14"/>
       <c r="H48" s="14"/>
@@ -3867,468 +4274,470 @@
       <c r="K48" s="14"/>
       <c r="L48" s="15"/>
     </row>
-    <row r="49" spans="1:12" ht="43.5">
+    <row r="49" spans="1:12" ht="45.75">
       <c r="A49" s="4">
-        <v>55</v>
-      </c>
-      <c r="B49" s="50"/>
-      <c r="C49" s="50"/>
+        <v>51</v>
+      </c>
+      <c r="B49" s="52"/>
+      <c r="C49" s="52"/>
       <c r="D49" s="6" t="s">
-        <v>175</v>
+        <v>209</v>
       </c>
       <c r="E49" s="18"/>
       <c r="F49" s="18" t="s">
-        <v>176</v>
-      </c>
-      <c r="G49" s="33" t="s">
-        <v>177</v>
-      </c>
-      <c r="H49" s="33" t="s">
-        <v>177</v>
-      </c>
-      <c r="I49" s="33" t="s">
-        <v>177</v>
-      </c>
-      <c r="J49" s="33" t="s">
-        <v>177</v>
-      </c>
-      <c r="K49" s="14" t="s">
-        <v>178</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="G49" s="14"/>
+      <c r="H49" s="14"/>
+      <c r="I49" s="14"/>
+      <c r="J49" s="14"/>
+      <c r="K49" s="14"/>
       <c r="L49" s="15"/>
     </row>
-    <row r="50" spans="1:12" ht="28.5">
+    <row r="50" spans="1:12" ht="30.75" customHeight="1">
       <c r="A50" s="4">
-        <v>56</v>
-      </c>
-      <c r="B50" s="50"/>
-      <c r="C50" s="50"/>
+        <v>54</v>
+      </c>
+      <c r="B50" s="52"/>
+      <c r="C50" s="52" t="s">
+        <v>211</v>
+      </c>
       <c r="D50" s="6" t="s">
-        <v>179</v>
+        <v>212</v>
       </c>
       <c r="E50" s="18"/>
       <c r="F50" s="18" t="s">
-        <v>180</v>
-      </c>
-      <c r="G50" s="34" t="s">
-        <v>181</v>
-      </c>
-      <c r="H50" s="34" t="s">
-        <v>181</v>
-      </c>
-      <c r="I50" s="34" t="s">
-        <v>181</v>
-      </c>
-      <c r="J50" s="34" t="s">
-        <v>181</v>
-      </c>
-      <c r="K50" s="14" t="s">
-        <v>178</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="G50" s="14"/>
+      <c r="H50" s="14"/>
+      <c r="I50" s="14"/>
+      <c r="J50" s="14"/>
+      <c r="K50" s="14"/>
       <c r="L50" s="15"/>
     </row>
-    <row r="51" spans="1:12">
+    <row r="51" spans="1:12" ht="43.5">
       <c r="A51" s="4">
-        <v>57</v>
-      </c>
-      <c r="B51" s="50"/>
-      <c r="C51" s="50"/>
+        <v>55</v>
+      </c>
+      <c r="B51" s="52"/>
+      <c r="C51" s="52"/>
       <c r="D51" s="6" t="s">
-        <v>182</v>
+        <v>214</v>
       </c>
       <c r="E51" s="18"/>
       <c r="F51" s="18" t="s">
-        <v>183</v>
+        <v>215</v>
       </c>
       <c r="G51" s="33" t="s">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="H51" s="33" t="s">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="I51" s="33" t="s">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="J51" s="33" t="s">
-        <v>184</v>
-      </c>
-      <c r="K51" s="33"/>
+        <v>216</v>
+      </c>
+      <c r="K51" s="14" t="s">
+        <v>217</v>
+      </c>
       <c r="L51" s="15"/>
     </row>
-    <row r="52" spans="1:12">
+    <row r="52" spans="1:12" ht="28.5">
       <c r="A52" s="4">
-        <v>58</v>
-      </c>
-      <c r="B52" s="50"/>
-      <c r="C52" s="50"/>
+        <v>56</v>
+      </c>
+      <c r="B52" s="52"/>
+      <c r="C52" s="52"/>
       <c r="D52" s="6" t="s">
-        <v>185</v>
+        <v>218</v>
       </c>
       <c r="E52" s="18"/>
       <c r="F52" s="18" t="s">
-        <v>186</v>
-      </c>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="14"/>
-      <c r="J52" s="14"/>
-      <c r="K52" s="14"/>
-      <c r="L52" s="32"/>
+        <v>219</v>
+      </c>
+      <c r="G52" s="34" t="s">
+        <v>220</v>
+      </c>
+      <c r="H52" s="34" t="s">
+        <v>220</v>
+      </c>
+      <c r="I52" s="34" t="s">
+        <v>220</v>
+      </c>
+      <c r="J52" s="34" t="s">
+        <v>220</v>
+      </c>
+      <c r="K52" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="L52" s="15"/>
     </row>
     <row r="53" spans="1:12">
       <c r="A53" s="4">
-        <v>59</v>
-      </c>
-      <c r="B53" s="50"/>
-      <c r="C53" s="50"/>
+        <v>57</v>
+      </c>
+      <c r="B53" s="52"/>
+      <c r="C53" s="52"/>
       <c r="D53" s="6" t="s">
-        <v>187</v>
+        <v>221</v>
       </c>
       <c r="E53" s="18"/>
       <c r="F53" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="G53" s="36" t="s">
-        <v>189</v>
-      </c>
-      <c r="H53" s="36" t="s">
-        <v>189</v>
-      </c>
-      <c r="I53" s="36" t="s">
-        <v>189</v>
-      </c>
-      <c r="J53" s="36" t="s">
-        <v>189</v>
-      </c>
-      <c r="K53" s="14"/>
+        <v>222</v>
+      </c>
+      <c r="G53" s="33" t="s">
+        <v>223</v>
+      </c>
+      <c r="H53" s="33" t="s">
+        <v>223</v>
+      </c>
+      <c r="I53" s="33" t="s">
+        <v>223</v>
+      </c>
+      <c r="J53" s="33" t="s">
+        <v>223</v>
+      </c>
+      <c r="K53" s="33"/>
       <c r="L53" s="15"/>
     </row>
-    <row r="54" spans="1:12" ht="43.5">
+    <row r="54" spans="1:12">
       <c r="A54" s="4">
-        <v>60</v>
-      </c>
-      <c r="B54" s="50"/>
-      <c r="C54" s="50" t="s">
-        <v>190</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="B54" s="52"/>
+      <c r="C54" s="52"/>
       <c r="D54" s="6" t="s">
-        <v>191</v>
+        <v>224</v>
       </c>
       <c r="E54" s="18"/>
       <c r="F54" s="18" t="s">
-        <v>192</v>
-      </c>
-      <c r="G54" s="34" t="s">
-        <v>193</v>
-      </c>
-      <c r="H54" s="34" t="s">
-        <v>194</v>
-      </c>
-      <c r="I54" s="34" t="s">
-        <v>194</v>
-      </c>
-      <c r="J54" s="34" t="s">
-        <v>193</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="G54" s="14"/>
+      <c r="H54" s="14"/>
+      <c r="I54" s="14"/>
+      <c r="J54" s="14"/>
       <c r="K54" s="14"/>
-      <c r="L54" s="15"/>
+      <c r="L54" s="32"/>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" s="4">
-        <v>61</v>
-      </c>
-      <c r="B55" s="50"/>
-      <c r="C55" s="50"/>
+        <v>59</v>
+      </c>
+      <c r="B55" s="52"/>
+      <c r="C55" s="52"/>
       <c r="D55" s="6" t="s">
-        <v>195</v>
+        <v>226</v>
       </c>
       <c r="E55" s="18"/>
-      <c r="F55" s="20" t="s">
-        <v>196</v>
-      </c>
-      <c r="G55" s="13"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="14"/>
-      <c r="J55" s="13"/>
+      <c r="F55" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="G55" s="36" t="s">
+        <v>228</v>
+      </c>
+      <c r="H55" s="36" t="s">
+        <v>228</v>
+      </c>
+      <c r="I55" s="36" t="s">
+        <v>228</v>
+      </c>
+      <c r="J55" s="36" t="s">
+        <v>228</v>
+      </c>
       <c r="K55" s="14"/>
       <c r="L55" s="15"/>
     </row>
-    <row r="56" spans="1:12">
+    <row r="56" spans="1:12" ht="43.5">
       <c r="A56" s="4">
-        <v>62</v>
-      </c>
-      <c r="B56" s="50"/>
-      <c r="C56" s="50"/>
+        <v>60</v>
+      </c>
+      <c r="B56" s="52"/>
+      <c r="C56" s="52" t="s">
+        <v>229</v>
+      </c>
       <c r="D56" s="6" t="s">
-        <v>197</v>
+        <v>230</v>
       </c>
       <c r="E56" s="18"/>
       <c r="F56" s="18" t="s">
-        <v>198</v>
-      </c>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="14"/>
-      <c r="J56" s="14"/>
+        <v>231</v>
+      </c>
+      <c r="G56" s="34" t="s">
+        <v>232</v>
+      </c>
+      <c r="H56" s="34" t="s">
+        <v>233</v>
+      </c>
+      <c r="I56" s="34" t="s">
+        <v>233</v>
+      </c>
+      <c r="J56" s="34" t="s">
+        <v>232</v>
+      </c>
       <c r="K56" s="14"/>
       <c r="L56" s="15"/>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" s="4">
-        <v>63</v>
-      </c>
-      <c r="B57" s="50"/>
-      <c r="C57" s="50"/>
+        <v>61</v>
+      </c>
+      <c r="B57" s="52"/>
+      <c r="C57" s="52"/>
       <c r="D57" s="6" t="s">
-        <v>199</v>
+        <v>234</v>
       </c>
       <c r="E57" s="18"/>
-      <c r="F57" s="18" t="s">
-        <v>200</v>
-      </c>
-      <c r="G57" s="14"/>
+      <c r="F57" s="20" t="s">
+        <v>235</v>
+      </c>
+      <c r="G57" s="13"/>
       <c r="H57" s="14"/>
       <c r="I57" s="14"/>
-      <c r="J57" s="14"/>
+      <c r="J57" s="13"/>
       <c r="K57" s="14"/>
       <c r="L57" s="15"/>
     </row>
-    <row r="58" spans="1:12" ht="28.5">
+    <row r="58" spans="1:12">
       <c r="A58" s="4">
-        <v>64</v>
-      </c>
-      <c r="B58" s="50"/>
-      <c r="C58" s="50"/>
+        <v>62</v>
+      </c>
+      <c r="B58" s="52"/>
+      <c r="C58" s="52"/>
       <c r="D58" s="6" t="s">
-        <v>201</v>
+        <v>236</v>
       </c>
       <c r="E58" s="18"/>
       <c r="F58" s="18" t="s">
-        <v>202</v>
-      </c>
-      <c r="G58" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="H58" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="I58" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="J58" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="K58" s="33" t="s">
-        <v>49</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="G58" s="14"/>
+      <c r="H58" s="14"/>
+      <c r="I58" s="14"/>
+      <c r="J58" s="14"/>
+      <c r="K58" s="14"/>
       <c r="L58" s="15"/>
     </row>
-    <row r="59" spans="1:12" ht="45.75">
+    <row r="59" spans="1:12">
       <c r="A59" s="4">
-        <v>65</v>
-      </c>
-      <c r="B59" s="50"/>
-      <c r="C59" s="50" t="s">
-        <v>203</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="B59" s="52"/>
+      <c r="C59" s="52"/>
       <c r="D59" s="6" t="s">
-        <v>204</v>
+        <v>238</v>
       </c>
       <c r="E59" s="18"/>
       <c r="F59" s="18" t="s">
-        <v>205</v>
-      </c>
-      <c r="G59" s="33" t="s">
-        <v>206</v>
-      </c>
-      <c r="H59" s="33" t="s">
-        <v>206</v>
-      </c>
-      <c r="I59" s="33" t="s">
-        <v>206</v>
-      </c>
-      <c r="J59" s="33" t="s">
-        <v>206</v>
-      </c>
-      <c r="K59" s="33" t="s">
-        <v>207</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="G59" s="14"/>
+      <c r="H59" s="14"/>
+      <c r="I59" s="14"/>
+      <c r="J59" s="14"/>
+      <c r="K59" s="14"/>
       <c r="L59" s="15"/>
     </row>
-    <row r="60" spans="1:12">
+    <row r="60" spans="1:12" ht="28.5">
       <c r="A60" s="4">
-        <v>66</v>
-      </c>
-      <c r="B60" s="50"/>
-      <c r="C60" s="50"/>
+        <v>64</v>
+      </c>
+      <c r="B60" s="52"/>
+      <c r="C60" s="52"/>
       <c r="D60" s="6" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="E60" s="18"/>
       <c r="F60" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="G60" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="H60" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="I60" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="J60" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="K60" s="33"/>
-      <c r="L60" s="32"/>
-    </row>
-    <row r="61" spans="1:12">
+        <v>241</v>
+      </c>
+      <c r="G60" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="H60" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="I60" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="J60" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="K60" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="L60" s="15"/>
+    </row>
+    <row r="61" spans="1:12" ht="45.75">
       <c r="A61" s="4">
-        <v>67</v>
-      </c>
-      <c r="B61" s="50"/>
-      <c r="C61" s="50"/>
+        <v>65</v>
+      </c>
+      <c r="B61" s="52"/>
+      <c r="C61" s="52" t="s">
+        <v>242</v>
+      </c>
       <c r="D61" s="6" t="s">
-        <v>210</v>
+        <v>243</v>
       </c>
       <c r="E61" s="18"/>
       <c r="F61" s="18" t="s">
-        <v>211</v>
-      </c>
-      <c r="G61" s="33"/>
-      <c r="H61" s="33"/>
-      <c r="I61" s="33"/>
-      <c r="J61" s="33"/>
-      <c r="K61" s="33"/>
+        <v>244</v>
+      </c>
+      <c r="G61" s="33" t="s">
+        <v>245</v>
+      </c>
+      <c r="H61" s="33" t="s">
+        <v>245</v>
+      </c>
+      <c r="I61" s="33" t="s">
+        <v>245</v>
+      </c>
+      <c r="J61" s="33" t="s">
+        <v>245</v>
+      </c>
+      <c r="K61" s="33" t="s">
+        <v>246</v>
+      </c>
       <c r="L61" s="15"/>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" s="4">
-        <v>68</v>
-      </c>
-      <c r="B62" s="50"/>
-      <c r="C62" s="50"/>
+        <v>66</v>
+      </c>
+      <c r="B62" s="52"/>
+      <c r="C62" s="52"/>
       <c r="D62" s="6" t="s">
-        <v>212</v>
+        <v>247</v>
       </c>
       <c r="E62" s="18"/>
       <c r="F62" s="18" t="s">
-        <v>213</v>
+        <v>138</v>
       </c>
       <c r="G62" s="33" t="s">
-        <v>214</v>
+        <v>248</v>
       </c>
       <c r="H62" s="33" t="s">
-        <v>215</v>
+        <v>248</v>
       </c>
       <c r="I62" s="33" t="s">
-        <v>215</v>
+        <v>248</v>
       </c>
       <c r="J62" s="33" t="s">
-        <v>214</v>
-      </c>
-      <c r="K62" s="14"/>
-      <c r="L62" s="15"/>
+        <v>248</v>
+      </c>
+      <c r="K62" s="33"/>
+      <c r="L62" s="32"/>
     </row>
     <row r="63" spans="1:12">
       <c r="A63" s="4">
-        <v>69</v>
-      </c>
-      <c r="B63" s="50"/>
-      <c r="C63" s="50"/>
+        <v>67</v>
+      </c>
+      <c r="B63" s="52"/>
+      <c r="C63" s="52"/>
       <c r="D63" s="6" t="s">
-        <v>216</v>
+        <v>249</v>
       </c>
       <c r="E63" s="18"/>
       <c r="F63" s="18" t="s">
-        <v>217</v>
+        <v>250</v>
       </c>
       <c r="G63" s="33"/>
       <c r="H63" s="33"/>
       <c r="I63" s="33"/>
       <c r="J63" s="33"/>
       <c r="K63" s="33"/>
-      <c r="L63" s="32"/>
-    </row>
-    <row r="64" spans="1:12" ht="45.75">
+      <c r="L63" s="15"/>
+    </row>
+    <row r="64" spans="1:12">
       <c r="A64" s="4">
-        <v>70</v>
-      </c>
-      <c r="B64" s="50"/>
-      <c r="C64" s="6" t="s">
-        <v>218</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="B64" s="52"/>
+      <c r="C64" s="52"/>
       <c r="D64" s="6" t="s">
-        <v>123</v>
+        <v>251</v>
       </c>
       <c r="E64" s="18"/>
       <c r="F64" s="18" t="s">
-        <v>219</v>
-      </c>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
-      <c r="I64" s="14"/>
-      <c r="J64" s="14"/>
+        <v>252</v>
+      </c>
+      <c r="G64" s="33" t="s">
+        <v>253</v>
+      </c>
+      <c r="H64" s="33" t="s">
+        <v>254</v>
+      </c>
+      <c r="I64" s="33" t="s">
+        <v>254</v>
+      </c>
+      <c r="J64" s="33" t="s">
+        <v>253</v>
+      </c>
       <c r="K64" s="14"/>
       <c r="L64" s="15"/>
     </row>
-    <row r="65" spans="1:12" ht="54" customHeight="1">
+    <row r="65" spans="1:12">
       <c r="A65" s="4">
-        <v>71</v>
-      </c>
-      <c r="B65" s="50" t="s">
-        <v>220</v>
-      </c>
-      <c r="C65" s="50" t="s">
-        <v>221</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="B65" s="52"/>
+      <c r="C65" s="52"/>
       <c r="D65" s="6" t="s">
-        <v>222</v>
+        <v>255</v>
       </c>
       <c r="E65" s="18"/>
       <c r="F65" s="18" t="s">
-        <v>223</v>
+        <v>256</v>
       </c>
       <c r="G65" s="33"/>
       <c r="H65" s="33"/>
       <c r="I65" s="33"/>
       <c r="J65" s="33"/>
       <c r="K65" s="33"/>
-      <c r="L65" s="15"/>
-    </row>
-    <row r="66" spans="1:12" ht="54" customHeight="1">
+      <c r="L65" s="32"/>
+    </row>
+    <row r="66" spans="1:12" ht="45.75">
       <c r="A66" s="4">
-        <v>72</v>
-      </c>
-      <c r="B66" s="50"/>
-      <c r="C66" s="50"/>
+        <v>70</v>
+      </c>
+      <c r="B66" s="52"/>
+      <c r="C66" s="6" t="s">
+        <v>257</v>
+      </c>
       <c r="D66" s="6" t="s">
-        <v>224</v>
+        <v>160</v>
       </c>
       <c r="E66" s="18"/>
       <c r="F66" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="G66" s="33"/>
-      <c r="H66" s="33"/>
-      <c r="I66" s="33"/>
-      <c r="J66" s="33"/>
-      <c r="K66" s="33"/>
+        <v>258</v>
+      </c>
+      <c r="G66" s="14"/>
+      <c r="H66" s="14"/>
+      <c r="I66" s="14"/>
+      <c r="J66" s="14"/>
+      <c r="K66" s="14"/>
       <c r="L66" s="15"/>
     </row>
     <row r="67" spans="1:12" ht="54" customHeight="1">
       <c r="A67" s="4">
-        <v>73</v>
-      </c>
-      <c r="B67" s="50"/>
-      <c r="C67" s="50"/>
+        <v>71</v>
+      </c>
+      <c r="B67" s="52" t="s">
+        <v>259</v>
+      </c>
+      <c r="C67" s="52" t="s">
+        <v>260</v>
+      </c>
       <c r="D67" s="6" t="s">
-        <v>226</v>
+        <v>261</v>
       </c>
       <c r="E67" s="18"/>
       <c r="F67" s="18" t="s">
-        <v>227</v>
+        <v>262</v>
       </c>
       <c r="G67" s="33"/>
       <c r="H67" s="33"/>
@@ -4339,18 +4748,16 @@
     </row>
     <row r="68" spans="1:12" ht="54" customHeight="1">
       <c r="A68" s="4">
-        <v>74</v>
-      </c>
-      <c r="B68" s="50"/>
-      <c r="C68" s="50" t="s">
-        <v>228</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="B68" s="52"/>
+      <c r="C68" s="52"/>
       <c r="D68" s="6" t="s">
-        <v>229</v>
+        <v>263</v>
       </c>
       <c r="E68" s="18"/>
       <c r="F68" s="18" t="s">
-        <v>230</v>
+        <v>264</v>
       </c>
       <c r="G68" s="33"/>
       <c r="H68" s="33"/>
@@ -4361,58 +4768,58 @@
     </row>
     <row r="69" spans="1:12" ht="54" customHeight="1">
       <c r="A69" s="4">
-        <v>75</v>
-      </c>
-      <c r="B69" s="50"/>
-      <c r="C69" s="50"/>
+        <v>73</v>
+      </c>
+      <c r="B69" s="52"/>
+      <c r="C69" s="52"/>
       <c r="D69" s="6" t="s">
-        <v>231</v>
+        <v>265</v>
       </c>
       <c r="E69" s="18"/>
       <c r="F69" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="G69" s="14"/>
-      <c r="H69" s="14"/>
-      <c r="I69" s="14"/>
-      <c r="J69" s="14"/>
-      <c r="K69" s="14"/>
+        <v>266</v>
+      </c>
+      <c r="G69" s="33"/>
+      <c r="H69" s="33"/>
+      <c r="I69" s="33"/>
+      <c r="J69" s="33"/>
+      <c r="K69" s="33"/>
       <c r="L69" s="15"/>
     </row>
     <row r="70" spans="1:12" ht="54" customHeight="1">
       <c r="A70" s="4">
-        <v>76</v>
-      </c>
-      <c r="B70" s="50"/>
-      <c r="C70" s="50"/>
+        <v>74</v>
+      </c>
+      <c r="B70" s="52"/>
+      <c r="C70" s="52" t="s">
+        <v>267</v>
+      </c>
       <c r="D70" s="6" t="s">
-        <v>233</v>
+        <v>268</v>
       </c>
       <c r="E70" s="18"/>
       <c r="F70" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="G70" s="14"/>
-      <c r="H70" s="14"/>
-      <c r="I70" s="14"/>
-      <c r="J70" s="14"/>
-      <c r="K70" s="14"/>
+        <v>269</v>
+      </c>
+      <c r="G70" s="33"/>
+      <c r="H70" s="33"/>
+      <c r="I70" s="33"/>
+      <c r="J70" s="33"/>
+      <c r="K70" s="33"/>
       <c r="L70" s="15"/>
     </row>
     <row r="71" spans="1:12" ht="54" customHeight="1">
       <c r="A71" s="4">
-        <v>77</v>
-      </c>
-      <c r="B71" s="50"/>
-      <c r="C71" s="50" t="s">
-        <v>235</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="B71" s="52"/>
+      <c r="C71" s="52"/>
       <c r="D71" s="6" t="s">
-        <v>236</v>
+        <v>270</v>
       </c>
       <c r="E71" s="18"/>
       <c r="F71" s="18" t="s">
-        <v>237</v>
+        <v>271</v>
       </c>
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
@@ -4423,16 +4830,16 @@
     </row>
     <row r="72" spans="1:12" ht="54" customHeight="1">
       <c r="A72" s="4">
-        <v>78</v>
-      </c>
-      <c r="B72" s="50"/>
-      <c r="C72" s="50"/>
+        <v>76</v>
+      </c>
+      <c r="B72" s="52"/>
+      <c r="C72" s="52"/>
       <c r="D72" s="6" t="s">
-        <v>238</v>
+        <v>272</v>
       </c>
       <c r="E72" s="18"/>
       <c r="F72" s="18" t="s">
-        <v>239</v>
+        <v>273</v>
       </c>
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
@@ -4443,18 +4850,18 @@
     </row>
     <row r="73" spans="1:12" ht="54" customHeight="1">
       <c r="A73" s="4">
-        <v>79</v>
-      </c>
-      <c r="B73" s="50"/>
-      <c r="C73" s="50" t="s">
-        <v>240</v>
+        <v>77</v>
+      </c>
+      <c r="B73" s="52"/>
+      <c r="C73" s="52" t="s">
+        <v>274</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>241</v>
+        <v>275</v>
       </c>
       <c r="E73" s="18"/>
       <c r="F73" s="18" t="s">
-        <v>242</v>
+        <v>276</v>
       </c>
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
@@ -4465,16 +4872,16 @@
     </row>
     <row r="74" spans="1:12" ht="54" customHeight="1">
       <c r="A74" s="4">
-        <v>80</v>
-      </c>
-      <c r="B74" s="50"/>
-      <c r="C74" s="50"/>
+        <v>78</v>
+      </c>
+      <c r="B74" s="52"/>
+      <c r="C74" s="52"/>
       <c r="D74" s="6" t="s">
-        <v>243</v>
+        <v>277</v>
       </c>
       <c r="E74" s="18"/>
-      <c r="F74" s="21" t="s">
-        <v>244</v>
+      <c r="F74" s="18" t="s">
+        <v>278</v>
       </c>
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
@@ -4483,22 +4890,20 @@
       <c r="K74" s="14"/>
       <c r="L74" s="15"/>
     </row>
-    <row r="75" spans="1:12" ht="71.25" customHeight="1">
+    <row r="75" spans="1:12" ht="54" customHeight="1">
       <c r="A75" s="4">
-        <v>81</v>
-      </c>
-      <c r="B75" s="50" t="s">
-        <v>65</v>
-      </c>
-      <c r="C75" s="50" t="s">
-        <v>245</v>
+        <v>79</v>
+      </c>
+      <c r="B75" s="52"/>
+      <c r="C75" s="6" t="s">
+        <v>279</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>246</v>
+        <v>280</v>
       </c>
       <c r="E75" s="18"/>
       <c r="F75" s="18" t="s">
-        <v>247</v>
+        <v>281</v>
       </c>
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
@@ -4507,18 +4912,22 @@
       <c r="K75" s="14"/>
       <c r="L75" s="15"/>
     </row>
-    <row r="76" spans="1:12" ht="94.5" customHeight="1">
+    <row r="76" spans="1:12" ht="71.25" customHeight="1">
       <c r="A76" s="4">
-        <v>82</v>
-      </c>
-      <c r="B76" s="50"/>
-      <c r="C76" s="50"/>
+        <v>81</v>
+      </c>
+      <c r="B76" s="52" t="s">
+        <v>102</v>
+      </c>
+      <c r="C76" s="52" t="s">
+        <v>282</v>
+      </c>
       <c r="D76" s="6" t="s">
-        <v>248</v>
+        <v>283</v>
       </c>
       <c r="E76" s="18"/>
       <c r="F76" s="18" t="s">
-        <v>249</v>
+        <v>284</v>
       </c>
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
@@ -4527,18 +4936,18 @@
       <c r="K76" s="14"/>
       <c r="L76" s="15"/>
     </row>
-    <row r="77" spans="1:12" ht="71.25" customHeight="1">
+    <row r="77" spans="1:12" ht="94.5" customHeight="1">
       <c r="A77" s="4">
-        <v>83</v>
-      </c>
-      <c r="B77" s="50"/>
-      <c r="C77" s="50"/>
+        <v>82</v>
+      </c>
+      <c r="B77" s="52"/>
+      <c r="C77" s="52"/>
       <c r="D77" s="6" t="s">
-        <v>250</v>
+        <v>285</v>
       </c>
       <c r="E77" s="18"/>
       <c r="F77" s="18" t="s">
-        <v>251</v>
+        <v>286</v>
       </c>
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
@@ -4547,178 +4956,174 @@
       <c r="K77" s="14"/>
       <c r="L77" s="15"/>
     </row>
-    <row r="78" spans="1:12" ht="121.5">
+    <row r="78" spans="1:12" ht="71.25" customHeight="1">
       <c r="A78" s="4">
+        <v>83</v>
+      </c>
+      <c r="B78" s="52"/>
+      <c r="C78" s="52"/>
+      <c r="D78" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="E78" s="18"/>
+      <c r="F78" s="18" t="s">
+        <v>288</v>
+      </c>
+      <c r="G78" s="14"/>
+      <c r="H78" s="14"/>
+      <c r="I78" s="14"/>
+      <c r="J78" s="14"/>
+      <c r="K78" s="14"/>
+      <c r="L78" s="15"/>
+    </row>
+    <row r="79" spans="1:12" ht="244.5">
+      <c r="A79" s="4">
         <v>84</v>
       </c>
-      <c r="B78" s="50"/>
-      <c r="C78" s="50" t="s">
-        <v>252</v>
-      </c>
-      <c r="D78" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="E78" s="18"/>
-      <c r="F78" s="21" t="s">
-        <v>254</v>
-      </c>
-      <c r="G78" s="13" t="s">
-        <v>255</v>
-      </c>
-      <c r="H78" s="13" t="s">
-        <v>256</v>
-      </c>
-      <c r="I78" s="13" t="s">
-        <v>257</v>
-      </c>
-      <c r="J78" s="13" t="s">
-        <v>255</v>
-      </c>
-      <c r="K78" s="13" t="s">
-        <v>258</v>
-      </c>
-      <c r="L78" s="15"/>
-    </row>
-    <row r="79" spans="1:12" ht="71.25" customHeight="1">
-      <c r="A79" s="4">
-        <v>85</v>
-      </c>
-      <c r="B79" s="50"/>
-      <c r="C79" s="50"/>
+      <c r="B79" s="52"/>
+      <c r="C79" s="52" t="s">
+        <v>289</v>
+      </c>
       <c r="D79" s="6" t="s">
-        <v>259</v>
+        <v>290</v>
       </c>
       <c r="E79" s="18"/>
-      <c r="F79" s="18" t="s">
-        <v>260</v>
-      </c>
-      <c r="G79" s="14"/>
-      <c r="H79" s="14"/>
-      <c r="I79" s="14"/>
-      <c r="J79" s="14"/>
-      <c r="K79" s="14"/>
-      <c r="L79" s="32"/>
+      <c r="F79" s="21" t="s">
+        <v>291</v>
+      </c>
+      <c r="G79" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="H79" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="I79" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="J79" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="K79" s="13" t="s">
+        <v>295</v>
+      </c>
+      <c r="L79" s="15"/>
     </row>
     <row r="80" spans="1:12" ht="71.25" customHeight="1">
       <c r="A80" s="4">
-        <v>86</v>
-      </c>
-      <c r="B80" s="50"/>
-      <c r="C80" s="50"/>
+        <v>85</v>
+      </c>
+      <c r="B80" s="52"/>
+      <c r="C80" s="52"/>
       <c r="D80" s="6" t="s">
-        <v>261</v>
+        <v>296</v>
       </c>
       <c r="E80" s="18"/>
       <c r="F80" s="18" t="s">
-        <v>262</v>
+        <v>297</v>
       </c>
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="14"/>
       <c r="J80" s="14"/>
       <c r="K80" s="14"/>
-      <c r="L80" s="15"/>
+      <c r="L80" s="32"/>
     </row>
     <row r="81" spans="1:12" ht="71.25" customHeight="1">
       <c r="A81" s="4">
-        <v>87</v>
-      </c>
-      <c r="B81" s="50"/>
-      <c r="C81" s="50" t="s">
-        <v>263</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="B81" s="52"/>
+      <c r="C81" s="52"/>
       <c r="D81" s="6" t="s">
-        <v>264</v>
+        <v>298</v>
       </c>
       <c r="E81" s="18"/>
       <c r="F81" s="18" t="s">
-        <v>265</v>
-      </c>
-      <c r="G81" s="33"/>
-      <c r="H81" s="33"/>
-      <c r="I81" s="33"/>
-      <c r="J81" s="33"/>
-      <c r="K81" s="33"/>
-      <c r="L81" s="32"/>
+        <v>299</v>
+      </c>
+      <c r="G81" s="14"/>
+      <c r="H81" s="14"/>
+      <c r="I81" s="14"/>
+      <c r="J81" s="14"/>
+      <c r="K81" s="14"/>
+      <c r="L81" s="15"/>
     </row>
     <row r="82" spans="1:12" ht="71.25" customHeight="1">
       <c r="A82" s="4">
-        <v>88</v>
-      </c>
-      <c r="B82" s="50"/>
-      <c r="C82" s="50"/>
+        <v>87</v>
+      </c>
+      <c r="B82" s="52"/>
+      <c r="C82" s="52" t="s">
+        <v>300</v>
+      </c>
       <c r="D82" s="6" t="s">
-        <v>266</v>
+        <v>301</v>
       </c>
       <c r="E82" s="18"/>
       <c r="F82" s="18" t="s">
-        <v>267</v>
-      </c>
-      <c r="G82" s="14"/>
-      <c r="H82" s="14"/>
-      <c r="I82" s="14"/>
-      <c r="J82" s="14"/>
-      <c r="K82" s="14"/>
-      <c r="L82" s="15"/>
-    </row>
-    <row r="83" spans="1:12" ht="88.5" customHeight="1">
+        <v>302</v>
+      </c>
+      <c r="G82" s="33"/>
+      <c r="H82" s="33"/>
+      <c r="I82" s="33"/>
+      <c r="J82" s="33"/>
+      <c r="K82" s="33"/>
+      <c r="L82" s="32"/>
+    </row>
+    <row r="83" spans="1:12" ht="71.25" customHeight="1">
       <c r="A83" s="4">
-        <v>89</v>
-      </c>
-      <c r="B83" s="50"/>
-      <c r="C83" s="50"/>
+        <v>88</v>
+      </c>
+      <c r="B83" s="52"/>
+      <c r="C83" s="52"/>
       <c r="D83" s="6" t="s">
-        <v>268</v>
+        <v>303</v>
       </c>
       <c r="E83" s="18"/>
       <c r="F83" s="18" t="s">
-        <v>269</v>
+        <v>304</v>
       </c>
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="14"/>
       <c r="J83" s="14"/>
       <c r="K83" s="14"/>
-      <c r="L83" s="32"/>
+      <c r="L83" s="15"/>
     </row>
     <row r="84" spans="1:12" ht="88.5" customHeight="1">
       <c r="A84" s="4">
-        <v>90</v>
-      </c>
-      <c r="B84" s="50"/>
-      <c r="C84" s="6" t="s">
-        <v>270</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="B84" s="52"/>
+      <c r="C84" s="52"/>
       <c r="D84" s="6" t="s">
-        <v>271</v>
+        <v>305</v>
       </c>
       <c r="E84" s="18"/>
       <c r="F84" s="18" t="s">
-        <v>272</v>
+        <v>306</v>
       </c>
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="14"/>
       <c r="J84" s="14"/>
       <c r="K84" s="14"/>
-      <c r="L84" s="15"/>
-    </row>
-    <row r="85" spans="1:12" ht="58.5" customHeight="1">
+      <c r="L84" s="32"/>
+    </row>
+    <row r="85" spans="1:12" ht="88.5" customHeight="1">
       <c r="A85" s="4">
-        <v>91</v>
-      </c>
-      <c r="B85" s="50" t="s">
-        <v>273</v>
-      </c>
-      <c r="C85" s="50" t="s">
-        <v>274</v>
+        <v>90</v>
+      </c>
+      <c r="B85" s="52"/>
+      <c r="C85" s="6" t="s">
+        <v>307</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>275</v>
+        <v>308</v>
       </c>
       <c r="E85" s="18"/>
       <c r="F85" s="18" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
@@ -4729,16 +5134,20 @@
     </row>
     <row r="86" spans="1:12" ht="58.5" customHeight="1">
       <c r="A86" s="4">
-        <v>92</v>
-      </c>
-      <c r="B86" s="50"/>
-      <c r="C86" s="50"/>
+        <v>91</v>
+      </c>
+      <c r="B86" s="52" t="s">
+        <v>310</v>
+      </c>
+      <c r="C86" s="52" t="s">
+        <v>311</v>
+      </c>
       <c r="D86" s="6" t="s">
-        <v>277</v>
+        <v>312</v>
       </c>
       <c r="E86" s="18"/>
       <c r="F86" s="18" t="s">
-        <v>278</v>
+        <v>313</v>
       </c>
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
@@ -4747,20 +5156,18 @@
       <c r="K86" s="14"/>
       <c r="L86" s="15"/>
     </row>
-    <row r="87" spans="1:12" ht="46.5" customHeight="1">
+    <row r="87" spans="1:12" ht="58.5" customHeight="1">
       <c r="A87" s="4">
-        <v>93</v>
-      </c>
-      <c r="B87" s="50"/>
-      <c r="C87" s="50" t="s">
-        <v>279</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="B87" s="52"/>
+      <c r="C87" s="52"/>
       <c r="D87" s="6" t="s">
-        <v>280</v>
+        <v>314</v>
       </c>
       <c r="E87" s="18"/>
       <c r="F87" s="18" t="s">
-        <v>281</v>
+        <v>315</v>
       </c>
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
@@ -4771,16 +5178,18 @@
     </row>
     <row r="88" spans="1:12" ht="46.5" customHeight="1">
       <c r="A88" s="4">
-        <v>94</v>
-      </c>
-      <c r="B88" s="50"/>
-      <c r="C88" s="50"/>
+        <v>93</v>
+      </c>
+      <c r="B88" s="52"/>
+      <c r="C88" s="52" t="s">
+        <v>316</v>
+      </c>
       <c r="D88" s="6" t="s">
-        <v>282</v>
+        <v>317</v>
       </c>
       <c r="E88" s="18"/>
       <c r="F88" s="18" t="s">
-        <v>283</v>
+        <v>318</v>
       </c>
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
@@ -4791,16 +5200,16 @@
     </row>
     <row r="89" spans="1:12" ht="46.5" customHeight="1">
       <c r="A89" s="4">
-        <v>95</v>
-      </c>
-      <c r="B89" s="50"/>
-      <c r="C89" s="50"/>
+        <v>94</v>
+      </c>
+      <c r="B89" s="52"/>
+      <c r="C89" s="52"/>
       <c r="D89" s="6" t="s">
-        <v>284</v>
+        <v>319</v>
       </c>
       <c r="E89" s="18"/>
       <c r="F89" s="18" t="s">
-        <v>285</v>
+        <v>320</v>
       </c>
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
@@ -4811,16 +5220,16 @@
     </row>
     <row r="90" spans="1:12" ht="46.5" customHeight="1">
       <c r="A90" s="4">
-        <v>96</v>
-      </c>
-      <c r="B90" s="50"/>
-      <c r="C90" s="50"/>
+        <v>95</v>
+      </c>
+      <c r="B90" s="52"/>
+      <c r="C90" s="52"/>
       <c r="D90" s="6" t="s">
-        <v>286</v>
+        <v>321</v>
       </c>
       <c r="E90" s="18"/>
       <c r="F90" s="18" t="s">
-        <v>287</v>
+        <v>322</v>
       </c>
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
@@ -4831,16 +5240,16 @@
     </row>
     <row r="91" spans="1:12" ht="46.5" customHeight="1">
       <c r="A91" s="4">
-        <v>97</v>
-      </c>
-      <c r="B91" s="50"/>
-      <c r="C91" s="50"/>
+        <v>96</v>
+      </c>
+      <c r="B91" s="52"/>
+      <c r="C91" s="52"/>
       <c r="D91" s="6" t="s">
-        <v>288</v>
+        <v>323</v>
       </c>
       <c r="E91" s="18"/>
       <c r="F91" s="18" t="s">
-        <v>289</v>
+        <v>324</v>
       </c>
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
@@ -4849,22 +5258,18 @@
       <c r="K91" s="14"/>
       <c r="L91" s="15"/>
     </row>
-    <row r="92" spans="1:12" ht="54" customHeight="1">
+    <row r="92" spans="1:12" ht="46.5" customHeight="1">
       <c r="A92" s="4">
-        <v>98</v>
-      </c>
-      <c r="B92" s="50" t="s">
-        <v>290</v>
-      </c>
-      <c r="C92" s="50" t="s">
-        <v>291</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="B92" s="52"/>
+      <c r="C92" s="52"/>
       <c r="D92" s="6" t="s">
-        <v>292</v>
+        <v>325</v>
       </c>
       <c r="E92" s="18"/>
       <c r="F92" s="18" t="s">
-        <v>293</v>
+        <v>326</v>
       </c>
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
@@ -4875,16 +5280,20 @@
     </row>
     <row r="93" spans="1:12" ht="54" customHeight="1">
       <c r="A93" s="4">
-        <v>99</v>
-      </c>
-      <c r="B93" s="50"/>
-      <c r="C93" s="50"/>
+        <v>98</v>
+      </c>
+      <c r="B93" s="52" t="s">
+        <v>327</v>
+      </c>
+      <c r="C93" s="52" t="s">
+        <v>328</v>
+      </c>
       <c r="D93" s="6" t="s">
-        <v>294</v>
+        <v>329</v>
       </c>
       <c r="E93" s="18"/>
       <c r="F93" s="18" t="s">
-        <v>295</v>
+        <v>330</v>
       </c>
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
@@ -4895,16 +5304,16 @@
     </row>
     <row r="94" spans="1:12" ht="54" customHeight="1">
       <c r="A94" s="4">
-        <v>100</v>
-      </c>
-      <c r="B94" s="50"/>
-      <c r="C94" s="50"/>
+        <v>99</v>
+      </c>
+      <c r="B94" s="52"/>
+      <c r="C94" s="52"/>
       <c r="D94" s="6" t="s">
-        <v>296</v>
+        <v>331</v>
       </c>
       <c r="E94" s="18"/>
       <c r="F94" s="18" t="s">
-        <v>297</v>
+        <v>332</v>
       </c>
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
@@ -4915,18 +5324,16 @@
     </row>
     <row r="95" spans="1:12" ht="54" customHeight="1">
       <c r="A95" s="4">
-        <v>101</v>
-      </c>
-      <c r="B95" s="50"/>
-      <c r="C95" s="50" t="s">
-        <v>298</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="B95" s="52"/>
+      <c r="C95" s="52"/>
       <c r="D95" s="6" t="s">
-        <v>299</v>
+        <v>333</v>
       </c>
       <c r="E95" s="18"/>
       <c r="F95" s="18" t="s">
-        <v>300</v>
+        <v>334</v>
       </c>
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
@@ -4937,16 +5344,18 @@
     </row>
     <row r="96" spans="1:12" ht="54" customHeight="1">
       <c r="A96" s="4">
-        <v>102</v>
-      </c>
-      <c r="B96" s="50"/>
-      <c r="C96" s="50"/>
+        <v>101</v>
+      </c>
+      <c r="B96" s="52"/>
+      <c r="C96" s="52" t="s">
+        <v>335</v>
+      </c>
       <c r="D96" s="6" t="s">
-        <v>301</v>
+        <v>336</v>
       </c>
       <c r="E96" s="18"/>
       <c r="F96" s="18" t="s">
-        <v>302</v>
+        <v>337</v>
       </c>
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
@@ -4957,16 +5366,16 @@
     </row>
     <row r="97" spans="1:12" ht="54" customHeight="1">
       <c r="A97" s="4">
-        <v>103</v>
-      </c>
-      <c r="B97" s="50"/>
-      <c r="C97" s="50"/>
+        <v>102</v>
+      </c>
+      <c r="B97" s="52"/>
+      <c r="C97" s="52"/>
       <c r="D97" s="6" t="s">
-        <v>303</v>
+        <v>338</v>
       </c>
       <c r="E97" s="18"/>
       <c r="F97" s="18" t="s">
-        <v>304</v>
+        <v>339</v>
       </c>
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
@@ -4977,16 +5386,16 @@
     </row>
     <row r="98" spans="1:12" ht="54" customHeight="1">
       <c r="A98" s="4">
-        <v>104</v>
-      </c>
-      <c r="B98" s="50"/>
-      <c r="C98" s="50"/>
+        <v>103</v>
+      </c>
+      <c r="B98" s="52"/>
+      <c r="C98" s="52"/>
       <c r="D98" s="6" t="s">
-        <v>305</v>
+        <v>340</v>
       </c>
       <c r="E98" s="18"/>
       <c r="F98" s="18" t="s">
-        <v>306</v>
+        <v>341</v>
       </c>
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
@@ -4997,16 +5406,16 @@
     </row>
     <row r="99" spans="1:12" ht="54" customHeight="1">
       <c r="A99" s="4">
-        <v>105</v>
-      </c>
-      <c r="B99" s="50"/>
-      <c r="C99" s="50"/>
+        <v>104</v>
+      </c>
+      <c r="B99" s="52"/>
+      <c r="C99" s="52"/>
       <c r="D99" s="6" t="s">
-        <v>307</v>
+        <v>342</v>
       </c>
       <c r="E99" s="18"/>
       <c r="F99" s="18" t="s">
-        <v>308</v>
+        <v>343</v>
       </c>
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
@@ -5017,18 +5426,16 @@
     </row>
     <row r="100" spans="1:12" ht="54" customHeight="1">
       <c r="A100" s="4">
-        <v>106</v>
-      </c>
-      <c r="B100" s="50"/>
-      <c r="C100" s="6" t="s">
-        <v>309</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="B100" s="52"/>
+      <c r="C100" s="52"/>
       <c r="D100" s="6" t="s">
-        <v>123</v>
+        <v>344</v>
       </c>
       <c r="E100" s="18"/>
       <c r="F100" s="18" t="s">
-        <v>310</v>
+        <v>345</v>
       </c>
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
@@ -5037,64 +5444,64 @@
       <c r="K100" s="14"/>
       <c r="L100" s="15"/>
     </row>
-    <row r="101" spans="1:12" ht="63" customHeight="1">
+    <row r="101" spans="1:12" ht="54" customHeight="1">
       <c r="A101" s="4">
-        <v>107</v>
-      </c>
-      <c r="B101" s="50" t="s">
-        <v>311</v>
-      </c>
-      <c r="C101" s="50" t="s">
-        <v>312</v>
+        <v>106</v>
+      </c>
+      <c r="B101" s="52"/>
+      <c r="C101" s="6" t="s">
+        <v>346</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>313</v>
+        <v>160</v>
       </c>
       <c r="E101" s="18"/>
       <c r="F101" s="18" t="s">
-        <v>314</v>
+        <v>347</v>
       </c>
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="14"/>
       <c r="J101" s="14"/>
       <c r="K101" s="14"/>
-      <c r="L101" s="32"/>
-    </row>
-    <row r="102" spans="1:12" ht="34.5" customHeight="1">
+      <c r="L101" s="15"/>
+    </row>
+    <row r="102" spans="1:12" ht="63" customHeight="1">
       <c r="A102" s="4">
-        <v>108</v>
-      </c>
-      <c r="B102" s="50"/>
-      <c r="C102" s="50"/>
+        <v>107</v>
+      </c>
+      <c r="B102" s="52" t="s">
+        <v>348</v>
+      </c>
+      <c r="C102" s="52" t="s">
+        <v>349</v>
+      </c>
       <c r="D102" s="6" t="s">
-        <v>315</v>
+        <v>350</v>
       </c>
       <c r="E102" s="18"/>
       <c r="F102" s="18" t="s">
-        <v>316</v>
+        <v>351</v>
       </c>
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="14"/>
       <c r="J102" s="14"/>
       <c r="K102" s="14"/>
-      <c r="L102" s="15"/>
-    </row>
-    <row r="103" spans="1:12" ht="36" customHeight="1">
+      <c r="L102" s="32"/>
+    </row>
+    <row r="103" spans="1:12" ht="34.5" customHeight="1">
       <c r="A103" s="4">
-        <v>109</v>
-      </c>
-      <c r="B103" s="50"/>
-      <c r="C103" s="6" t="s">
-        <v>317</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="B103" s="52"/>
+      <c r="C103" s="52"/>
       <c r="D103" s="6" t="s">
-        <v>318</v>
+        <v>352</v>
       </c>
       <c r="E103" s="18"/>
       <c r="F103" s="18" t="s">
-        <v>319</v>
+        <v>353</v>
       </c>
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
@@ -5103,132 +5510,134 @@
       <c r="K103" s="14"/>
       <c r="L103" s="15"/>
     </row>
-    <row r="104" spans="1:12" ht="45.75">
+    <row r="104" spans="1:12" ht="36" customHeight="1">
       <c r="A104" s="4">
-        <v>110</v>
-      </c>
-      <c r="B104" s="50"/>
-      <c r="C104" s="50" t="s">
-        <v>320</v>
+        <v>109</v>
+      </c>
+      <c r="B104" s="52"/>
+      <c r="C104" s="6" t="s">
+        <v>354</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>321</v>
+        <v>355</v>
       </c>
       <c r="E104" s="18"/>
       <c r="F104" s="18" t="s">
-        <v>322</v>
-      </c>
-      <c r="G104" s="13" t="s">
-        <v>323</v>
-      </c>
-      <c r="H104" s="13" t="s">
-        <v>323</v>
-      </c>
-      <c r="I104" s="13" t="s">
-        <v>323</v>
-      </c>
-      <c r="J104" s="13" t="s">
-        <v>323</v>
-      </c>
-      <c r="K104" s="13" t="s">
-        <v>323</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="G104" s="14"/>
+      <c r="H104" s="14"/>
+      <c r="I104" s="14"/>
+      <c r="J104" s="14"/>
+      <c r="K104" s="14"/>
       <c r="L104" s="15"/>
     </row>
-    <row r="105" spans="1:12" ht="41.25" customHeight="1">
+    <row r="105" spans="1:12" ht="45.75">
       <c r="A105" s="4">
-        <v>111</v>
-      </c>
-      <c r="B105" s="50"/>
-      <c r="C105" s="50"/>
+        <v>110</v>
+      </c>
+      <c r="B105" s="52"/>
+      <c r="C105" s="52" t="s">
+        <v>357</v>
+      </c>
       <c r="D105" s="6" t="s">
-        <v>324</v>
+        <v>358</v>
       </c>
       <c r="E105" s="18"/>
       <c r="F105" s="18" t="s">
-        <v>325</v>
-      </c>
-      <c r="G105" s="14" t="s">
-        <v>326</v>
-      </c>
-      <c r="H105" s="14" t="s">
-        <v>326</v>
-      </c>
-      <c r="I105" s="14" t="s">
-        <v>326</v>
-      </c>
-      <c r="J105" s="14" t="s">
-        <v>326</v>
-      </c>
-      <c r="K105" s="14" t="s">
-        <v>326</v>
+        <v>359</v>
+      </c>
+      <c r="G105" s="13" t="s">
+        <v>360</v>
+      </c>
+      <c r="H105" s="13" t="s">
+        <v>360</v>
+      </c>
+      <c r="I105" s="13" t="s">
+        <v>360</v>
+      </c>
+      <c r="J105" s="13" t="s">
+        <v>360</v>
+      </c>
+      <c r="K105" s="13" t="s">
+        <v>360</v>
       </c>
       <c r="L105" s="15"/>
     </row>
     <row r="106" spans="1:12" ht="41.25" customHeight="1">
       <c r="A106" s="4">
-        <v>112</v>
-      </c>
-      <c r="B106" s="50"/>
-      <c r="C106" s="50"/>
+        <v>111</v>
+      </c>
+      <c r="B106" s="52"/>
+      <c r="C106" s="52"/>
       <c r="D106" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="E106" s="29"/>
-      <c r="F106" s="29" t="s">
-        <v>328</v>
-      </c>
-      <c r="G106" s="30" t="s">
-        <v>326</v>
-      </c>
-      <c r="H106" s="30" t="s">
-        <v>326</v>
-      </c>
-      <c r="I106" s="30" t="s">
-        <v>326</v>
-      </c>
-      <c r="J106" s="30" t="s">
-        <v>326</v>
-      </c>
-      <c r="K106" s="30" t="s">
-        <v>326</v>
-      </c>
-      <c r="L106" s="31"/>
+        <v>361</v>
+      </c>
+      <c r="E106" s="18"/>
+      <c r="F106" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G106" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="H106" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="I106" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="J106" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="K106" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="L106" s="15"/>
     </row>
     <row r="107" spans="1:12" ht="41.25" customHeight="1">
       <c r="A107" s="4">
-        <v>113</v>
-      </c>
-      <c r="B107" s="50"/>
-      <c r="C107" s="50" t="s">
-        <v>329</v>
-      </c>
-      <c r="D107" s="18" t="s">
-        <v>330</v>
-      </c>
-      <c r="E107" s="18"/>
-      <c r="F107" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="G107" s="14"/>
-      <c r="H107" s="14"/>
-      <c r="I107" s="14"/>
-      <c r="J107" s="14"/>
-      <c r="K107" s="14"/>
-      <c r="L107" s="15"/>
+        <v>112</v>
+      </c>
+      <c r="B107" s="52"/>
+      <c r="C107" s="52"/>
+      <c r="D107" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="E107" s="29"/>
+      <c r="F107" s="29" t="s">
+        <v>365</v>
+      </c>
+      <c r="G107" s="30" t="s">
+        <v>363</v>
+      </c>
+      <c r="H107" s="30" t="s">
+        <v>363</v>
+      </c>
+      <c r="I107" s="30" t="s">
+        <v>363</v>
+      </c>
+      <c r="J107" s="30" t="s">
+        <v>363</v>
+      </c>
+      <c r="K107" s="30" t="s">
+        <v>363</v>
+      </c>
+      <c r="L107" s="31"/>
     </row>
     <row r="108" spans="1:12" ht="41.25" customHeight="1">
       <c r="A108" s="4">
-        <v>114</v>
-      </c>
-      <c r="B108" s="50"/>
-      <c r="C108" s="50"/>
+        <v>113</v>
+      </c>
+      <c r="B108" s="52"/>
+      <c r="C108" s="52" t="s">
+        <v>366</v>
+      </c>
       <c r="D108" s="18" t="s">
-        <v>332</v>
+        <v>367</v>
       </c>
       <c r="E108" s="18"/>
       <c r="F108" s="6" t="s">
-        <v>333</v>
+        <v>368</v>
       </c>
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
@@ -5237,13 +5646,25 @@
       <c r="K108" s="14"/>
       <c r="L108" s="15"/>
     </row>
-    <row r="109" spans="1:12">
-      <c r="G109" s="26"/>
-      <c r="H109" s="26"/>
-      <c r="I109" s="26"/>
-      <c r="J109" s="26"/>
-      <c r="K109" s="26"/>
-      <c r="L109" s="27"/>
+    <row r="109" spans="1:12" ht="41.25" customHeight="1">
+      <c r="A109" s="4">
+        <v>114</v>
+      </c>
+      <c r="B109" s="52"/>
+      <c r="C109" s="52"/>
+      <c r="D109" s="18" t="s">
+        <v>369</v>
+      </c>
+      <c r="E109" s="18"/>
+      <c r="F109" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="G109" s="14"/>
+      <c r="H109" s="14"/>
+      <c r="I109" s="14"/>
+      <c r="J109" s="14"/>
+      <c r="K109" s="14"/>
+      <c r="L109" s="15"/>
     </row>
     <row r="110" spans="1:12">
       <c r="G110" s="26"/>
@@ -5275,7 +5696,7 @@
       <c r="I113" s="26"/>
       <c r="J113" s="26"/>
       <c r="K113" s="26"/>
-      <c r="L113" s="28"/>
+      <c r="L113" s="27"/>
     </row>
     <row r="114" spans="7:12">
       <c r="G114" s="26"/>
@@ -5283,7 +5704,7 @@
       <c r="I114" s="26"/>
       <c r="J114" s="26"/>
       <c r="K114" s="26"/>
-      <c r="L114" s="27"/>
+      <c r="L114" s="28"/>
     </row>
     <row r="115" spans="7:12">
       <c r="G115" s="26"/>
@@ -5318,7 +5739,7 @@
       <c r="L118" s="27"/>
     </row>
     <row r="119" spans="7:12">
-      <c r="G119" s="27"/>
+      <c r="G119" s="26"/>
       <c r="H119" s="26"/>
       <c r="I119" s="26"/>
       <c r="J119" s="26"/>
@@ -5363,7 +5784,7 @@
       <c r="I124" s="26"/>
       <c r="J124" s="26"/>
       <c r="K124" s="26"/>
-      <c r="L124" s="28"/>
+      <c r="L124" s="27"/>
     </row>
     <row r="125" spans="7:12">
       <c r="G125" s="27"/>
@@ -5371,7 +5792,7 @@
       <c r="I125" s="26"/>
       <c r="J125" s="26"/>
       <c r="K125" s="26"/>
-      <c r="L125" s="27"/>
+      <c r="L125" s="28"/>
     </row>
     <row r="126" spans="7:12">
       <c r="G126" s="27"/>
@@ -5454,10 +5875,12 @@
       <c r="L135" s="27"/>
     </row>
     <row r="136" spans="7:12">
-      <c r="H136" s="12"/>
-      <c r="I136" s="12"/>
-      <c r="J136" s="12"/>
-      <c r="K136" s="12"/>
+      <c r="G136" s="27"/>
+      <c r="H136" s="26"/>
+      <c r="I136" s="26"/>
+      <c r="J136" s="26"/>
+      <c r="K136" s="26"/>
+      <c r="L136" s="27"/>
     </row>
     <row r="137" spans="7:12">
       <c r="H137" s="12"/>
@@ -5597,13 +6020,19 @@
       <c r="J159" s="12"/>
       <c r="K159" s="12"/>
     </row>
+    <row r="160" spans="8:11">
+      <c r="H160" s="12"/>
+      <c r="I160" s="12"/>
+      <c r="J160" s="12"/>
+      <c r="K160" s="12"/>
+    </row>
   </sheetData>
-  <mergeCells count="38">
+  <mergeCells count="37">
     <mergeCell ref="C2:C8"/>
     <mergeCell ref="B14:B18"/>
-    <mergeCell ref="C38:C41"/>
-    <mergeCell ref="B36:B45"/>
-    <mergeCell ref="C42:C45"/>
+    <mergeCell ref="C38:C44"/>
+    <mergeCell ref="B36:B47"/>
+    <mergeCell ref="C45:C47"/>
     <mergeCell ref="B19:B27"/>
     <mergeCell ref="B28:B35"/>
     <mergeCell ref="C19:C21"/>
@@ -5613,36 +6042,35 @@
     <mergeCell ref="C36:C37"/>
     <mergeCell ref="C9:C13"/>
     <mergeCell ref="B2:B13"/>
-    <mergeCell ref="B46:B64"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="C48:C53"/>
-    <mergeCell ref="C54:C58"/>
-    <mergeCell ref="C59:C63"/>
-    <mergeCell ref="B65:B74"/>
-    <mergeCell ref="C65:C67"/>
-    <mergeCell ref="C68:C70"/>
-    <mergeCell ref="C71:C72"/>
+    <mergeCell ref="B67:B75"/>
+    <mergeCell ref="C67:C69"/>
+    <mergeCell ref="C70:C72"/>
     <mergeCell ref="C73:C74"/>
-    <mergeCell ref="C107:C108"/>
-    <mergeCell ref="B101:B108"/>
-    <mergeCell ref="B75:B84"/>
-    <mergeCell ref="C75:C77"/>
-    <mergeCell ref="C78:C80"/>
-    <mergeCell ref="C81:C83"/>
-    <mergeCell ref="B85:B91"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="C87:C91"/>
-    <mergeCell ref="B92:B100"/>
-    <mergeCell ref="C92:C94"/>
-    <mergeCell ref="C95:C99"/>
-    <mergeCell ref="C101:C102"/>
-    <mergeCell ref="C104:C106"/>
+    <mergeCell ref="B48:B66"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="C50:C55"/>
+    <mergeCell ref="C56:C60"/>
+    <mergeCell ref="C61:C65"/>
+    <mergeCell ref="C108:C109"/>
+    <mergeCell ref="B102:B109"/>
+    <mergeCell ref="B76:B85"/>
+    <mergeCell ref="C76:C78"/>
+    <mergeCell ref="C79:C81"/>
+    <mergeCell ref="C82:C84"/>
+    <mergeCell ref="B86:B92"/>
+    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="C88:C92"/>
+    <mergeCell ref="B93:B101"/>
+    <mergeCell ref="C93:C95"/>
+    <mergeCell ref="C96:C100"/>
+    <mergeCell ref="C102:C103"/>
+    <mergeCell ref="C105:C107"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B18A7A7-6460-480C-B7E4-348011A6A97C}">
   <dimension ref="A1:Z56"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -5657,19 +6085,19 @@
   <sheetData>
     <row r="1" spans="1:26" s="8" customFormat="1">
       <c r="A1" s="3" t="s">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -5697,751 +6125,751 @@
       <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="50" t="s">
-        <v>334</v>
-      </c>
-      <c r="C2" s="50" t="s">
-        <v>335</v>
+      <c r="B2" s="52" t="s">
+        <v>371</v>
+      </c>
+      <c r="C2" s="52" t="s">
+        <v>372</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>336</v>
+        <v>373</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>337</v>
+        <v>374</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="60.75" customHeight="1">
       <c r="A3" s="7">
         <v>2</v>
       </c>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
       <c r="D3" s="6" t="s">
-        <v>338</v>
+        <v>375</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>339</v>
+        <v>376</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="60.75" customHeight="1">
       <c r="A4" s="7">
         <v>3</v>
       </c>
-      <c r="B4" s="50"/>
-      <c r="C4" s="50"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
       <c r="D4" s="6" t="s">
-        <v>340</v>
+        <v>377</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>341</v>
+        <v>378</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="60.75" customHeight="1">
       <c r="A5" s="7">
         <v>4</v>
       </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="50"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="52"/>
       <c r="D5" s="6" t="s">
-        <v>342</v>
+        <v>379</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>343</v>
+        <v>380</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="60.75" customHeight="1">
       <c r="A6" s="7">
         <v>5</v>
       </c>
-      <c r="B6" s="50"/>
-      <c r="C6" s="50"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
       <c r="D6" s="6" t="s">
-        <v>344</v>
+        <v>381</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>345</v>
+        <v>382</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="60.75" customHeight="1">
       <c r="A7" s="7">
         <v>6</v>
       </c>
-      <c r="B7" s="50"/>
-      <c r="C7" s="50"/>
+      <c r="B7" s="52"/>
+      <c r="C7" s="52"/>
       <c r="D7" s="6" t="s">
-        <v>346</v>
+        <v>383</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>347</v>
+        <v>384</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="60.75" customHeight="1">
       <c r="A8" s="7">
         <v>7</v>
       </c>
-      <c r="B8" s="50"/>
-      <c r="C8" s="50" t="s">
-        <v>348</v>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52" t="s">
+        <v>385</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>349</v>
+        <v>386</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>350</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="60.75" customHeight="1">
       <c r="A9" s="7">
         <v>8</v>
       </c>
-      <c r="B9" s="50"/>
-      <c r="C9" s="50"/>
+      <c r="B9" s="52"/>
+      <c r="C9" s="52"/>
       <c r="D9" s="6" t="s">
-        <v>351</v>
+        <v>388</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>352</v>
+        <v>389</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="60.75" customHeight="1">
       <c r="A10" s="7">
         <v>9</v>
       </c>
-      <c r="B10" s="50"/>
-      <c r="C10" s="50"/>
+      <c r="B10" s="52"/>
+      <c r="C10" s="52"/>
       <c r="D10" s="6" t="s">
-        <v>353</v>
+        <v>390</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>354</v>
+        <v>391</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="60.75" customHeight="1">
       <c r="A11" s="7">
         <v>10</v>
       </c>
-      <c r="B11" s="50"/>
-      <c r="C11" s="50"/>
+      <c r="B11" s="52"/>
+      <c r="C11" s="52"/>
       <c r="D11" s="6" t="s">
-        <v>355</v>
+        <v>392</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>356</v>
+        <v>393</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="60.75" customHeight="1">
       <c r="A12" s="7">
         <v>11</v>
       </c>
-      <c r="B12" s="50"/>
-      <c r="C12" s="50" t="s">
-        <v>357</v>
+      <c r="B12" s="52"/>
+      <c r="C12" s="52" t="s">
+        <v>394</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>358</v>
+        <v>395</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>359</v>
+        <v>396</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="60.75" customHeight="1">
       <c r="A13" s="7">
         <v>12</v>
       </c>
-      <c r="B13" s="50"/>
-      <c r="C13" s="50"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="52"/>
       <c r="D13" s="6" t="s">
-        <v>360</v>
+        <v>397</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>361</v>
+        <v>398</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="60.75" customHeight="1">
       <c r="A14" s="7">
         <v>13</v>
       </c>
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
+      <c r="B14" s="52"/>
+      <c r="C14" s="52"/>
       <c r="D14" s="6" t="s">
-        <v>362</v>
+        <v>399</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>363</v>
+        <v>400</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="60.75" customHeight="1">
       <c r="A15" s="7">
         <v>14</v>
       </c>
-      <c r="B15" s="50"/>
-      <c r="C15" s="50"/>
+      <c r="B15" s="52"/>
+      <c r="C15" s="52"/>
       <c r="D15" s="6" t="s">
-        <v>364</v>
+        <v>401</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>365</v>
+        <v>402</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="60.75" customHeight="1">
       <c r="A16" s="7">
         <v>15</v>
       </c>
-      <c r="B16" s="50"/>
-      <c r="C16" s="50"/>
+      <c r="B16" s="52"/>
+      <c r="C16" s="52"/>
       <c r="D16" s="6" t="s">
-        <v>366</v>
+        <v>403</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>367</v>
+        <v>404</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="60.75" customHeight="1">
       <c r="A17" s="7">
         <v>16</v>
       </c>
-      <c r="B17" s="50"/>
-      <c r="C17" s="50"/>
+      <c r="B17" s="52"/>
+      <c r="C17" s="52"/>
       <c r="D17" s="6" t="s">
-        <v>368</v>
+        <v>405</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>369</v>
+        <v>406</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="60.75" customHeight="1">
       <c r="A18" s="7">
         <v>17</v>
       </c>
-      <c r="B18" s="50"/>
-      <c r="C18" s="50"/>
+      <c r="B18" s="52"/>
+      <c r="C18" s="52"/>
       <c r="D18" s="6" t="s">
-        <v>370</v>
+        <v>407</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>371</v>
+        <v>408</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="60.75" customHeight="1">
       <c r="A19" s="7">
         <v>18</v>
       </c>
-      <c r="B19" s="50"/>
-      <c r="C19" s="50"/>
+      <c r="B19" s="52"/>
+      <c r="C19" s="52"/>
       <c r="D19" s="6" t="s">
-        <v>372</v>
+        <v>409</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>373</v>
+        <v>410</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="60.75" customHeight="1">
       <c r="A20" s="7">
         <v>19</v>
       </c>
-      <c r="B20" s="50"/>
-      <c r="C20" s="50"/>
+      <c r="B20" s="52"/>
+      <c r="C20" s="52"/>
       <c r="D20" s="6" t="s">
-        <v>374</v>
+        <v>411</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>375</v>
+        <v>412</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="60.75" customHeight="1">
       <c r="A21" s="7">
         <v>20</v>
       </c>
-      <c r="B21" s="50"/>
-      <c r="C21" s="50" t="s">
-        <v>376</v>
+      <c r="B21" s="52"/>
+      <c r="C21" s="52" t="s">
+        <v>413</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>377</v>
+        <v>414</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>378</v>
+        <v>415</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="60.75" customHeight="1">
       <c r="A22" s="7">
         <v>21</v>
       </c>
-      <c r="B22" s="50"/>
-      <c r="C22" s="50"/>
+      <c r="B22" s="52"/>
+      <c r="C22" s="52"/>
       <c r="D22" s="6" t="s">
-        <v>379</v>
+        <v>416</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>380</v>
+        <v>417</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="60.75" customHeight="1">
       <c r="A23" s="7">
         <v>22</v>
       </c>
-      <c r="B23" s="50"/>
-      <c r="C23" s="50"/>
+      <c r="B23" s="52"/>
+      <c r="C23" s="52"/>
       <c r="D23" s="6" t="s">
-        <v>381</v>
+        <v>418</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>382</v>
+        <v>419</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="60.75" customHeight="1">
       <c r="A24" s="7">
         <v>23</v>
       </c>
-      <c r="B24" s="50"/>
-      <c r="C24" s="50" t="s">
-        <v>383</v>
+      <c r="B24" s="52"/>
+      <c r="C24" s="52" t="s">
+        <v>420</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>384</v>
+        <v>421</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>385</v>
+        <v>422</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="60.75" customHeight="1">
       <c r="A25" s="7">
         <v>24</v>
       </c>
-      <c r="B25" s="50"/>
-      <c r="C25" s="50"/>
+      <c r="B25" s="52"/>
+      <c r="C25" s="52"/>
       <c r="D25" s="6" t="s">
-        <v>386</v>
+        <v>423</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>387</v>
+        <v>424</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="60.75" customHeight="1">
       <c r="A26" s="7">
         <v>25</v>
       </c>
-      <c r="B26" s="50"/>
-      <c r="C26" s="50"/>
+      <c r="B26" s="52"/>
+      <c r="C26" s="52"/>
       <c r="D26" s="6" t="s">
-        <v>388</v>
+        <v>425</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>389</v>
+        <v>426</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="60.75" customHeight="1">
       <c r="A27" s="7">
         <v>26</v>
       </c>
-      <c r="B27" s="50"/>
-      <c r="C27" s="50"/>
+      <c r="B27" s="52"/>
+      <c r="C27" s="52"/>
       <c r="D27" s="6" t="s">
-        <v>390</v>
+        <v>427</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>391</v>
+        <v>428</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="60.75" customHeight="1">
       <c r="A28" s="7">
         <v>27</v>
       </c>
-      <c r="B28" s="50"/>
-      <c r="C28" s="50"/>
+      <c r="B28" s="52"/>
+      <c r="C28" s="52"/>
       <c r="D28" s="6" t="s">
-        <v>392</v>
+        <v>429</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>393</v>
+        <v>430</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="60.75" customHeight="1">
       <c r="A29" s="7">
         <v>28</v>
       </c>
-      <c r="B29" s="50"/>
-      <c r="C29" s="50" t="s">
-        <v>394</v>
+      <c r="B29" s="52"/>
+      <c r="C29" s="52" t="s">
+        <v>431</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>395</v>
+        <v>432</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>396</v>
+        <v>433</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="60.75" customHeight="1">
       <c r="A30" s="7">
         <v>29</v>
       </c>
-      <c r="B30" s="50"/>
-      <c r="C30" s="50"/>
+      <c r="B30" s="52"/>
+      <c r="C30" s="52"/>
       <c r="D30" s="6" t="s">
-        <v>397</v>
+        <v>434</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>398</v>
+        <v>435</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="60.75" customHeight="1">
       <c r="A31" s="7">
         <v>30</v>
       </c>
-      <c r="B31" s="55"/>
-      <c r="C31" s="55"/>
+      <c r="B31" s="57"/>
+      <c r="C31" s="57"/>
       <c r="D31" s="10" t="s">
-        <v>399</v>
+        <v>436</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>400</v>
+        <v>437</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="60.75" customHeight="1">
       <c r="A32" s="9">
         <v>31</v>
       </c>
-      <c r="B32" s="50" t="s">
-        <v>401</v>
-      </c>
-      <c r="C32" s="50" t="s">
-        <v>402</v>
+      <c r="B32" s="52" t="s">
+        <v>438</v>
+      </c>
+      <c r="C32" s="52" t="s">
+        <v>439</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>403</v>
+        <v>440</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>404</v>
+        <v>441</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="60.75" customHeight="1">
       <c r="A33" s="9">
         <v>32</v>
       </c>
-      <c r="B33" s="50"/>
-      <c r="C33" s="50"/>
+      <c r="B33" s="52"/>
+      <c r="C33" s="52"/>
       <c r="D33" s="11" t="s">
-        <v>405</v>
+        <v>442</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>406</v>
+        <v>443</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="60.75" customHeight="1">
       <c r="A34" s="9">
         <v>33</v>
       </c>
-      <c r="B34" s="50"/>
-      <c r="C34" s="50"/>
+      <c r="B34" s="52"/>
+      <c r="C34" s="52"/>
       <c r="D34" s="11" t="s">
-        <v>407</v>
+        <v>444</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>408</v>
+        <v>445</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="60.75" customHeight="1">
       <c r="A35" s="9">
         <v>34</v>
       </c>
-      <c r="B35" s="50"/>
-      <c r="C35" s="50" t="s">
-        <v>409</v>
+      <c r="B35" s="52"/>
+      <c r="C35" s="52" t="s">
+        <v>446</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>410</v>
+        <v>447</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>411</v>
+        <v>448</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="60.75" customHeight="1">
       <c r="A36" s="9">
         <v>35</v>
       </c>
-      <c r="B36" s="50"/>
-      <c r="C36" s="50"/>
+      <c r="B36" s="52"/>
+      <c r="C36" s="52"/>
       <c r="D36" s="11" t="s">
-        <v>412</v>
+        <v>449</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>413</v>
+        <v>450</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="60.75" customHeight="1">
       <c r="A37" s="9">
         <v>36</v>
       </c>
-      <c r="B37" s="50"/>
-      <c r="C37" s="50"/>
+      <c r="B37" s="52"/>
+      <c r="C37" s="52"/>
       <c r="D37" s="11" t="s">
-        <v>414</v>
+        <v>451</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>415</v>
+        <v>452</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="60.75" customHeight="1">
       <c r="A38" s="9">
         <v>37</v>
       </c>
-      <c r="B38" s="50"/>
-      <c r="C38" s="50"/>
+      <c r="B38" s="52"/>
+      <c r="C38" s="52"/>
       <c r="D38" s="11" t="s">
-        <v>416</v>
+        <v>453</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>417</v>
+        <v>454</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="60.75" customHeight="1">
       <c r="A39" s="9">
         <v>38</v>
       </c>
-      <c r="B39" s="50"/>
-      <c r="C39" s="50" t="s">
-        <v>418</v>
+      <c r="B39" s="52"/>
+      <c r="C39" s="52" t="s">
+        <v>455</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>419</v>
+        <v>456</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>420</v>
+        <v>457</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="60.75" customHeight="1">
       <c r="A40" s="9">
         <v>39</v>
       </c>
-      <c r="B40" s="50"/>
-      <c r="C40" s="50"/>
+      <c r="B40" s="52"/>
+      <c r="C40" s="52"/>
       <c r="D40" s="11" t="s">
-        <v>421</v>
+        <v>458</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>422</v>
+        <v>459</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="60.75" customHeight="1">
       <c r="A41" s="9">
         <v>40</v>
       </c>
-      <c r="B41" s="50"/>
-      <c r="C41" s="50" t="s">
-        <v>423</v>
+      <c r="B41" s="52"/>
+      <c r="C41" s="52" t="s">
+        <v>460</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>424</v>
+        <v>461</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>411</v>
+        <v>448</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="60.75" customHeight="1">
       <c r="A42" s="9">
         <v>41</v>
       </c>
-      <c r="B42" s="50"/>
-      <c r="C42" s="50"/>
+      <c r="B42" s="52"/>
+      <c r="C42" s="52"/>
       <c r="D42" s="11" t="s">
-        <v>425</v>
+        <v>462</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>426</v>
+        <v>463</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="60.75" customHeight="1">
       <c r="A43" s="9">
         <v>42</v>
       </c>
-      <c r="B43" s="50"/>
-      <c r="C43" s="50" t="s">
-        <v>427</v>
+      <c r="B43" s="52"/>
+      <c r="C43" s="52" t="s">
+        <v>464</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>428</v>
+        <v>465</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="60.75" customHeight="1">
       <c r="A44" s="9">
         <v>43</v>
       </c>
-      <c r="B44" s="50"/>
-      <c r="C44" s="50"/>
+      <c r="B44" s="52"/>
+      <c r="C44" s="52"/>
       <c r="D44" s="11" t="s">
-        <v>429</v>
+        <v>466</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>430</v>
+        <v>467</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="60.75" customHeight="1">
       <c r="A45" s="9"/>
-      <c r="B45" s="50"/>
-      <c r="C45" s="50"/>
+      <c r="B45" s="52"/>
+      <c r="C45" s="52"/>
       <c r="D45" s="11" t="s">
-        <v>431</v>
+        <v>468</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>432</v>
+        <v>469</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="60.75" customHeight="1">
       <c r="A46" s="9">
         <v>45</v>
       </c>
-      <c r="B46" s="50" t="s">
-        <v>433</v>
-      </c>
-      <c r="C46" s="50" t="s">
-        <v>434</v>
+      <c r="B46" s="52" t="s">
+        <v>470</v>
+      </c>
+      <c r="C46" s="52" t="s">
+        <v>471</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>435</v>
+        <v>472</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>436</v>
+        <v>473</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="60.75" customHeight="1">
       <c r="A47" s="9">
         <v>46</v>
       </c>
-      <c r="B47" s="50"/>
-      <c r="C47" s="50"/>
+      <c r="B47" s="52"/>
+      <c r="C47" s="52"/>
       <c r="D47" s="11" t="s">
-        <v>437</v>
+        <v>474</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>438</v>
+        <v>475</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="60.75" customHeight="1">
       <c r="A48" s="9">
         <v>47</v>
       </c>
-      <c r="B48" s="50"/>
-      <c r="C48" s="50" t="s">
-        <v>409</v>
+      <c r="B48" s="52"/>
+      <c r="C48" s="52" t="s">
+        <v>446</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>439</v>
+        <v>476</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>440</v>
+        <v>477</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="60.75" customHeight="1">
       <c r="A49" s="9">
         <v>48</v>
       </c>
-      <c r="B49" s="50"/>
-      <c r="C49" s="50"/>
+      <c r="B49" s="52"/>
+      <c r="C49" s="52"/>
       <c r="D49" s="11" t="s">
-        <v>441</v>
+        <v>478</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>442</v>
+        <v>479</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="60.75" customHeight="1">
       <c r="A50" s="9">
         <v>49</v>
       </c>
-      <c r="B50" s="50"/>
-      <c r="C50" s="50"/>
+      <c r="B50" s="52"/>
+      <c r="C50" s="52"/>
       <c r="D50" s="11" t="s">
-        <v>443</v>
+        <v>480</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>444</v>
+        <v>481</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="60.75" customHeight="1">
       <c r="A51" s="9">
         <v>50</v>
       </c>
-      <c r="B51" s="50"/>
-      <c r="C51" s="50"/>
+      <c r="B51" s="52"/>
+      <c r="C51" s="52"/>
       <c r="D51" s="11" t="s">
-        <v>445</v>
+        <v>482</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>446</v>
+        <v>483</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="60.75" customHeight="1">
       <c r="A52" s="9">
         <v>51</v>
       </c>
-      <c r="B52" s="50"/>
-      <c r="C52" s="50" t="s">
-        <v>447</v>
+      <c r="B52" s="52"/>
+      <c r="C52" s="52" t="s">
+        <v>484</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>448</v>
+        <v>485</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>449</v>
+        <v>486</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="60.75" customHeight="1">
       <c r="A53" s="9">
         <v>52</v>
       </c>
-      <c r="B53" s="50"/>
-      <c r="C53" s="50"/>
+      <c r="B53" s="52"/>
+      <c r="C53" s="52"/>
       <c r="D53" s="11" t="s">
-        <v>450</v>
+        <v>487</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>451</v>
+        <v>488</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="60.75" customHeight="1">
       <c r="A54" s="9">
         <v>53</v>
       </c>
-      <c r="B54" s="50"/>
+      <c r="B54" s="52"/>
       <c r="C54" s="11" t="s">
-        <v>452</v>
+        <v>489</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>453</v>
+        <v>490</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>454</v>
+        <v>491</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="60.75" customHeight="1">
       <c r="A55" s="9">
         <v>55</v>
       </c>
-      <c r="B55" s="50"/>
-      <c r="C55" s="50" t="s">
-        <v>455</v>
+      <c r="B55" s="52"/>
+      <c r="C55" s="52" t="s">
+        <v>492</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>456</v>
+        <v>493</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>457</v>
+        <v>494</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="60.75" customHeight="1">
       <c r="A56" s="9">
         <v>56</v>
       </c>
-      <c r="B56" s="50"/>
-      <c r="C56" s="50"/>
+      <c r="B56" s="52"/>
+      <c r="C56" s="52"/>
       <c r="D56" s="11" t="s">
-        <v>458</v>
+        <v>495</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>459</v>
+        <v>496</v>
       </c>
     </row>
   </sheetData>
@@ -6469,9 +6897,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7BFED6D-21E8-4E6D-9269-B75B7E326689}">
-  <dimension ref="A1:N44"/>
+  <dimension ref="A1:N43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="35.7109375" customWidth="1"/>
@@ -6487,115 +6915,115 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="1" customFormat="1">
-      <c r="A1" s="49" t="s">
-        <v>460</v>
-      </c>
-      <c r="B1" s="49" t="s">
-        <v>461</v>
-      </c>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="49" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49" t="s">
-        <v>10</v>
-      </c>
-      <c r="N1" s="49"/>
+      <c r="A1" s="64" t="s">
+        <v>497</v>
+      </c>
+      <c r="B1" s="64" t="s">
+        <v>498</v>
+      </c>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="64" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64" t="s">
+        <v>44</v>
+      </c>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64" t="s">
+        <v>46</v>
+      </c>
+      <c r="L1" s="64"/>
+      <c r="M1" s="64" t="s">
+        <v>47</v>
+      </c>
+      <c r="N1" s="64"/>
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="30.75">
-      <c r="A2" s="49"/>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
+      <c r="A2" s="64"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
       <c r="E2" s="37" t="s">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="F2" s="37" t="s">
-        <v>462</v>
+        <v>499</v>
       </c>
       <c r="G2" s="37" t="s">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="H2" s="37" t="s">
-        <v>462</v>
+        <v>499</v>
       </c>
       <c r="I2" s="37" t="s">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="J2" s="37" t="s">
-        <v>462</v>
+        <v>499</v>
       </c>
       <c r="K2" s="37" t="s">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="L2" s="37" t="s">
-        <v>462</v>
+        <v>499</v>
       </c>
       <c r="M2" s="37" t="s">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="N2" s="37" t="s">
-        <v>462</v>
+        <v>499</v>
       </c>
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="29.25">
-      <c r="A3" s="46" t="s">
-        <v>85</v>
-      </c>
-      <c r="B3" s="46" t="s">
-        <v>463</v>
-      </c>
-      <c r="C3" s="46"/>
+      <c r="A3" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="B3" s="58" t="s">
+        <v>500</v>
+      </c>
+      <c r="C3" s="58"/>
       <c r="D3" s="38" t="s">
-        <v>464</v>
+        <v>501</v>
       </c>
       <c r="E3" s="45" t="s">
-        <v>465</v>
+        <v>502</v>
       </c>
       <c r="F3" s="45"/>
       <c r="G3" s="45" t="s">
-        <v>465</v>
+        <v>502</v>
       </c>
       <c r="H3" s="45"/>
       <c r="I3" s="45" t="s">
-        <v>465</v>
+        <v>502</v>
       </c>
       <c r="J3" s="45"/>
       <c r="K3" s="45" t="s">
-        <v>465</v>
+        <v>502</v>
       </c>
       <c r="L3" s="38"/>
       <c r="M3" s="45" t="s">
-        <v>466</v>
+        <v>503</v>
       </c>
       <c r="N3" s="45" t="s">
-        <v>467</v>
+        <v>504</v>
       </c>
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="29.25">
-      <c r="A4" s="46"/>
-      <c r="B4" s="46" t="s">
-        <v>468</v>
-      </c>
-      <c r="C4" s="46"/>
+      <c r="A4" s="58"/>
+      <c r="B4" s="58" t="s">
+        <v>505</v>
+      </c>
+      <c r="C4" s="58"/>
       <c r="D4" s="38" t="s">
-        <v>469</v>
+        <v>506</v>
       </c>
       <c r="E4" s="38"/>
       <c r="F4" s="38"/>
@@ -6606,29 +7034,29 @@
       <c r="K4" s="38"/>
       <c r="L4" s="38"/>
       <c r="M4" s="45" t="s">
-        <v>470</v>
+        <v>507</v>
       </c>
       <c r="N4" s="45" t="s">
-        <v>471</v>
+        <v>508</v>
       </c>
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1">
-      <c r="A5" s="46"/>
-      <c r="B5" s="46" t="s">
-        <v>472</v>
-      </c>
-      <c r="C5" s="46"/>
+      <c r="A5" s="58"/>
+      <c r="B5" s="58" t="s">
+        <v>509</v>
+      </c>
+      <c r="C5" s="58"/>
       <c r="D5" s="39" t="s">
-        <v>473</v>
+        <v>510</v>
       </c>
       <c r="E5" s="38"/>
       <c r="F5" s="38"/>
       <c r="G5" s="45" t="s">
-        <v>474</v>
+        <v>511</v>
       </c>
       <c r="H5" s="45"/>
       <c r="I5" s="45" t="s">
-        <v>474</v>
+        <v>511</v>
       </c>
       <c r="J5" s="45"/>
       <c r="K5" s="38"/>
@@ -6637,13 +7065,13 @@
       <c r="N5" s="38"/>
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="44.25">
-      <c r="A6" s="46"/>
-      <c r="B6" s="46" t="s">
-        <v>475</v>
-      </c>
-      <c r="C6" s="46"/>
+      <c r="A6" s="58"/>
+      <c r="B6" s="58" t="s">
+        <v>512</v>
+      </c>
+      <c r="C6" s="58"/>
       <c r="D6" s="39" t="s">
-        <v>476</v>
+        <v>513</v>
       </c>
       <c r="E6" s="38"/>
       <c r="F6" s="38"/>
@@ -6654,119 +7082,119 @@
       <c r="K6" s="38"/>
       <c r="L6" s="38"/>
       <c r="M6" s="45" t="s">
-        <v>477</v>
+        <v>514</v>
       </c>
       <c r="N6" s="45" t="s">
-        <v>478</v>
+        <v>515</v>
       </c>
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1">
-      <c r="A7" s="46"/>
-      <c r="B7" s="46" t="s">
-        <v>479</v>
-      </c>
-      <c r="C7" s="46"/>
+      <c r="A7" s="58"/>
+      <c r="B7" s="58" t="s">
+        <v>516</v>
+      </c>
+      <c r="C7" s="58"/>
       <c r="D7" s="39" t="s">
-        <v>480</v>
+        <v>517</v>
       </c>
       <c r="E7" s="45" t="s">
-        <v>481</v>
+        <v>518</v>
       </c>
       <c r="F7" s="45"/>
       <c r="G7" s="45" t="s">
-        <v>481</v>
+        <v>518</v>
       </c>
       <c r="H7" s="45"/>
       <c r="I7" s="45" t="s">
-        <v>481</v>
+        <v>518</v>
       </c>
       <c r="J7" s="45"/>
       <c r="K7" s="45" t="s">
-        <v>481</v>
+        <v>518</v>
       </c>
       <c r="L7" s="38"/>
       <c r="M7" s="38"/>
       <c r="N7" s="38"/>
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1">
-      <c r="A8" s="46"/>
-      <c r="B8" s="46" t="s">
-        <v>482</v>
-      </c>
-      <c r="C8" s="46"/>
+      <c r="A8" s="58"/>
+      <c r="B8" s="58" t="s">
+        <v>519</v>
+      </c>
+      <c r="C8" s="58"/>
       <c r="D8" s="38" t="s">
-        <v>483</v>
+        <v>520</v>
       </c>
       <c r="E8" s="45" t="s">
-        <v>484</v>
+        <v>521</v>
       </c>
       <c r="F8" s="45"/>
       <c r="G8" s="38" t="s">
-        <v>484</v>
+        <v>521</v>
       </c>
       <c r="H8" s="38"/>
       <c r="I8" s="45" t="s">
-        <v>484</v>
+        <v>521</v>
       </c>
       <c r="J8" s="45"/>
       <c r="K8" s="45" t="s">
-        <v>484</v>
+        <v>521</v>
       </c>
       <c r="L8" s="38"/>
       <c r="M8" s="38"/>
       <c r="N8" s="38"/>
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="73.5">
-      <c r="A9" s="46"/>
-      <c r="B9" s="46" t="s">
-        <v>485</v>
-      </c>
-      <c r="C9" s="46"/>
+      <c r="A9" s="58"/>
+      <c r="B9" s="58" t="s">
+        <v>522</v>
+      </c>
+      <c r="C9" s="58"/>
       <c r="D9" s="38" t="s">
-        <v>486</v>
+        <v>523</v>
       </c>
       <c r="E9" s="45" t="s">
-        <v>487</v>
+        <v>524</v>
       </c>
       <c r="F9" s="45"/>
       <c r="G9" s="45" t="s">
-        <v>487</v>
+        <v>524</v>
       </c>
       <c r="H9" s="45"/>
       <c r="I9" s="45" t="s">
-        <v>487</v>
+        <v>524</v>
       </c>
       <c r="J9" s="45"/>
       <c r="K9" s="45" t="s">
-        <v>487</v>
+        <v>524</v>
       </c>
       <c r="L9" s="38"/>
       <c r="M9" s="45" t="s">
-        <v>488</v>
+        <v>525</v>
       </c>
       <c r="N9" s="45" t="s">
-        <v>489</v>
+        <v>526</v>
       </c>
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="29.25">
-      <c r="A10" s="46"/>
-      <c r="B10" s="46" t="s">
-        <v>490</v>
-      </c>
-      <c r="C10" s="46"/>
+      <c r="A10" s="58"/>
+      <c r="B10" s="58" t="s">
+        <v>527</v>
+      </c>
+      <c r="C10" s="58"/>
       <c r="D10" s="39" t="s">
-        <v>491</v>
+        <v>528</v>
       </c>
       <c r="E10" s="38"/>
       <c r="F10" s="38"/>
       <c r="G10" s="45" t="s">
-        <v>492</v>
+        <v>529</v>
       </c>
       <c r="H10" s="45" t="s">
-        <v>493</v>
+        <v>530</v>
       </c>
       <c r="I10" s="45" t="s">
-        <v>494</v>
+        <v>531</v>
       </c>
       <c r="J10" s="45"/>
       <c r="K10" s="38"/>
@@ -6775,27 +7203,27 @@
       <c r="N10" s="38"/>
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="29.25">
-      <c r="A11" s="46"/>
-      <c r="B11" s="46" t="s">
-        <v>495</v>
-      </c>
-      <c r="C11" s="46"/>
+      <c r="A11" s="58"/>
+      <c r="B11" s="58" t="s">
+        <v>532</v>
+      </c>
+      <c r="C11" s="58"/>
       <c r="D11" s="39" t="s">
-        <v>496</v>
+        <v>533</v>
       </c>
       <c r="E11" s="38"/>
       <c r="F11" s="38"/>
       <c r="G11" s="38" t="s">
-        <v>497</v>
+        <v>534</v>
       </c>
       <c r="H11" s="45" t="s">
-        <v>498</v>
+        <v>535</v>
       </c>
       <c r="I11" s="45" t="s">
-        <v>499</v>
+        <v>536</v>
       </c>
       <c r="J11" s="45" t="s">
-        <v>500</v>
+        <v>537</v>
       </c>
       <c r="K11" s="38"/>
       <c r="L11" s="38"/>
@@ -6803,773 +7231,775 @@
       <c r="N11" s="38"/>
     </row>
     <row r="12" spans="1:14" s="1" customFormat="1">
-      <c r="A12" s="46" t="s">
-        <v>501</v>
-      </c>
-      <c r="B12" s="46" t="s">
-        <v>502</v>
-      </c>
-      <c r="C12" s="46"/>
+      <c r="A12" s="58" t="s">
+        <v>538</v>
+      </c>
+      <c r="B12" s="58" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="58"/>
       <c r="D12" s="38" t="s">
-        <v>46</v>
-      </c>
-      <c r="E12" s="47" t="s">
-        <v>48</v>
-      </c>
-      <c r="F12" s="47"/>
-      <c r="G12" s="47" t="s">
-        <v>48</v>
-      </c>
-      <c r="H12" s="47"/>
-      <c r="I12" s="47" t="s">
-        <v>48</v>
-      </c>
-      <c r="J12" s="47"/>
-      <c r="K12" s="47" t="s">
-        <v>48</v>
-      </c>
-      <c r="L12" s="47"/>
-      <c r="M12" s="46"/>
-      <c r="N12" s="46"/>
+        <v>83</v>
+      </c>
+      <c r="E12" s="62" t="s">
+        <v>85</v>
+      </c>
+      <c r="F12" s="62"/>
+      <c r="G12" s="62" t="s">
+        <v>85</v>
+      </c>
+      <c r="H12" s="62"/>
+      <c r="I12" s="62" t="s">
+        <v>85</v>
+      </c>
+      <c r="J12" s="62"/>
+      <c r="K12" s="62" t="s">
+        <v>85</v>
+      </c>
+      <c r="L12" s="62"/>
+      <c r="M12" s="58"/>
+      <c r="N12" s="58"/>
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1">
-      <c r="A13" s="46"/>
-      <c r="B13" s="46" t="s">
-        <v>503</v>
-      </c>
-      <c r="C13" s="46"/>
+      <c r="A13" s="58"/>
+      <c r="B13" s="58" t="s">
+        <v>539</v>
+      </c>
+      <c r="C13" s="58"/>
       <c r="D13" s="38" t="s">
-        <v>504</v>
-      </c>
-      <c r="E13" s="48" t="s">
-        <v>505</v>
-      </c>
-      <c r="F13" s="46"/>
-      <c r="G13" s="48" t="s">
-        <v>506</v>
-      </c>
-      <c r="H13" s="46"/>
-      <c r="I13" s="48" t="s">
-        <v>507</v>
-      </c>
-      <c r="J13" s="46"/>
-      <c r="K13" s="46"/>
-      <c r="L13" s="46"/>
-      <c r="M13" s="47" t="s">
-        <v>508</v>
-      </c>
-      <c r="N13" s="46"/>
+        <v>540</v>
+      </c>
+      <c r="E13" s="63" t="s">
+        <v>541</v>
+      </c>
+      <c r="F13" s="58"/>
+      <c r="G13" s="63" t="s">
+        <v>542</v>
+      </c>
+      <c r="H13" s="58"/>
+      <c r="I13" s="63" t="s">
+        <v>543</v>
+      </c>
+      <c r="J13" s="58"/>
+      <c r="K13" s="58"/>
+      <c r="L13" s="58"/>
+      <c r="M13" s="62" t="s">
+        <v>544</v>
+      </c>
+      <c r="N13" s="58"/>
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="30.75">
-      <c r="A14" s="46"/>
-      <c r="B14" s="46" t="s">
-        <v>509</v>
-      </c>
-      <c r="C14" s="46"/>
+      <c r="A14" s="58"/>
+      <c r="B14" s="58" t="s">
+        <v>545</v>
+      </c>
+      <c r="C14" s="58"/>
       <c r="D14" s="39" t="s">
-        <v>510</v>
+        <v>546</v>
       </c>
       <c r="E14" s="45" t="s">
-        <v>511</v>
+        <v>547</v>
       </c>
       <c r="F14" s="45" t="s">
-        <v>512</v>
+        <v>548</v>
       </c>
       <c r="G14" s="45" t="s">
-        <v>511</v>
+        <v>547</v>
       </c>
       <c r="H14" s="38" t="s">
-        <v>513</v>
+        <v>549</v>
       </c>
       <c r="I14" s="45" t="s">
-        <v>514</v>
+        <v>550</v>
       </c>
       <c r="J14" s="45" t="s">
-        <v>513</v>
+        <v>549</v>
       </c>
       <c r="K14" s="45" t="s">
-        <v>514</v>
+        <v>550</v>
       </c>
       <c r="L14" s="45" t="s">
-        <v>515</v>
+        <v>551</v>
       </c>
       <c r="M14" s="38"/>
       <c r="N14" s="38"/>
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" ht="44.25">
-      <c r="A15" s="46"/>
-      <c r="B15" s="46" t="s">
-        <v>516</v>
-      </c>
-      <c r="C15" s="46"/>
+      <c r="A15" s="58"/>
+      <c r="B15" s="58" t="s">
+        <v>552</v>
+      </c>
+      <c r="C15" s="58"/>
       <c r="D15" s="39" t="s">
-        <v>517</v>
+        <v>553</v>
       </c>
       <c r="E15" s="45" t="s">
-        <v>518</v>
+        <v>554</v>
       </c>
       <c r="F15" s="45" t="s">
-        <v>519</v>
+        <v>555</v>
       </c>
       <c r="G15" s="38" t="s">
-        <v>518</v>
+        <v>554</v>
       </c>
       <c r="H15" s="45" t="s">
-        <v>520</v>
+        <v>556</v>
       </c>
       <c r="I15" s="45" t="s">
-        <v>518</v>
+        <v>554</v>
       </c>
       <c r="J15" s="45" t="s">
-        <v>520</v>
+        <v>556</v>
       </c>
       <c r="K15" s="45" t="s">
-        <v>518</v>
+        <v>554</v>
       </c>
       <c r="L15" s="45" t="s">
-        <v>519</v>
+        <v>555</v>
       </c>
       <c r="M15" s="45" t="s">
-        <v>521</v>
+        <v>557</v>
       </c>
       <c r="N15" s="45" t="s">
-        <v>508</v>
+        <v>544</v>
       </c>
     </row>
     <row r="16" spans="1:14" s="1" customFormat="1" ht="30.75">
-      <c r="A16" s="46"/>
-      <c r="B16" s="46" t="s">
-        <v>522</v>
-      </c>
-      <c r="C16" s="46"/>
+      <c r="A16" s="58"/>
+      <c r="B16" s="58" t="s">
+        <v>558</v>
+      </c>
+      <c r="C16" s="58"/>
       <c r="D16" s="38" t="s">
-        <v>523</v>
+        <v>559</v>
       </c>
       <c r="E16" s="45" t="s">
-        <v>524</v>
+        <v>560</v>
       </c>
       <c r="F16" s="45" t="s">
-        <v>525</v>
+        <v>561</v>
       </c>
       <c r="G16" s="45" t="s">
-        <v>524</v>
+        <v>560</v>
       </c>
       <c r="H16" s="45" t="s">
-        <v>526</v>
+        <v>562</v>
       </c>
       <c r="I16" s="45" t="s">
-        <v>524</v>
+        <v>560</v>
       </c>
       <c r="J16" s="38"/>
       <c r="K16" s="45" t="s">
-        <v>524</v>
+        <v>560</v>
       </c>
       <c r="L16" s="38" t="s">
-        <v>525</v>
+        <v>561</v>
       </c>
       <c r="M16" s="45" t="s">
+        <v>563</v>
+      </c>
+      <c r="N16" s="45" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" s="1" customFormat="1" ht="198">
+      <c r="A17" s="58" t="s">
+        <v>565</v>
+      </c>
+      <c r="B17" s="58"/>
+      <c r="C17" s="58"/>
+      <c r="D17" s="40" t="s">
+        <v>95</v>
+      </c>
+      <c r="E17" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="F17" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="G17" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="H17" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="I17" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="J17" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="K17" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="L17" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="M17" s="38" t="s">
+        <v>168</v>
+      </c>
+      <c r="N17" s="38" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" s="47" customFormat="1" hidden="1">
+      <c r="A18" s="58" t="s">
+        <v>99</v>
+      </c>
+      <c r="B18" s="60" t="s">
+        <v>122</v>
+      </c>
+      <c r="C18" s="46" t="s">
+        <v>500</v>
+      </c>
+      <c r="D18" s="46" t="s">
+        <v>501</v>
+      </c>
+      <c r="E18" s="61"/>
+      <c r="F18" s="61"/>
+      <c r="G18" s="60"/>
+      <c r="H18" s="60"/>
+      <c r="I18" s="60"/>
+      <c r="J18" s="60"/>
+      <c r="K18" s="60"/>
+      <c r="L18" s="60"/>
+      <c r="M18" s="60"/>
+      <c r="N18" s="60"/>
+    </row>
+    <row r="19" spans="1:14" s="47" customFormat="1" hidden="1">
+      <c r="A19" s="58"/>
+      <c r="B19" s="60"/>
+      <c r="C19" s="46" t="s">
+        <v>505</v>
+      </c>
+      <c r="D19" s="46" t="s">
+        <v>506</v>
+      </c>
+      <c r="E19" s="61"/>
+      <c r="F19" s="61"/>
+      <c r="G19" s="60"/>
+      <c r="H19" s="60"/>
+      <c r="I19" s="60"/>
+      <c r="J19" s="60"/>
+      <c r="K19" s="60"/>
+      <c r="L19" s="60"/>
+      <c r="M19" s="60"/>
+      <c r="N19" s="60"/>
+    </row>
+    <row r="20" spans="1:14" s="47" customFormat="1" hidden="1">
+      <c r="A20" s="58"/>
+      <c r="B20" s="60"/>
+      <c r="C20" s="46" t="s">
+        <v>509</v>
+      </c>
+      <c r="D20" s="48" t="s">
+        <v>510</v>
+      </c>
+      <c r="E20" s="61"/>
+      <c r="F20" s="61"/>
+      <c r="G20" s="60"/>
+      <c r="H20" s="60"/>
+      <c r="I20" s="60"/>
+      <c r="J20" s="60"/>
+      <c r="K20" s="60"/>
+      <c r="L20" s="60"/>
+      <c r="M20" s="60"/>
+      <c r="N20" s="60"/>
+    </row>
+    <row r="21" spans="1:14" s="47" customFormat="1" hidden="1">
+      <c r="A21" s="58"/>
+      <c r="B21" s="60"/>
+      <c r="C21" s="46" t="s">
+        <v>512</v>
+      </c>
+      <c r="D21" s="48" t="s">
+        <v>513</v>
+      </c>
+      <c r="E21" s="61"/>
+      <c r="F21" s="61"/>
+      <c r="G21" s="60"/>
+      <c r="H21" s="60"/>
+      <c r="I21" s="60"/>
+      <c r="J21" s="60"/>
+      <c r="K21" s="60"/>
+      <c r="L21" s="60"/>
+      <c r="M21" s="60"/>
+      <c r="N21" s="60"/>
+    </row>
+    <row r="22" spans="1:14" s="47" customFormat="1" hidden="1">
+      <c r="A22" s="58"/>
+      <c r="B22" s="60"/>
+      <c r="C22" s="46" t="s">
+        <v>516</v>
+      </c>
+      <c r="D22" s="48" t="s">
+        <v>517</v>
+      </c>
+      <c r="E22" s="61"/>
+      <c r="F22" s="61"/>
+      <c r="G22" s="60"/>
+      <c r="H22" s="60"/>
+      <c r="I22" s="60"/>
+      <c r="J22" s="60"/>
+      <c r="K22" s="60"/>
+      <c r="L22" s="60"/>
+      <c r="M22" s="60"/>
+      <c r="N22" s="60"/>
+    </row>
+    <row r="23" spans="1:14" s="47" customFormat="1" hidden="1">
+      <c r="A23" s="58"/>
+      <c r="B23" s="60"/>
+      <c r="C23" s="46" t="s">
+        <v>519</v>
+      </c>
+      <c r="D23" s="46" t="s">
+        <v>520</v>
+      </c>
+      <c r="E23" s="61"/>
+      <c r="F23" s="61"/>
+      <c r="G23" s="60"/>
+      <c r="H23" s="60"/>
+      <c r="I23" s="60"/>
+      <c r="J23" s="60"/>
+      <c r="K23" s="60"/>
+      <c r="L23" s="60"/>
+      <c r="M23" s="60"/>
+      <c r="N23" s="60"/>
+    </row>
+    <row r="24" spans="1:14" s="47" customFormat="1" hidden="1">
+      <c r="A24" s="58"/>
+      <c r="B24" s="60"/>
+      <c r="C24" s="46" t="s">
+        <v>522</v>
+      </c>
+      <c r="D24" s="46" t="s">
+        <v>523</v>
+      </c>
+      <c r="E24" s="61"/>
+      <c r="F24" s="61"/>
+      <c r="G24" s="60"/>
+      <c r="H24" s="60"/>
+      <c r="I24" s="60"/>
+      <c r="J24" s="60"/>
+      <c r="K24" s="60"/>
+      <c r="L24" s="60"/>
+      <c r="M24" s="60"/>
+      <c r="N24" s="60"/>
+    </row>
+    <row r="25" spans="1:14" s="47" customFormat="1" hidden="1">
+      <c r="A25" s="58"/>
+      <c r="B25" s="60"/>
+      <c r="C25" s="46" t="s">
         <v>527</v>
       </c>
-      <c r="N16" s="45" t="s">
+      <c r="D25" s="48" t="s">
         <v>528</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" s="1" customFormat="1">
-      <c r="A17" s="46"/>
-      <c r="B17" s="46" t="s">
-        <v>529</v>
-      </c>
-      <c r="C17" s="46"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="38"/>
-      <c r="J17" s="38"/>
-      <c r="K17" s="38"/>
-      <c r="L17" s="38"/>
-      <c r="M17" s="38"/>
-      <c r="N17" s="38"/>
-    </row>
-    <row r="18" spans="1:14" s="1" customFormat="1" ht="336">
-      <c r="A18" s="46" t="s">
-        <v>530</v>
-      </c>
-      <c r="B18" s="46"/>
-      <c r="C18" s="46"/>
-      <c r="D18" s="40" t="s">
-        <v>58</v>
-      </c>
-      <c r="E18" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="F18" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="G18" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="H18" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="I18" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="J18" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="K18" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="L18" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="M18" s="38" t="s">
-        <v>131</v>
-      </c>
-      <c r="N18" s="38" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" s="1" customFormat="1">
-      <c r="A19" s="46" t="s">
-        <v>62</v>
-      </c>
-      <c r="B19" s="46" t="s">
-        <v>85</v>
-      </c>
-      <c r="C19" s="38" t="s">
-        <v>463</v>
-      </c>
-      <c r="D19" s="38" t="s">
-        <v>464</v>
-      </c>
-      <c r="E19" s="47"/>
-      <c r="F19" s="47"/>
-      <c r="G19" s="46"/>
-      <c r="H19" s="46"/>
-      <c r="I19" s="46"/>
-      <c r="J19" s="46"/>
-      <c r="K19" s="46"/>
-      <c r="L19" s="46"/>
-      <c r="M19" s="46"/>
-      <c r="N19" s="46"/>
-    </row>
-    <row r="20" spans="1:14" s="1" customFormat="1">
-      <c r="A20" s="46"/>
-      <c r="B20" s="46"/>
-      <c r="C20" s="38" t="s">
-        <v>468</v>
-      </c>
-      <c r="D20" s="38" t="s">
-        <v>469</v>
-      </c>
-      <c r="E20" s="47"/>
-      <c r="F20" s="47"/>
-      <c r="G20" s="46"/>
-      <c r="H20" s="46"/>
-      <c r="I20" s="46"/>
-      <c r="J20" s="46"/>
-      <c r="K20" s="46"/>
-      <c r="L20" s="46"/>
-      <c r="M20" s="46"/>
-      <c r="N20" s="46"/>
-    </row>
-    <row r="21" spans="1:14" s="1" customFormat="1">
-      <c r="A21" s="46"/>
-      <c r="B21" s="46"/>
-      <c r="C21" s="38" t="s">
-        <v>472</v>
-      </c>
-      <c r="D21" s="39" t="s">
-        <v>473</v>
-      </c>
-      <c r="E21" s="47"/>
-      <c r="F21" s="47"/>
-      <c r="G21" s="46"/>
-      <c r="H21" s="46"/>
-      <c r="I21" s="46"/>
-      <c r="J21" s="46"/>
-      <c r="K21" s="46"/>
-      <c r="L21" s="46"/>
-      <c r="M21" s="46"/>
-      <c r="N21" s="46"/>
-    </row>
-    <row r="22" spans="1:14" s="1" customFormat="1">
-      <c r="A22" s="46"/>
-      <c r="B22" s="46"/>
-      <c r="C22" s="38" t="s">
-        <v>475</v>
-      </c>
-      <c r="D22" s="39" t="s">
-        <v>476</v>
-      </c>
-      <c r="E22" s="47"/>
-      <c r="F22" s="47"/>
-      <c r="G22" s="46"/>
-      <c r="H22" s="46"/>
-      <c r="I22" s="46"/>
-      <c r="J22" s="46"/>
-      <c r="K22" s="46"/>
-      <c r="L22" s="46"/>
-      <c r="M22" s="46"/>
-      <c r="N22" s="46"/>
-    </row>
-    <row r="23" spans="1:14" s="1" customFormat="1">
-      <c r="A23" s="46"/>
-      <c r="B23" s="46"/>
-      <c r="C23" s="38" t="s">
-        <v>479</v>
-      </c>
-      <c r="D23" s="39" t="s">
-        <v>480</v>
-      </c>
-      <c r="E23" s="47"/>
-      <c r="F23" s="47"/>
-      <c r="G23" s="46"/>
-      <c r="H23" s="46"/>
-      <c r="I23" s="46"/>
-      <c r="J23" s="46"/>
-      <c r="K23" s="46"/>
-      <c r="L23" s="46"/>
-      <c r="M23" s="46"/>
-      <c r="N23" s="46"/>
-    </row>
-    <row r="24" spans="1:14" s="1" customFormat="1">
-      <c r="A24" s="46"/>
-      <c r="B24" s="46"/>
-      <c r="C24" s="38" t="s">
-        <v>482</v>
-      </c>
-      <c r="D24" s="38" t="s">
-        <v>483</v>
-      </c>
-      <c r="E24" s="47"/>
-      <c r="F24" s="47"/>
-      <c r="G24" s="46"/>
-      <c r="H24" s="46"/>
-      <c r="I24" s="46"/>
-      <c r="J24" s="46"/>
-      <c r="K24" s="46"/>
-      <c r="L24" s="46"/>
-      <c r="M24" s="46"/>
-      <c r="N24" s="46"/>
-    </row>
-    <row r="25" spans="1:14" s="1" customFormat="1">
-      <c r="A25" s="46"/>
-      <c r="B25" s="46"/>
-      <c r="C25" s="38" t="s">
-        <v>485</v>
-      </c>
-      <c r="D25" s="38" t="s">
-        <v>486</v>
-      </c>
-      <c r="E25" s="47"/>
-      <c r="F25" s="47"/>
-      <c r="G25" s="46"/>
-      <c r="H25" s="46"/>
-      <c r="I25" s="46"/>
-      <c r="J25" s="46"/>
-      <c r="K25" s="46"/>
-      <c r="L25" s="46"/>
-      <c r="M25" s="46"/>
-      <c r="N25" s="46"/>
-    </row>
-    <row r="26" spans="1:14" s="1" customFormat="1">
-      <c r="A26" s="46"/>
-      <c r="B26" s="46"/>
-      <c r="C26" s="38" t="s">
-        <v>490</v>
-      </c>
-      <c r="D26" s="39" t="s">
-        <v>491</v>
-      </c>
-      <c r="E26" s="47"/>
-      <c r="F26" s="47"/>
-      <c r="G26" s="46"/>
-      <c r="H26" s="46"/>
-      <c r="I26" s="46"/>
-      <c r="J26" s="46"/>
-      <c r="K26" s="46"/>
-      <c r="L26" s="46"/>
-      <c r="M26" s="46"/>
-      <c r="N26" s="46"/>
-    </row>
-    <row r="27" spans="1:14" s="1" customFormat="1">
-      <c r="A27" s="46"/>
-      <c r="B27" s="46"/>
-      <c r="C27" s="38" t="s">
-        <v>495</v>
-      </c>
-      <c r="D27" s="39" t="s">
-        <v>496</v>
-      </c>
-      <c r="E27" s="47"/>
-      <c r="F27" s="47"/>
-      <c r="G27" s="46"/>
-      <c r="H27" s="46"/>
-      <c r="I27" s="46"/>
-      <c r="J27" s="46"/>
-      <c r="K27" s="46"/>
-      <c r="L27" s="46"/>
-      <c r="M27" s="46"/>
-      <c r="N27" s="46"/>
-    </row>
-    <row r="28" spans="1:14" s="1" customFormat="1" ht="76.5">
-      <c r="A28" s="46"/>
-      <c r="B28" s="46" t="s">
-        <v>530</v>
-      </c>
-      <c r="C28" s="46"/>
+      <c r="E25" s="61"/>
+      <c r="F25" s="61"/>
+      <c r="G25" s="60"/>
+      <c r="H25" s="60"/>
+      <c r="I25" s="60"/>
+      <c r="J25" s="60"/>
+      <c r="K25" s="60"/>
+      <c r="L25" s="60"/>
+      <c r="M25" s="60"/>
+      <c r="N25" s="60"/>
+    </row>
+    <row r="26" spans="1:14" s="47" customFormat="1" hidden="1">
+      <c r="A26" s="58"/>
+      <c r="B26" s="60"/>
+      <c r="C26" s="46" t="s">
+        <v>532</v>
+      </c>
+      <c r="D26" s="48" t="s">
+        <v>533</v>
+      </c>
+      <c r="E26" s="61"/>
+      <c r="F26" s="61"/>
+      <c r="G26" s="60"/>
+      <c r="H26" s="60"/>
+      <c r="I26" s="60"/>
+      <c r="J26" s="60"/>
+      <c r="K26" s="60"/>
+      <c r="L26" s="60"/>
+      <c r="M26" s="60"/>
+      <c r="N26" s="60"/>
+    </row>
+    <row r="27" spans="1:14" s="1" customFormat="1" ht="60.75">
+      <c r="A27" s="58"/>
+      <c r="B27" s="58" t="s">
+        <v>566</v>
+      </c>
+      <c r="C27" s="58"/>
+      <c r="D27" s="38" t="s">
+        <v>95</v>
+      </c>
+      <c r="E27" s="38" t="s">
+        <v>567</v>
+      </c>
+      <c r="F27" s="38" t="s">
+        <v>567</v>
+      </c>
+      <c r="G27" s="38" t="s">
+        <v>567</v>
+      </c>
+      <c r="H27" s="38" t="s">
+        <v>567</v>
+      </c>
+      <c r="I27" s="38" t="s">
+        <v>567</v>
+      </c>
+      <c r="J27" s="38" t="s">
+        <v>567</v>
+      </c>
+      <c r="K27" s="38" t="s">
+        <v>567</v>
+      </c>
+      <c r="L27" s="38" t="s">
+        <v>567</v>
+      </c>
+      <c r="M27" s="38" t="s">
+        <v>567</v>
+      </c>
+      <c r="N27" s="38" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" s="1" customFormat="1" ht="30.75">
+      <c r="A28" s="58"/>
+      <c r="B28" s="58" t="s">
+        <v>568</v>
+      </c>
+      <c r="C28" s="58"/>
       <c r="D28" s="38" t="s">
-        <v>58</v>
+        <v>569</v>
       </c>
       <c r="E28" s="38" t="s">
-        <v>531</v>
+        <v>569</v>
       </c>
       <c r="F28" s="38" t="s">
-        <v>531</v>
+        <v>569</v>
       </c>
       <c r="G28" s="38" t="s">
-        <v>531</v>
+        <v>569</v>
       </c>
       <c r="H28" s="38" t="s">
-        <v>531</v>
+        <v>569</v>
       </c>
       <c r="I28" s="38" t="s">
-        <v>531</v>
+        <v>569</v>
       </c>
       <c r="J28" s="38" t="s">
-        <v>531</v>
+        <v>569</v>
       </c>
       <c r="K28" s="38" t="s">
-        <v>531</v>
+        <v>569</v>
       </c>
       <c r="L28" s="38" t="s">
-        <v>531</v>
+        <v>569</v>
       </c>
       <c r="M28" s="38" t="s">
-        <v>531</v>
+        <v>569</v>
       </c>
       <c r="N28" s="38" t="s">
-        <v>531</v>
+        <v>569</v>
       </c>
     </row>
     <row r="29" spans="1:14" s="1" customFormat="1" ht="30.75">
-      <c r="A29" s="46"/>
-      <c r="B29" s="46" t="s">
+      <c r="A29" s="58"/>
+      <c r="B29" s="58" t="s">
+        <v>570</v>
+      </c>
+      <c r="C29" s="58"/>
+      <c r="D29" s="38" t="s">
+        <v>569</v>
+      </c>
+      <c r="E29" s="38" t="s">
+        <v>569</v>
+      </c>
+      <c r="F29" s="38" t="s">
+        <v>569</v>
+      </c>
+      <c r="G29" s="38" t="s">
+        <v>569</v>
+      </c>
+      <c r="H29" s="38" t="s">
+        <v>569</v>
+      </c>
+      <c r="I29" s="38" t="s">
+        <v>569</v>
+      </c>
+      <c r="J29" s="38" t="s">
+        <v>569</v>
+      </c>
+      <c r="K29" s="38" t="s">
+        <v>569</v>
+      </c>
+      <c r="L29" s="38" t="s">
+        <v>569</v>
+      </c>
+      <c r="M29" s="38" t="s">
+        <v>569</v>
+      </c>
+      <c r="N29" s="38" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" s="1" customFormat="1" ht="183">
+      <c r="A30" s="58"/>
+      <c r="B30" s="58" t="s">
+        <v>571</v>
+      </c>
+      <c r="C30" s="58"/>
+      <c r="D30" s="50" t="s">
+        <v>572</v>
+      </c>
+      <c r="E30" s="38" t="s">
+        <v>573</v>
+      </c>
+      <c r="F30" s="38" t="s">
+        <v>573</v>
+      </c>
+      <c r="G30" s="38" t="s">
+        <v>573</v>
+      </c>
+      <c r="H30" s="38" t="s">
+        <v>573</v>
+      </c>
+      <c r="I30" s="38" t="s">
+        <v>573</v>
+      </c>
+      <c r="J30" s="38" t="s">
+        <v>573</v>
+      </c>
+      <c r="K30" s="38" t="s">
+        <v>573</v>
+      </c>
+      <c r="L30" s="38" t="s">
+        <v>573</v>
+      </c>
+      <c r="M30" s="38" t="s">
+        <v>573</v>
+      </c>
+      <c r="N30" s="38" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" s="1" customFormat="1">
+      <c r="A31" s="58" t="s">
+        <v>102</v>
+      </c>
+      <c r="B31" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="C31" s="49" t="s">
+        <v>500</v>
+      </c>
+      <c r="D31" s="38" t="s">
+        <v>501</v>
+      </c>
+      <c r="E31" s="59"/>
+      <c r="F31" s="58"/>
+      <c r="G31" s="58"/>
+      <c r="H31" s="58"/>
+      <c r="I31" s="58"/>
+      <c r="J31" s="58"/>
+      <c r="K31" s="58"/>
+      <c r="L31" s="58"/>
+      <c r="M31" s="58"/>
+      <c r="N31" s="58"/>
+    </row>
+    <row r="32" spans="1:14" s="1" customFormat="1">
+      <c r="A32" s="58"/>
+      <c r="B32" s="58"/>
+      <c r="C32" s="49" t="s">
+        <v>505</v>
+      </c>
+      <c r="D32" s="38" t="s">
+        <v>506</v>
+      </c>
+      <c r="E32" s="59"/>
+      <c r="F32" s="58"/>
+      <c r="G32" s="58"/>
+      <c r="H32" s="58"/>
+      <c r="I32" s="58"/>
+      <c r="J32" s="58"/>
+      <c r="K32" s="58"/>
+      <c r="L32" s="58"/>
+      <c r="M32" s="58"/>
+      <c r="N32" s="58"/>
+    </row>
+    <row r="33" spans="1:14" s="1" customFormat="1">
+      <c r="A33" s="58"/>
+      <c r="B33" s="58"/>
+      <c r="C33" s="49" t="s">
+        <v>509</v>
+      </c>
+      <c r="D33" s="39" t="s">
+        <v>510</v>
+      </c>
+      <c r="E33" s="59"/>
+      <c r="F33" s="58"/>
+      <c r="G33" s="58"/>
+      <c r="H33" s="58"/>
+      <c r="I33" s="58"/>
+      <c r="J33" s="58"/>
+      <c r="K33" s="58"/>
+      <c r="L33" s="58"/>
+      <c r="M33" s="58"/>
+      <c r="N33" s="58"/>
+    </row>
+    <row r="34" spans="1:14" s="1" customFormat="1">
+      <c r="A34" s="58"/>
+      <c r="B34" s="58"/>
+      <c r="C34" s="49" t="s">
+        <v>512</v>
+      </c>
+      <c r="D34" s="39" t="s">
+        <v>513</v>
+      </c>
+      <c r="E34" s="59"/>
+      <c r="F34" s="58"/>
+      <c r="G34" s="58"/>
+      <c r="H34" s="58"/>
+      <c r="I34" s="58"/>
+      <c r="J34" s="58"/>
+      <c r="K34" s="58"/>
+      <c r="L34" s="58"/>
+      <c r="M34" s="58"/>
+      <c r="N34" s="58"/>
+    </row>
+    <row r="35" spans="1:14" s="1" customFormat="1">
+      <c r="A35" s="58"/>
+      <c r="B35" s="58"/>
+      <c r="C35" s="49" t="s">
+        <v>516</v>
+      </c>
+      <c r="D35" s="39" t="s">
+        <v>517</v>
+      </c>
+      <c r="E35" s="59"/>
+      <c r="F35" s="58"/>
+      <c r="G35" s="58"/>
+      <c r="H35" s="58"/>
+      <c r="I35" s="58"/>
+      <c r="J35" s="58"/>
+      <c r="K35" s="58"/>
+      <c r="L35" s="58"/>
+      <c r="M35" s="58"/>
+      <c r="N35" s="58"/>
+    </row>
+    <row r="36" spans="1:14" s="1" customFormat="1">
+      <c r="A36" s="58"/>
+      <c r="B36" s="58"/>
+      <c r="C36" s="49" t="s">
+        <v>519</v>
+      </c>
+      <c r="D36" s="38" t="s">
+        <v>520</v>
+      </c>
+      <c r="E36" s="59"/>
+      <c r="F36" s="58"/>
+      <c r="G36" s="58"/>
+      <c r="H36" s="58"/>
+      <c r="I36" s="58"/>
+      <c r="J36" s="58"/>
+      <c r="K36" s="58"/>
+      <c r="L36" s="58"/>
+      <c r="M36" s="58"/>
+      <c r="N36" s="58"/>
+    </row>
+    <row r="37" spans="1:14" s="1" customFormat="1">
+      <c r="A37" s="58"/>
+      <c r="B37" s="58"/>
+      <c r="C37" s="49" t="s">
+        <v>522</v>
+      </c>
+      <c r="D37" s="38" t="s">
+        <v>523</v>
+      </c>
+      <c r="E37" s="59"/>
+      <c r="F37" s="58"/>
+      <c r="G37" s="58"/>
+      <c r="H37" s="58"/>
+      <c r="I37" s="58"/>
+      <c r="J37" s="58"/>
+      <c r="K37" s="58"/>
+      <c r="L37" s="58"/>
+      <c r="M37" s="58"/>
+      <c r="N37" s="58"/>
+    </row>
+    <row r="38" spans="1:14" s="1" customFormat="1">
+      <c r="A38" s="58"/>
+      <c r="B38" s="58"/>
+      <c r="C38" s="49" t="s">
+        <v>527</v>
+      </c>
+      <c r="D38" s="39" t="s">
+        <v>528</v>
+      </c>
+      <c r="E38" s="59"/>
+      <c r="F38" s="58"/>
+      <c r="G38" s="58"/>
+      <c r="H38" s="58"/>
+      <c r="I38" s="58"/>
+      <c r="J38" s="58"/>
+      <c r="K38" s="58"/>
+      <c r="L38" s="58"/>
+      <c r="M38" s="58"/>
+      <c r="N38" s="58"/>
+    </row>
+    <row r="39" spans="1:14" s="1" customFormat="1">
+      <c r="A39" s="58"/>
+      <c r="B39" s="58"/>
+      <c r="C39" s="38" t="s">
         <v>532</v>
       </c>
-      <c r="C29" s="46"/>
-      <c r="D29" s="38" t="s">
+      <c r="D39" s="51" t="s">
         <v>533</v>
       </c>
-      <c r="E29" s="38" t="s">
-        <v>533</v>
-      </c>
-      <c r="F29" s="38" t="s">
-        <v>533</v>
-      </c>
-      <c r="G29" s="38" t="s">
-        <v>533</v>
-      </c>
-      <c r="H29" s="38" t="s">
-        <v>533</v>
-      </c>
-      <c r="I29" s="38" t="s">
-        <v>533</v>
-      </c>
-      <c r="J29" s="38" t="s">
-        <v>533</v>
-      </c>
-      <c r="K29" s="38" t="s">
-        <v>533</v>
-      </c>
-      <c r="L29" s="38" t="s">
-        <v>533</v>
-      </c>
-      <c r="M29" s="38" t="s">
-        <v>533</v>
-      </c>
-      <c r="N29" s="38" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" s="1" customFormat="1" ht="30.75">
-      <c r="A30" s="46"/>
-      <c r="B30" s="46" t="s">
-        <v>534</v>
-      </c>
-      <c r="C30" s="46"/>
-      <c r="D30" s="38" t="s">
-        <v>533</v>
-      </c>
-      <c r="E30" s="38" t="s">
-        <v>533</v>
-      </c>
-      <c r="F30" s="38" t="s">
-        <v>533</v>
-      </c>
-      <c r="G30" s="38" t="s">
-        <v>533</v>
-      </c>
-      <c r="H30" s="38" t="s">
-        <v>533</v>
-      </c>
-      <c r="I30" s="38" t="s">
-        <v>533</v>
-      </c>
-      <c r="J30" s="38" t="s">
-        <v>533</v>
-      </c>
-      <c r="K30" s="38" t="s">
-        <v>533</v>
-      </c>
-      <c r="L30" s="38" t="s">
-        <v>533</v>
-      </c>
-      <c r="M30" s="38" t="s">
-        <v>533</v>
-      </c>
-      <c r="N30" s="38" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" s="1" customFormat="1" ht="244.5">
-      <c r="A31" s="46"/>
-      <c r="B31" s="46" t="s">
-        <v>535</v>
-      </c>
-      <c r="C31" s="46"/>
-      <c r="D31" s="38" t="s">
-        <v>536</v>
-      </c>
-      <c r="E31" s="38" t="s">
-        <v>537</v>
-      </c>
-      <c r="F31" s="38" t="s">
+      <c r="E39" s="58"/>
+      <c r="F39" s="58"/>
+      <c r="G39" s="58"/>
+      <c r="H39" s="58"/>
+      <c r="I39" s="58"/>
+      <c r="J39" s="58"/>
+      <c r="K39" s="58"/>
+      <c r="L39" s="58"/>
+      <c r="M39" s="58"/>
+      <c r="N39" s="58"/>
+    </row>
+    <row r="40" spans="1:14" s="1" customFormat="1">
+      <c r="A40" s="58"/>
+      <c r="B40" s="58" t="s">
         <v>538</v>
       </c>
-      <c r="G31" s="38" t="s">
-        <v>538</v>
-      </c>
-      <c r="H31" s="38" t="s">
-        <v>538</v>
-      </c>
-      <c r="I31" s="38" t="s">
-        <v>538</v>
-      </c>
-      <c r="J31" s="38" t="s">
-        <v>538</v>
-      </c>
-      <c r="K31" s="38" t="s">
-        <v>538</v>
-      </c>
-      <c r="L31" s="38" t="s">
-        <v>538</v>
-      </c>
-      <c r="M31" s="38" t="s">
-        <v>538</v>
-      </c>
-      <c r="N31" s="38" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" s="1" customFormat="1">
-      <c r="A32" s="46" t="s">
-        <v>65</v>
-      </c>
-      <c r="B32" s="46" t="s">
-        <v>85</v>
-      </c>
-      <c r="C32" s="38" t="s">
-        <v>463</v>
-      </c>
-      <c r="D32" s="38" t="s">
-        <v>464</v>
-      </c>
-      <c r="E32" s="46"/>
-      <c r="F32" s="46"/>
-      <c r="G32" s="46"/>
-      <c r="H32" s="46"/>
-      <c r="I32" s="46"/>
-      <c r="J32" s="46"/>
-      <c r="K32" s="46"/>
-      <c r="L32" s="46"/>
-      <c r="M32" s="46"/>
-      <c r="N32" s="46"/>
-    </row>
-    <row r="33" spans="1:14" s="1" customFormat="1">
-      <c r="A33" s="46"/>
-      <c r="B33" s="46"/>
-      <c r="C33" s="38" t="s">
-        <v>468</v>
-      </c>
-      <c r="D33" s="38" t="s">
-        <v>469</v>
-      </c>
-      <c r="E33" s="46"/>
-      <c r="F33" s="46"/>
-      <c r="G33" s="46"/>
-      <c r="H33" s="46"/>
-      <c r="I33" s="46"/>
-      <c r="J33" s="46"/>
-      <c r="K33" s="46"/>
-      <c r="L33" s="46"/>
-      <c r="M33" s="46"/>
-      <c r="N33" s="46"/>
-    </row>
-    <row r="34" spans="1:14" s="1" customFormat="1">
-      <c r="A34" s="46"/>
-      <c r="B34" s="46"/>
-      <c r="C34" s="38" t="s">
-        <v>472</v>
-      </c>
-      <c r="D34" s="39" t="s">
-        <v>473</v>
-      </c>
-      <c r="E34" s="46"/>
-      <c r="F34" s="46"/>
-      <c r="G34" s="46"/>
-      <c r="H34" s="46"/>
-      <c r="I34" s="46"/>
-      <c r="J34" s="46"/>
-      <c r="K34" s="46"/>
-      <c r="L34" s="46"/>
-      <c r="M34" s="46"/>
-      <c r="N34" s="46"/>
-    </row>
-    <row r="35" spans="1:14" s="1" customFormat="1">
-      <c r="A35" s="46"/>
-      <c r="B35" s="46"/>
-      <c r="C35" s="38" t="s">
-        <v>475</v>
-      </c>
-      <c r="D35" s="39" t="s">
-        <v>476</v>
-      </c>
-      <c r="E35" s="46"/>
-      <c r="F35" s="46"/>
-      <c r="G35" s="46"/>
-      <c r="H35" s="46"/>
-      <c r="I35" s="46"/>
-      <c r="J35" s="46"/>
-      <c r="K35" s="46"/>
-      <c r="L35" s="46"/>
-      <c r="M35" s="46"/>
-      <c r="N35" s="46"/>
-    </row>
-    <row r="36" spans="1:14" s="1" customFormat="1">
-      <c r="A36" s="46"/>
-      <c r="B36" s="46"/>
-      <c r="C36" s="38" t="s">
-        <v>479</v>
-      </c>
-      <c r="D36" s="39" t="s">
-        <v>480</v>
-      </c>
-      <c r="E36" s="46"/>
-      <c r="F36" s="46"/>
-      <c r="G36" s="46"/>
-      <c r="H36" s="46"/>
-      <c r="I36" s="46"/>
-      <c r="J36" s="46"/>
-      <c r="K36" s="46"/>
-      <c r="L36" s="46"/>
-      <c r="M36" s="46"/>
-      <c r="N36" s="46"/>
-    </row>
-    <row r="37" spans="1:14" s="1" customFormat="1">
-      <c r="A37" s="46"/>
-      <c r="B37" s="46"/>
-      <c r="C37" s="38" t="s">
-        <v>482</v>
-      </c>
-      <c r="D37" s="38" t="s">
-        <v>483</v>
-      </c>
-      <c r="E37" s="46"/>
-      <c r="F37" s="46"/>
-      <c r="G37" s="46"/>
-      <c r="H37" s="46"/>
-      <c r="I37" s="46"/>
-      <c r="J37" s="46"/>
-      <c r="K37" s="46"/>
-      <c r="L37" s="46"/>
-      <c r="M37" s="46"/>
-      <c r="N37" s="46"/>
-    </row>
-    <row r="38" spans="1:14" s="1" customFormat="1">
-      <c r="A38" s="46"/>
-      <c r="B38" s="46"/>
-      <c r="C38" s="38" t="s">
-        <v>485</v>
-      </c>
-      <c r="D38" s="38" t="s">
-        <v>486</v>
-      </c>
-      <c r="E38" s="46"/>
-      <c r="F38" s="46"/>
-      <c r="G38" s="46"/>
-      <c r="H38" s="46"/>
-      <c r="I38" s="46"/>
-      <c r="J38" s="46"/>
-      <c r="K38" s="46"/>
-      <c r="L38" s="46"/>
-      <c r="M38" s="46"/>
-      <c r="N38" s="46"/>
-    </row>
-    <row r="39" spans="1:14" s="1" customFormat="1">
-      <c r="A39" s="46"/>
-      <c r="B39" s="46"/>
-      <c r="C39" s="38" t="s">
-        <v>490</v>
-      </c>
-      <c r="D39" s="39" t="s">
-        <v>491</v>
-      </c>
-      <c r="E39" s="46"/>
-      <c r="F39" s="46"/>
-      <c r="G39" s="46"/>
-      <c r="H39" s="46"/>
-      <c r="I39" s="46"/>
-      <c r="J39" s="46"/>
-      <c r="K39" s="46"/>
-      <c r="L39" s="46"/>
-      <c r="M39" s="46"/>
-      <c r="N39" s="46"/>
-    </row>
-    <row r="40" spans="1:14" s="1" customFormat="1">
-      <c r="A40" s="46"/>
-      <c r="B40" s="46"/>
       <c r="C40" s="38" t="s">
-        <v>495</v>
-      </c>
-      <c r="D40" s="39" t="s">
-        <v>496</v>
-      </c>
-      <c r="E40" s="46"/>
-      <c r="F40" s="46"/>
-      <c r="G40" s="46"/>
-      <c r="H40" s="46"/>
-      <c r="I40" s="46"/>
-      <c r="J40" s="46"/>
-      <c r="K40" s="46"/>
-      <c r="L40" s="46"/>
-      <c r="M40" s="46"/>
-      <c r="N40" s="46"/>
+        <v>2</v>
+      </c>
+      <c r="D40" s="38" t="s">
+        <v>83</v>
+      </c>
+      <c r="E40" s="38"/>
+      <c r="F40" s="38"/>
+      <c r="G40" s="38"/>
+      <c r="H40" s="38"/>
+      <c r="I40" s="38"/>
+      <c r="J40" s="38"/>
+      <c r="K40" s="38"/>
+      <c r="L40" s="38"/>
+      <c r="M40" s="38"/>
+      <c r="N40" s="38"/>
     </row>
     <row r="41" spans="1:14" s="1" customFormat="1">
-      <c r="A41" s="46"/>
-      <c r="B41" s="46" t="s">
-        <v>501</v>
-      </c>
+      <c r="A41" s="58"/>
+      <c r="B41" s="58"/>
       <c r="C41" s="38" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="D41" s="38" t="s">
-        <v>46</v>
+        <v>540</v>
       </c>
       <c r="E41" s="38"/>
       <c r="F41" s="38"/>
@@ -7583,13 +8013,13 @@
       <c r="N41" s="38"/>
     </row>
     <row r="42" spans="1:14" s="1" customFormat="1">
-      <c r="A42" s="46"/>
-      <c r="B42" s="46"/>
-      <c r="C42" s="38" t="s">
-        <v>503</v>
-      </c>
-      <c r="D42" s="38" t="s">
-        <v>504</v>
+      <c r="A42" s="58"/>
+      <c r="B42" s="58" t="s">
+        <v>565</v>
+      </c>
+      <c r="C42" s="58"/>
+      <c r="D42" s="40" t="s">
+        <v>95</v>
       </c>
       <c r="E42" s="38"/>
       <c r="F42" s="38"/>
@@ -7603,13 +8033,13 @@
       <c r="N42" s="38"/>
     </row>
     <row r="43" spans="1:14" s="1" customFormat="1">
-      <c r="A43" s="46"/>
-      <c r="B43" s="46" t="s">
-        <v>530</v>
-      </c>
-      <c r="C43" s="46"/>
-      <c r="D43" s="40" t="s">
-        <v>58</v>
+      <c r="A43" s="58"/>
+      <c r="B43" s="58" t="s">
+        <v>99</v>
+      </c>
+      <c r="C43" s="58"/>
+      <c r="D43" s="38" t="s">
+        <v>574</v>
       </c>
       <c r="E43" s="38"/>
       <c r="F43" s="38"/>
@@ -7622,45 +8052,23 @@
       <c r="M43" s="38"/>
       <c r="N43" s="38"/>
     </row>
-    <row r="44" spans="1:14" s="1" customFormat="1">
-      <c r="A44" s="46"/>
-      <c r="B44" s="46" t="s">
-        <v>62</v>
-      </c>
-      <c r="C44" s="46"/>
-      <c r="D44" s="38" t="s">
-        <v>539</v>
-      </c>
-      <c r="E44" s="38"/>
-      <c r="F44" s="38"/>
-      <c r="G44" s="38"/>
-      <c r="H44" s="38"/>
-      <c r="I44" s="38"/>
-      <c r="J44" s="38"/>
-      <c r="K44" s="38"/>
-      <c r="L44" s="38"/>
-      <c r="M44" s="38"/>
-      <c r="N44" s="38"/>
-    </row>
   </sheetData>
-  <mergeCells count="57">
-    <mergeCell ref="I1:J1"/>
+  <mergeCells count="56">
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B15:C15"/>
+    <mergeCell ref="I1:J1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:C2"/>
     <mergeCell ref="D1:D2"/>
-    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A12:A16"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
     <mergeCell ref="A3:A11"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
@@ -7668,6 +8076,7 @@
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B11:C11"/>
     <mergeCell ref="K12:L12"/>
     <mergeCell ref="M12:N12"/>
     <mergeCell ref="B13:C13"/>
@@ -7679,417 +8088,34 @@
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="I12:J12"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:A31"/>
-    <mergeCell ref="B19:B27"/>
-    <mergeCell ref="E19:F27"/>
-    <mergeCell ref="G19:H27"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A18:A30"/>
+    <mergeCell ref="B18:B26"/>
+    <mergeCell ref="E18:F26"/>
+    <mergeCell ref="G18:H26"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="I19:J27"/>
-    <mergeCell ref="K19:L27"/>
-    <mergeCell ref="M19:N27"/>
+    <mergeCell ref="I18:J26"/>
+    <mergeCell ref="K18:L26"/>
+    <mergeCell ref="M18:N26"/>
+    <mergeCell ref="B27:C27"/>
     <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="A32:A44"/>
-    <mergeCell ref="B32:B40"/>
-    <mergeCell ref="E32:F40"/>
-    <mergeCell ref="G32:H40"/>
-    <mergeCell ref="I32:J40"/>
-    <mergeCell ref="K32:L40"/>
-    <mergeCell ref="M32:N40"/>
-    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="A31:A43"/>
+    <mergeCell ref="B31:B39"/>
+    <mergeCell ref="E31:F39"/>
+    <mergeCell ref="G31:H39"/>
+    <mergeCell ref="I31:J39"/>
+    <mergeCell ref="K31:L39"/>
+    <mergeCell ref="M31:N39"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="B42:C42"/>
     <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0E62D68-85D6-4E11-B076-F1BCD7E7D187}">
-  <dimension ref="A1:C68"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="31.28515625" customWidth="1"/>
-    <col min="2" max="2" width="34.42578125" customWidth="1"/>
-    <col min="3" max="3" width="31.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1">
-      <c r="A1" s="3" t="s">
-        <v>540</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>541</v>
-      </c>
-      <c r="C1" s="41"/>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="40" t="s">
-        <v>502</v>
-      </c>
-      <c r="B2" s="40" t="s">
-        <v>542</v>
-      </c>
-      <c r="C2" s="41" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="42" t="s">
-        <v>544</v>
-      </c>
-      <c r="B3" s="42" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="42" t="s">
-        <v>546</v>
-      </c>
-      <c r="B4" s="42" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="42" t="s">
-        <v>548</v>
-      </c>
-      <c r="B5" s="42" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="42" t="s">
-        <v>550</v>
-      </c>
-      <c r="B6" s="42" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="42" t="s">
-        <v>552</v>
-      </c>
-      <c r="B7" s="43" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="42" t="s">
-        <v>554</v>
-      </c>
-      <c r="B8" s="42" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="42" t="s">
-        <v>556</v>
-      </c>
-      <c r="B9" s="42" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="42" t="s">
-        <v>558</v>
-      </c>
-      <c r="B10" s="42" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="42" t="s">
-        <v>560</v>
-      </c>
-      <c r="B11" s="42" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="42" t="s">
-        <v>562</v>
-      </c>
-      <c r="B12" s="42" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="42" t="s">
-        <v>564</v>
-      </c>
-      <c r="B13" s="42" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="42" t="s">
-        <v>566</v>
-      </c>
-      <c r="B14" s="42" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="42" t="s">
-        <v>568</v>
-      </c>
-      <c r="B15" s="42" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="42" t="s">
-        <v>570</v>
-      </c>
-      <c r="B16" s="42" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="42" t="s">
-        <v>572</v>
-      </c>
-      <c r="B17" s="42" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="42" t="s">
-        <v>574</v>
-      </c>
-      <c r="B18" s="42" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="44"/>
-      <c r="B19" s="44"/>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="44"/>
-      <c r="B20" s="44"/>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="44"/>
-      <c r="B21" s="44"/>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="44"/>
-      <c r="B22" s="44"/>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="44"/>
-      <c r="B23" s="44"/>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="44"/>
-      <c r="B24" s="44"/>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="44"/>
-      <c r="B25" s="44"/>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="44"/>
-      <c r="B26" s="44"/>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="44"/>
-      <c r="B27" s="44"/>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="44"/>
-      <c r="B28" s="44"/>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" s="44"/>
-      <c r="B29" s="44"/>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="44"/>
-      <c r="B30" s="44"/>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="44"/>
-      <c r="B31" s="44"/>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" s="44"/>
-      <c r="B32" s="44"/>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" s="44"/>
-      <c r="B33" s="44"/>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" s="44"/>
-      <c r="B34" s="44"/>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" s="44"/>
-      <c r="B35" s="44"/>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" s="44"/>
-      <c r="B36" s="44"/>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="44"/>
-      <c r="B37" s="44"/>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" s="44"/>
-      <c r="B38" s="44"/>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" s="44"/>
-      <c r="B39" s="44"/>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" s="44"/>
-      <c r="B40" s="44"/>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="44"/>
-      <c r="B41" s="44"/>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" s="44"/>
-      <c r="B42" s="44"/>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43" s="44"/>
-      <c r="B43" s="44"/>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44" s="44"/>
-      <c r="B44" s="44"/>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45" s="44"/>
-      <c r="B45" s="44"/>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46" s="44"/>
-      <c r="B46" s="44"/>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" s="44"/>
-      <c r="B47" s="44"/>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" s="44"/>
-      <c r="B48" s="44"/>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" s="44"/>
-      <c r="B49" s="44"/>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" s="44"/>
-      <c r="B50" s="44"/>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51" s="44"/>
-      <c r="B51" s="44"/>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52" s="44"/>
-      <c r="B52" s="44"/>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53" s="44"/>
-      <c r="B53" s="44"/>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" s="44"/>
-      <c r="B54" s="44"/>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55" s="44"/>
-      <c r="B55" s="44"/>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="A56" s="44"/>
-      <c r="B56" s="44"/>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57" s="44"/>
-      <c r="B57" s="44"/>
-    </row>
-    <row r="58" spans="1:2">
-      <c r="A58" s="44"/>
-      <c r="B58" s="44"/>
-    </row>
-    <row r="59" spans="1:2">
-      <c r="A59" s="44"/>
-      <c r="B59" s="44"/>
-    </row>
-    <row r="60" spans="1:2">
-      <c r="A60" s="44"/>
-      <c r="B60" s="44"/>
-    </row>
-    <row r="61" spans="1:2">
-      <c r="A61" s="44"/>
-      <c r="B61" s="44"/>
-    </row>
-    <row r="62" spans="1:2">
-      <c r="A62" s="44"/>
-      <c r="B62" s="44"/>
-    </row>
-    <row r="63" spans="1:2">
-      <c r="A63" s="44"/>
-      <c r="B63" s="44"/>
-    </row>
-    <row r="64" spans="1:2">
-      <c r="A64" s="44"/>
-      <c r="B64" s="44"/>
-    </row>
-    <row r="65" spans="1:2">
-      <c r="A65" s="44"/>
-      <c r="B65" s="44"/>
-    </row>
-    <row r="66" spans="1:2">
-      <c r="A66" s="44"/>
-      <c r="B66" s="44"/>
-    </row>
-    <row r="67" spans="1:2">
-      <c r="A67" s="44"/>
-      <c r="B67" s="44"/>
-    </row>
-    <row r="68" spans="1:2">
-      <c r="A68" s="44"/>
-      <c r="B68" s="44"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cb815603-3128-4aee-956f-7cdc70044e75">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="6bc95d49-17e3-4d0a-929b-830fe3aa2f74" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Tài liệu" ma:contentTypeID="0x01010005FFA18751C0744EA482910462967CE1" ma:contentTypeVersion="14" ma:contentTypeDescription="Tạo tài liệu mới." ma:contentTypeScope="" ma:versionID="ccb1c2cb59a6d87295d36fd0bb2c7bf9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6bc95d49-17e3-4d0a-929b-830fe3aa2f74" xmlns:ns3="cb815603-3128-4aee-956f-7cdc70044e75" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e7fb121f459fab52ba0e926b4f132522" ns2:_="" ns3:_="">
     <xsd:import namespace="6bc95d49-17e3-4d0a-929b-830fe3aa2f74"/>
@@ -8318,14 +8344,34 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cb815603-3128-4aee-956f-7cdc70044e75">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="6bc95d49-17e3-4d0a-929b-830fe3aa2f74" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{059D3F59-86D6-44A9-B7D5-015CA0B15632}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FAE44C8-DF97-4C2B-A6B5-D921CCAD45C2}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32957C99-1122-410C-A6E5-151072F54127}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{059D3F59-86D6-44A9-B7D5-015CA0B15632}"/>
 </file>